--- a/analysis_outputs/Analysis_Summary.xlsx
+++ b/analysis_outputs/Analysis_Summary.xlsx
@@ -20,6 +20,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T9_Other_Fish" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T10_Margin_Summary" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T11_Retail_Price_by_Market" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T12_Pair_Detail" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T12b_Wilcoxon_Result" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T13_Species_Market_Spread" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T14_Species_Market_KruskalWalli" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T14b_Dunn_Holm_Posthoc" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T15_Payment_Actor_ChiSquare" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T16_Stratum_Margin_MannWhitney" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T17_Retailer_MC_Profit_Spearman" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -31,7 +39,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +70,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
@@ -94,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -114,6 +127,10 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E16"/>
+  <dimension ref="B2:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="2" max="2"/>
@@ -738,6 +755,150 @@
       </c>
       <c r="E16" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>T12_Pair_Detail</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Table 12. Matched buyer-seller pairs (Pair_ID)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>16</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>T12b_Wilcoxon_Result</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Table 12b. Wilcoxon signed-rank test on matched pairs</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>T13_Species_Market_Spread</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Table 13. Species x market price spread (BDT/kg)</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>60</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>T14_Species_Market_KruskalWalli</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Table 14. Kruskal-Wallis: species price across markets</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>T14b_Dunn_Holm_Posthoc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Table 14b. Dunn-Holm pairwise market comparisons</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>41</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>T15_Payment_Actor_ChiSquare</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Table 15. Payment mode x actor chi-square</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>T16_Stratum_Margin_MannWhitney</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Table 16. Trader stratum margins and Mann-Whitney tests</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>T17_Retailer_MC_Profit_Spearman</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Table 17. Retailer marketing cost vs net margin (Spearman)</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>31</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1291,7 +1452,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>All values are unweighted means of species-level means, so levels are composition-consistent (identical to the ALL row of Table 3). Margin % is expressed as a share of the pooled consumer price; producer's share is the classic marketing-efficiency measure.</t>
+          <t>Unweighted means of species-level means over chain-complete species only (n_species=9; see Table 3 note). Producer &amp; auction prices from landing-linked markets M1/M6 (first-sale proxy, Methodology 3.11c); wholesale price = Bepari sell over all markets; retail price = consumer-paid anchor (Form C slips). Margins are differences of consecutive level means, so they sum exactly to the total spread and PS% + spread% = 100. Margin % is expressed as a share of the pooled consumer price.</t>
         </is>
       </c>
     </row>
@@ -1318,19 +1479,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Aratdar (auction margin)</t>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Aratdar (auction margin, M1/M6)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>24.81</v>
+        <v>25.79</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -1340,29 +1501,29 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>62.57</v>
+        <v>92.72</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>8.5</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Retailer (khuchra margin)</t>
+          <t>Retailer (margin to consumer)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>122.18</v>
+        <v>111.41</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>16.7</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="8">
@@ -1372,13 +1533,13 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>191.2</v>
+        <v>229.92</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>26.1</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="9">
@@ -1388,10 +1549,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>73.90000000000001</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1688,6 +1849,4765 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:L20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Table 12. Matched buyer-seller pairs (Pair_ID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Matched-pair transaction prices (Methodology 3.3.4). Seller_sell = the seller's quoted sale price of the lot; Buyer_buy = the buyer's quoted purchase price of the same lot. Diff = seller sell - buyer buy (≈ 0 if self-reports are consistent). Complete = both sides quoted numerically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Pair_ID</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Species_code</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Seller_ID</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Seller_actor</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Seller_sell_BDT_kg</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Buyer_ID</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Buyer_actor</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>Buyer_buy_BDT_kg</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>Diff_BDT_kg</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PAIR-M1-01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M1-A-03</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1024.92</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>M1-R-01</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>1030</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>-5.08</v>
+      </c>
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>PAIR-M1-02</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>M1-A-04</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>1145.5</v>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>M1-R-04</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>1145</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L6" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PAIR-M1-03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>M1-A-05</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1004.82</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>M1-R-02</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>1005</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>PAIR-M2-01</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>M2-A-05</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>435.42</v>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>M2-R-02</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>435</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L8" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PAIR-M2-02</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>M2-A-02</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1292.87</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>M2-R-05</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1290</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>PAIR-M3-01</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>M3-A-03</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>1091.91</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>M3-R-01</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>1095</v>
+      </c>
+      <c r="K10" s="16" t="n">
+        <v>-3.09</v>
+      </c>
+      <c r="L10" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PAIR-M3-02</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="L11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>PAIR-M3-03</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>M3-A-01</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>468.92</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>M3-R-02</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>465</v>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="L12" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PAIR-M4-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>M4-A-04</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>1205.79</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>M4-R-03</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>1205</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>PAIR-M4-02</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>M4-A-03</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>401.93</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>M4-R-05</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>401.93</v>
+      </c>
+      <c r="K14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PAIR-M5-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>M5-A-04</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>468.92</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>M5-R-03</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>465</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>PAIR-M5-02</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>M5-A-02</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>1138.8</v>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>M5-R-01</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>1135</v>
+      </c>
+      <c r="K16" s="16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L16" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PAIR-M5-03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>PAIR-M6-01</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>M6-A-04</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>1185.69</v>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>M6-R-05</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>1185</v>
+      </c>
+      <c r="K18" s="16" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L18" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PAIR-M6-02</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>M6-A-01</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>415.33</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>M6-R-04</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>415</v>
+      </c>
+      <c r="K19" s="15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>PAIR-M6-03</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>M6-A-02</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>422.03</v>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>M6-R-03</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="K20" s="16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="L20" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Table 12b. Wilcoxon signed-rank test on matched pairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Wilcoxon signed-rank on paired differences (seller's sell - buyer's buy) of the same matched lot (Methodology 3.3.4). Diagnostic consistency check, not a powered hypothesis test; report n alongside the result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Usable matched pairs (n)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Pairs with non-zero difference</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Median difference (BDT/kg)</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="n">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Mean difference (BDT/kg)</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Wilcoxon W statistic</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>p-value (two-sided)</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="n">
+        <v>0.1157</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Interpretation</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>p &gt;= 0.05: seller-sell and buyer-buy quotes of matched lots do not differ systematically - self-reported chain prices are internally consistent</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:K64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Table 13. Species x market price spread (BDT/kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Species x market price decomposition. Wholesale = Bepari/Faria sell quotes; Retailer quote = khuchra sell quotes; Consumer = Form C slips. The difference between quote- and paid-based margins reflects bargaining at retail. Cells with n=0 are not observed. Per Methodology 3.8 cells with n&lt;5 support descriptive statements only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Wholesale_sell_mean</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>n_wholesale</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Retailer_sell_quote_mean</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>n_retailer</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Consumer_paid_mean</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>n_consumer</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>Retail_margin_quote_BDT_kg</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>Retail_margin_paid_BDT_kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1138.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1416.25</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>1352.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>277.45</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>213.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1266.08</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>1480</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8" t="n">
+        <v>213.92</v>
+      </c>
+      <c r="K6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1333.07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1491</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1456.67</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>157.93</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>123.6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>1225.88</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>1496.76</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="8" t="n">
+        <v>270.88</v>
+      </c>
+      <c r="K8" s="7" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>1282.82</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>1570.75</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>287.93</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>1244.31</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>1445</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>1445</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="8" t="n">
+        <v>200.69</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>200.69</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>1309.62</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>1586</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1475</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>276.38</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>165.38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>1415.13</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>1603.33</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>188.2</v>
+      </c>
+      <c r="K12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1426.85</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1645</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>218.15</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>1343.11</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>1596.67</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>253.56</v>
+      </c>
+      <c r="K14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1429.53</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>1717.17</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1685</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>287.64</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>255.47</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>1321.34</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>1590</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="8" t="n">
+        <v>268.66</v>
+      </c>
+      <c r="K16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>817.26</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>886.48</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>1080</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>1055</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>193.52</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>168.52</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>895.41</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>1046.67</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>151.26</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>877.54</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>919.41</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>1112.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>1075</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>193.09</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>155.59</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>866.38</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>1045</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>970</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="8" t="n">
+        <v>178.62</v>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>103.62</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>710.08</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>803.86</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>957.5</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H24" s="7" t="n"/>
+      <c r="I24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>153.64</v>
+      </c>
+      <c r="K24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>788.23</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>938.33</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>925</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>150.1</v>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>136.77</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>743.5700000000001</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>895</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>860</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>151.43</v>
+      </c>
+      <c r="K26" s="8" t="n">
+        <v>116.43</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>790.46</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>963.33</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="6" t="n">
+        <v>172.87</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>741.89</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>902.5</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>877.5</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>160.61</v>
+      </c>
+      <c r="K28" s="8" t="n">
+        <v>135.61</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>485</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>565</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>545</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="15" t="n">
+        <v>80</v>
+      </c>
+      <c r="K29" s="15" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>495.71</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>585</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>615</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="16" t="n">
+        <v>89.29000000000001</v>
+      </c>
+      <c r="K30" s="8" t="n">
+        <v>119.29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>527.53</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>613.75</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>590</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="15" t="n">
+        <v>86.22</v>
+      </c>
+      <c r="K31" s="15" t="n">
+        <v>62.47</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>524.74</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>569.05</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>585</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" s="16" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="K32" s="16" t="n">
+        <v>60.26</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>518.04</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>611.53</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>610</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" s="15" t="n">
+        <v>93.48999999999999</v>
+      </c>
+      <c r="K33" s="15" t="n">
+        <v>91.95999999999999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>462.22</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>551</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>580</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="16" t="n">
+        <v>88.78</v>
+      </c>
+      <c r="K34" s="8" t="n">
+        <v>117.78</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>360.06</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>416.25</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>420</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" s="15" t="n">
+        <v>56.19</v>
+      </c>
+      <c r="K35" s="15" t="n">
+        <v>59.94</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="n">
+        <v>378.49</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>472.5</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>443.33</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" s="16" t="n">
+        <v>94.01000000000001</v>
+      </c>
+      <c r="K36" s="16" t="n">
+        <v>64.84</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>385.85</v>
+      </c>
+      <c r="E37" t="n">
+        <v>5</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>470</v>
+      </c>
+      <c r="G37" t="n">
+        <v>4</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>457.5</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" s="15" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="K37" s="15" t="n">
+        <v>71.65000000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>390.77</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>463.06</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>445</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" s="16" t="n">
+        <v>72.29000000000001</v>
+      </c>
+      <c r="K38" s="16" t="n">
+        <v>54.23</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>393</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>484.46</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>468.33</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" s="15" t="n">
+        <v>91.45999999999999</v>
+      </c>
+      <c r="K39" s="15" t="n">
+        <v>75.33</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>375.13</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>460</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="8" t="n">
+        <v>425</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="16" t="n">
+        <v>84.87</v>
+      </c>
+      <c r="K40" s="16" t="n">
+        <v>49.87</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>433.19</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>527.5</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>510</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="15" t="n">
+        <v>94.31</v>
+      </c>
+      <c r="K41" s="15" t="n">
+        <v>76.81</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>462.22</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>555</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="8" t="n">
+        <v>535</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="16" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="K42" s="16" t="n">
+        <v>72.78</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>448.82</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>595</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>550</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="6" t="n">
+        <v>146.18</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>101.18</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>455.52</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>562.7</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>530</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>107.18</v>
+      </c>
+      <c r="K44" s="16" t="n">
+        <v>74.48</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>455.52</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>547.5</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" s="15" t="n">
+        <v>91.98</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D46" s="8" t="n">
+        <v>462.22</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>505</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="8" t="n">
+        <v>490</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="16" t="n">
+        <v>42.78</v>
+      </c>
+      <c r="K46" s="16" t="n">
+        <v>27.78</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>251.88</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>310</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="15" t="n">
+        <v>58.12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="n"/>
+      <c r="E48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="7" t="n"/>
+      <c r="G48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="7" t="n"/>
+      <c r="I48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="7" t="n"/>
+      <c r="K48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>281.35</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="n">
+        <v>291.4</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="8" t="n">
+        <v>330</v>
+      </c>
+      <c r="I50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="7" t="n"/>
+      <c r="K50" s="16" t="n">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>340</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="7" t="n"/>
+      <c r="I52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="7" t="n"/>
+      <c r="K52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>246.67</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="n">
+        <v>219.72</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="7" t="n"/>
+      <c r="G54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="8" t="n">
+        <v>265</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" s="7" t="n"/>
+      <c r="K54" s="16" t="n">
+        <v>45.28</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>241.16</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" s="15" t="n">
+        <v>28.84</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="8" t="n">
+        <v>279.35</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" s="8" t="n">
+        <v>275</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" s="7" t="n"/>
+      <c r="K56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>241.16</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>270</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" s="15" t="n">
+        <v>28.84</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="n">
+        <v>235.8</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="7" t="n"/>
+      <c r="G58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="8" t="n">
+        <v>260</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="7" t="n"/>
+      <c r="K58" s="16" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>182.21</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="7" t="n"/>
+      <c r="G60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="I60" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="7" t="n"/>
+      <c r="K60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>230</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" s="7" t="n"/>
+      <c r="I62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="16" t="n">
+        <v>45.11</v>
+      </c>
+      <c r="K62" s="7" t="n"/>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="n">
+        <v>171.49</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="7" t="n"/>
+      <c r="G64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="7" t="n"/>
+      <c r="I64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="7" t="n"/>
+      <c r="K64" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:J14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Table 14. Kruskal-Wallis: species price across markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Kruskal-Wallis H (Methodology 3.8): do retailer selling prices of the same species differ across markets? Cells with n&gt;=5 in &gt;=3 markets use the pre-specified test; otherwise an exploratory tier (n&gt;=3) is flagged and species with thinner coverage are reported descriptively only (no pooled-across-species tests).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Local_name</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Test_tier</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Markets_qualifying</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>n_per_market</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>df</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ilish</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>exploratory (n&gt;=3)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>M1; M2; M3; M4; M5</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>M1=4; M2=4; M3=5; M4=4; M5=4</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>10.721</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>reject H0 (p&lt;0.05): prices differ across markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Rupchanda</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>exploratory (n&gt;=3)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>M1; M2; M3; M4; M5; M6</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>M1=5; M2=3; M3=4; M4=3; M5=3; M6=4</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>11.163</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>0.0482</v>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>reject H0 (p&lt;0.05): prices differ across markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lakkha</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>exploratory (n&gt;=3)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>M3; M5; M6</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>M3=3; M5=4; M6=5</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>6.121</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>reject H0 (p&lt;0.05): prices differ across markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Koral/Kurl</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>exploratory (n&gt;=3)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>M2; M3; M5; M6</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>M2=4; M3=3; M5=3; M6=4</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>7.741</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>fail to reject H0 (p&gt;=0.05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Surma</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>exploratory (n&gt;=3)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>M2; M3; M4; M5; M6</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>M2=3; M3=4; M4=4; M5=3; M6=5</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>reject H0 (p&lt;0.05): prices differ across markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Churi</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>exploratory (n&gt;=3)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>M1; M3; M4</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>M1=4; M3=4; M4=4</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>6.885</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>reject H0 (p&lt;0.05): prices differ across markets</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Poa</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>cells &lt; n threshold in &lt;3 markets -&gt; descriptive only</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Kankoita</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>cells &lt; n threshold in &lt;3 markets -&gt; descriptive only</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Loitta</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>cells &lt; n threshold in &lt;3 markets -&gt; descriptive only</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Harina</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>cells &lt; n threshold in &lt;3 markets -&gt; descriptive only</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:H45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Table 14b. Dunn-Holm pairwise market comparisons</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Dunn's post-hoc with Holm step-down (p_holm) following significant Kruskal-Wallis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Market_i</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Market_j</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>raw_p</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>p_holm</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>significant_0.05</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>-3.252</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>-1.937</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.4752</v>
+      </c>
+      <c r="G6" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>-1.769</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>0.6156</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>-1.655</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="G8" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>-1.598</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.1101</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>-1.491</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>0.1358</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="G10" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>-1.483</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>0.6861</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>-0.373</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>0.7092000000000001</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0.8474</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>-0.171</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>0.8641</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>-2.828</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>0.0702</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>2.548</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>0.1518</v>
+      </c>
+      <c r="G16" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>-2.171</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>-2.171</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="G18" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="n">
+        <v>-1.786</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>0.8144</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>1.526</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>0.1271</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="n">
+        <v>-1.186</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0.2358</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>0.2358</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>-1.135</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0.2563</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>-0.401</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>0.6884</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="n">
+        <v>-0.401</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0.6884</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>0.8204</v>
+      </c>
+      <c r="F26" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.8204</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>-0.178</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>0.8587</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="n">
+        <v>2.209</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="F30" s="16" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="G30" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>0.0814</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>-0.114</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="G32" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="n">
+        <v>2.883</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="F33" s="15" t="n">
+        <v>0.0394</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="n">
+        <v>2.669</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="G34" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="n">
+        <v>2.017</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="F35" s="15" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="G35" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>-1.887</v>
+      </c>
+      <c r="E36" s="16" t="n">
+        <v>0.0592</v>
+      </c>
+      <c r="F36" s="16" t="n">
+        <v>0.4145</v>
+      </c>
+      <c r="G36" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0.1261</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>0.7567</v>
+      </c>
+      <c r="G37" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>-1.07</v>
+      </c>
+      <c r="E38" s="16" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="F38" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="n">
+        <v>-1.019</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="F39" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="E40" s="16" t="n">
+        <v>0.4252</v>
+      </c>
+      <c r="F40" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="E42" s="16" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="F42" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="n">
+        <v>-2.509</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="F43" s="15" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="G43" t="b">
+        <v>1</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>-1.919</v>
+      </c>
+      <c r="E44" s="16" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="F44" s="16" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G44" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.5548999999999999</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>0.5548999999999999</v>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:G9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Table 15. Payment mode x actor chi-square</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Payment-mode adoption by trader class (Methodology 3.8 Q4). Chi-square on MFS-use frequency (Regular/Occasional/Never); where expected cell counts &lt; 5 the likelihood-ratio (G) test is reported alongside Pearson chi-square as the sparse-cell fallback. Consumer payment method is a separate question and appears in Tables 5/8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Actor</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>MFS_Regular</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>MFS_Occasional</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>MFS_Never</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>MFS_share_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Bepari/Faria</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>43.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Retailer</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>chi-square (actor x MFS frequency)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>chi2=1.22, df=4, p=0.8749, G-test p=0.8809</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Cramer's V / smallest expected count</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>V=0.082 / min exp=3.67</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -1970,6 +6890,879 @@
   <mergeCells count="1">
     <mergeCell ref="B3:J3"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Table 16. Trader stratum margins and Mann-Whitney tests</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Per-respondent mean own-quote margin = mean of (sell - buy) over species quoted with both prices on the interview day (Methodology 3.7.2: M = P_s - P_b). Mann-Whitney U per stratum pair (Q2); Holm adjustment is recommended when quoting all three comparisons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Actor</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Median_margin_BDT_kg</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>IQR_BDT_kg</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Mean_margin_BDT_kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>30.62</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Bepari_Faria</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>83.73999999999999</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>84.06999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>182</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>176.02</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Mann-Whitney U: Aratdar vs Bepari_Faria</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>30/30</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>U=0, p&lt;0.0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mann-Whitney U: Aratdar vs Khuchra</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>30/30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>U=0, p&lt;0.0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Mann-Whitney U: Bepari_Faria vs Khuchra</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>30/30</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+      <c r="E10" s="7" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>U=10, p&lt;0.0001</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Table 17. Retailer marketing cost vs net margin (Spearman)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Retailers only (daily cost structure is unambiguous): MC/kg = (stall rent + ice + wash/water/other, all BDT/day) / daily capacity kg; net margin = own-quote margin - MC/kg. Spearman rho between MC and net margin (Methodology 3.8 Q5). Other strata mix monthly/yearly/per-trip frequencies, so per-kg MC is not computed for them until the cost module defines the period consistently (flagged in review).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Respondent_ID</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>Mean_margin_BDT_kg</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>MC_BDT_kg</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Net_profit_BDT_kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M1-R-01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>200</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>195.58</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>M1-R-02</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>218.75</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>210.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M1-R-03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>148.33</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>142.51</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>M1-R-04</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>175</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>169.94</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>M1-R-05</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>158.75</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>155.81</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>M2-R-01</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>198.33</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>189.86</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M2-R-02</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>111.33</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>M2-R-03</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>184</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>175.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M2-R-04</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>160</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>156.38</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>M2-R-05</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>193.38</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>M3-R-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>205</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>199.62</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>M3-R-02</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>154</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>149.76</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>M3-R-03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>201</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>197.6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>M3-R-04</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>192.5</v>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>188.27</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>M3-R-05</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>184</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>6.07</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>177.93</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>M4-R-01</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>129.34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>M4-R-02</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>133.33</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>130.31</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>M4-R-03</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>179</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>174.87</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M4-R-04</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>151</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>145.9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>M4-R-05</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>96.47</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <v>91.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>M5-R-01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>188.33</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>182.79</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>M5-R-02</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>171.25</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>166.54</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>M5-R-03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>202</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>197.63</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>M5-R-04</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="E28" s="16" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>195.21</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>M5-R-05</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>241.16</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>235.15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>M6-R-01</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>180</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>174.52</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>M6-R-02</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>142</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>137.94</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>M6-R-03</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>154.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>M6-R-04</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>201.25</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>196.76</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>M6-R-05</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="n">
+        <v>210</v>
+      </c>
+      <c r="E34" s="16" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>205.15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Spearman rho(MC, net margin)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>n=30</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" s="15" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="F35" s="15" t="n">
+        <v>0.0177</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2939,7 +8732,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.6" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="13.55" customWidth="1" min="5" max="5"/>
     <col width="17.75" customWidth="1" min="6" max="6"/>
@@ -2964,7 +8757,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Producer price = net auction price paid to fishers (Form A buy). Aratdar sell = auction hammer price to Bepari. Retailer sell = khuchra counter price. Consumer = focal-species retail purchases. Margins are simple differences of level means. K (not traded today) / D (refused) price flags excluded.</t>
+          <t>Producer price = net auction price paid to fishers (Form A buy) at the landing-linked markets M1/M6 only; Aratdar sell = auction hammer price at M1/M6; Bepari sell = Form B sell over all markets; Retailer sell = Form R vendor quote (descriptive; margins use the consumer-paid anchor); Consumer = focal-species purchases actually paid (Form C). Margins = differences of consecutive level means and telescope to the total spread. K/D-flagged prices excluded. Species without a complete chain show blank margins and are excluded from ALL (see Local_name note).</t>
         </is>
       </c>
     </row>
@@ -3060,10 +8853,10 @@
         <v>71</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1062.24</v>
+        <v>1031.62</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1113.6</v>
+        <v>1083.3</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>1236.41</v>
@@ -3075,19 +8868,19 @@
         <v>1420</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>51.36</v>
+        <v>51.68</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>122.81</v>
+        <v>153.11</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>250.55</v>
+        <v>183.59</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>357.76</v>
+        <v>388.38</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>74.8</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -3110,10 +8903,10 @@
         <v>64</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1183.09</v>
+        <v>1110.67</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1238.49</v>
+        <v>1165.59</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>1378.04</v>
@@ -3125,19 +8918,19 @@
         <v>1615</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>55.4</v>
+        <v>54.92</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>139.55</v>
+        <v>212.45</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>241.12</v>
+        <v>236.96</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>431.91</v>
+        <v>504.33</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>73.3</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="7">
@@ -3160,10 +8953,10 @@
         <v>52</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>767.02</v>
+        <v>735.53</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>800.6900000000001</v>
+        <v>771.7</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>886.61</v>
@@ -3175,19 +8968,19 @@
         <v>1033.33</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>33.67</v>
+        <v>36.17</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>85.92</v>
+        <v>114.91</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>183.03</v>
+        <v>146.72</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>266.31</v>
+        <v>297.8</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>74.2</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="8">
@@ -3210,10 +9003,10 @@
         <v>46</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>678.25</v>
+        <v>660.95</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>707.64</v>
+        <v>687.75</v>
       </c>
       <c r="H8" s="8" t="n">
         <v>762.77</v>
@@ -3225,19 +9018,19 @@
         <v>885</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>29.39</v>
+        <v>26.8</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>55.13</v>
+        <v>75.02</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>170.67</v>
+        <v>122.23</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>206.75</v>
+        <v>224.05</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>76.59999999999999</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="9">
@@ -3260,10 +9053,10 @@
         <v>74</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>427.85</v>
+        <v>407.79</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>447.15</v>
+        <v>428.72</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>501.77</v>
@@ -3275,19 +9068,19 @@
         <v>585</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>19.3</v>
+        <v>20.93</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>54.62</v>
+        <v>73.05</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>79.45999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>157.15</v>
+        <v>177.21</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>73.09999999999999</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="10">
@@ -3310,10 +9103,10 @@
         <v>63</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>324.76</v>
+        <v>314.1</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>336.93</v>
+        <v>323.55</v>
       </c>
       <c r="H10" s="8" t="n">
         <v>380.42</v>
@@ -3325,19 +9118,19 @@
         <v>446.54</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>12.17</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>43.49</v>
+        <v>56.87</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>76.70999999999999</v>
+        <v>66.12</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>121.78</v>
+        <v>132.44</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>72.7</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="11">
@@ -3360,10 +9153,10 @@
         <v>29</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>376.47</v>
+        <v>361.74</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>393.74</v>
+        <v>377.81</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>450.16</v>
@@ -3375,19 +9168,19 @@
         <v>530</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>17.27</v>
+        <v>16.07</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>56.42</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>95.29000000000001</v>
+        <v>79.84</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>153.53</v>
+        <v>168.26</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>71</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="12">
@@ -3410,10 +9203,10 @@
         <v>9</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>236.69</v>
+        <v>231.78</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>247.41</v>
+        <v>241.16</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>279.01</v>
@@ -3425,19 +9218,19 @@
         <v>330</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>10.72</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>31.6</v>
+        <v>37.85</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>45.99</v>
+        <v>50.99</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>93.31</v>
+        <v>98.22</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>71.7</v>
+        <v>70.2</v>
       </c>
     </row>
     <row r="13">
@@ -3460,10 +9253,10 @@
         <v>15</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>194.27</v>
+        <v>188.91</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>203.64</v>
+        <v>195.61</v>
       </c>
       <c r="H13" s="6" t="n">
         <v>234.46</v>
@@ -3475,19 +9268,19 @@
         <v>267.5</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>9.369999999999999</v>
+        <v>6.7</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>30.82</v>
+        <v>38.85</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>28.55</v>
+        <v>33.04</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>73.23</v>
+        <v>78.59</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>72.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -3510,11 +9303,9 @@
         <v>6</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>164.79</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>174.17</v>
-      </c>
+        <v>163.45</v>
+      </c>
+      <c r="G14" s="7" t="n"/>
       <c r="H14" s="8" t="n">
         <v>179.53</v>
       </c>
@@ -3524,20 +9315,12 @@
       <c r="J14" s="8" t="n">
         <v>215</v>
       </c>
-      <c r="K14" s="8" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="M14" s="8" t="n">
-        <v>50.47</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>50.21</v>
-      </c>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="7" t="n"/>
+      <c r="N14" s="7" t="n"/>
       <c r="O14" s="8" t="n">
-        <v>76.59999999999999</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15">
@@ -3546,9 +9329,9 @@
           <t>ALL</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Mean of species means</t>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Mean of species means (chain-complete: S01, S02, S03, S04, S05, S06, S07, S08, S09)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3557,37 +9340,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>541.54</v>
+        <v>560.34</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>566.35</v>
+        <v>586.13</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>628.92</v>
+        <v>678.85</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>751.1</v>
+        <v>809</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>732.74</v>
+        <v>790.26</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>24.81</v>
+        <v>25.79</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>62.57</v>
+        <v>92.72</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>122.18</v>
+        <v>111.41</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>191.2</v>
+        <v>229.92</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>73.90000000000001</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3750,7 +9533,6 @@
       <c r="G7" s="6" t="n">
         <v>9440.799999999999</v>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="B8" s="7" t="inlineStr">
@@ -3804,7 +9586,6 @@
       <c r="G9" s="6" t="n">
         <v>2223.17</v>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
@@ -3862,7 +9643,6 @@
       <c r="G11" s="6" t="n">
         <v>122.43</v>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="B12" s="7" t="inlineStr">
@@ -3974,7 +9754,6 @@
       <c r="G15" s="6" t="n">
         <v>0.84</v>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
@@ -4028,7 +9807,6 @@
       <c r="G17" s="6" t="n">
         <v>27.03</v>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
@@ -4082,7 +9860,6 @@
       <c r="G19" s="6" t="n">
         <v>0.96</v>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="7" t="inlineStr">
@@ -4136,7 +9913,6 @@
       <c r="G21" s="6" t="n">
         <v>1.86</v>
       </c>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="B22" s="7" t="inlineStr">
@@ -4190,7 +9966,6 @@
       <c r="G23" s="6" t="n">
         <v>56.54</v>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="7" t="inlineStr">
@@ -4244,7 +10019,6 @@
       <c r="G25" s="6" t="n">
         <v>1.77</v>
       </c>
-      <c r="H25" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/analysis_outputs/Analysis_Summary.xlsx
+++ b/analysis_outputs/Analysis_Summary.xlsx
@@ -28,6 +28,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T15_Payment_Actor_ChiSquare" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T16_Stratum_Margin_MannWhitney" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T17_Retailer_MC_Profit_Spearman" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T18_ShapiroWilk_Screening" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -496,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E24"/>
+  <dimension ref="B2:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="2" max="2"/>
@@ -610,7 +611,7 @@
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -711,7 +712,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Table 9. Other fish/items purchased by consumers</t>
+          <t>Table 9. Other aquatic products purchased by consumers</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -898,6 +899,24 @@
         <v>31</v>
       </c>
       <c r="E24" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>T18_ShapiroWilk_Screening</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Table 18. Shapiro-Wilk normality screening</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1258,14 +1277,14 @@
     <row r="2">
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Table 9. Other fish/items purchased by consumers</t>
+          <t>Table 9. Other aquatic products purchased by consumers</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Non-focal marine items consumers reported buying (Consumer_Other_Fish sheet).</t>
+          <t>Non-focal aquatic items consumers reported buying on the interview day (Consumer_Other_Fish sheet). Includes crustaceans (Bagda shrimp, Kakra crab) and finfish (Khoira, Datina, Moid, Faisya, lobster) - comparison items outside the ten focal marine-finfish species of Table 3.4.</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6486,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Payment-mode adoption by trader class (Methodology 3.8 Q4). Chi-square on MFS-use frequency (Regular/Occasional/Never); where expected cell counts &lt; 5 the likelihood-ratio (G) test is reported alongside Pearson chi-square as the sparse-cell fallback. Consumer payment method is a separate question and appears in Tables 5/8.</t>
+          <t>Payment-mode adoption by trader class (Methodology 3.8 Q4). Chi-square on MFS-use frequency (Regular/Occasional/Never); because the smallest expected cell &lt; 5, sparse-cell fallbacks are reported alongside Pearson chi-square: the likelihood-ratio (G) test and the exact Freeman-Halton/Fisher test (p from the marginal-conditional enumeration). Consumer payment method is a separate question and appears in Tables 5/8.</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6602,7 @@
       <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>chi2=1.22, df=4, p=0.8749, G-test p=0.8809</t>
+          <t>chi2=1.22, df=4, p=0.8749, G-test p=0.8809, Fisher-exact p=0.8945</t>
         </is>
       </c>
     </row>
@@ -7760,6 +7779,166 @@
       </c>
       <c r="F35" s="15" t="n">
         <v>0.0177</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>Table 18. Shapiro-Wilk normality screening</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Shapiro-Wilk screening on pooled price series run BEFORE any inferential test, as pre-registered in Methodology 3.8 ('confirmed here by Shapiro-Wilk screening on the pooled series before any test is applied'). Screening motivates the distribution-free battery (Kruskal-Wallis/Mann-Whitney/Wilcoxon) used in Tables 12b/14/16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Series</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>p_value</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Producer price - landing markets M1/M6 (Form A buy)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>47</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>0.8544</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>p&lt;=0.05 - non-normal; nonparametric tests used</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Aratdar auction sell - M1/M6</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>47</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>0.8457</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>p&lt;=0.05 - non-normal; nonparametric tests used</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bepari/Faria sell - all markets</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>135</v>
+      </c>
+      <c r="D7" s="15" t="n">
+        <v>0.9076</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>p&lt;=0.05 - non-normal; nonparametric tests used</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Khuchra retailer sell quotes - all markets</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>128</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>0.8967000000000001</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>p&lt;=0.05 - non-normal; nonparametric tests used</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Consumer-paid prices (Form C slips)</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>52</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>p&lt;=0.05 - non-normal; nonparametric tests used</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -8728,23 +8907,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:O15"/>
+  <dimension ref="B2:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.6" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="13.55" customWidth="1" min="5" max="5"/>
-    <col width="17.75" customWidth="1" min="6" max="6"/>
-    <col width="21.95" customWidth="1" min="7" max="7"/>
-    <col width="20.9" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="24.05" customWidth="1" min="11" max="11"/>
+    <col width="18.8" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="17.75" customWidth="1" min="8" max="8"/>
+    <col width="21.95" customWidth="1" min="9" max="9"/>
+    <col width="20.9" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="25.1" customWidth="1" min="13" max="13"/>
-    <col width="21.95" customWidth="1" min="14" max="14"/>
-    <col width="20.9" customWidth="1" min="15" max="15"/>
+    <col width="24.05" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
+    <col width="25.1" customWidth="1" min="15" max="15"/>
+    <col width="21.95" customWidth="1" min="16" max="16"/>
+    <col width="20.9" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -8757,7 +8938,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Producer price = net auction price paid to fishers (Form A buy) at the landing-linked markets M1/M6 only; Aratdar sell = auction hammer price at M1/M6; Bepari sell = Form B sell over all markets; Retailer sell = Form R vendor quote (descriptive; margins use the consumer-paid anchor); Consumer = focal-species purchases actually paid (Form C). Margins = differences of consecutive level means and telescope to the total spread. K/D-flagged prices excluded. Species without a complete chain show blank margins and are excluded from ALL (see Local_name note).</t>
+          <t>Producer price = net auction price paid to fishers (Form A buy) at the landing-linked markets M1/M6 only; Aratdar sell = auction hammer price at M1/M6; Bepari sell = Form B sell over all markets; Retailer sell = Form R vendor quote (descriptive; margins use the consumer-paid anchor); Consumer = focal-species purchases actually paid (Form C). Margins = differences of consecutive level means and telescope to the total spread. K/D-flagged prices excluded. Species without a complete chain show blank margins and are excluded from ALL (see Local_name note). Reporting_status marks species observed in fewer than three markets as descriptive-only (Methodology 3.8): S08/S09/S10 quotes are few and their share figures are indicative, not inferential.</t>
         </is>
       </c>
     </row>
@@ -8784,50 +8965,60 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
+          <t>Retail_markets_n</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Reporting_status</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
           <t>Producer_BDT_kg</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Aratdar_sell_BDT_kg</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Bepari_sell_BDT_kg</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Retailer_sell_BDT_kg</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Consumer_paid_BDT_kg</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Aratdar_margin_BDT_kg</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Bepari_margin_BDT_kg</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>Retailer_margin_BDT_kg</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>Total_spread_BDT_kg</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>Producer_share_pct</t>
         </is>
@@ -8853,33 +9044,36 @@
         <v>71</v>
       </c>
       <c r="F5" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>1031.62</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>1083.3</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>1236.41</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>1486.96</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="L5" s="6" t="n">
         <v>1420</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="M5" s="6" t="n">
         <v>51.68</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="N5" s="6" t="n">
         <v>153.11</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="O5" s="6" t="n">
         <v>183.59</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="P5" s="6" t="n">
         <v>388.38</v>
       </c>
-      <c r="O5" s="6" t="n">
+      <c r="Q5" s="6" t="n">
         <v>72.59999999999999</v>
       </c>
     </row>
@@ -8903,33 +9097,37 @@
         <v>64</v>
       </c>
       <c r="F6" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="8" t="n">
         <v>1110.67</v>
       </c>
-      <c r="G6" s="8" t="n">
+      <c r="I6" s="8" t="n">
         <v>1165.59</v>
       </c>
-      <c r="H6" s="8" t="n">
+      <c r="J6" s="8" t="n">
         <v>1378.04</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="K6" s="8" t="n">
         <v>1619.16</v>
       </c>
-      <c r="J6" s="8" t="n">
+      <c r="L6" s="8" t="n">
         <v>1615</v>
       </c>
-      <c r="K6" s="8" t="n">
+      <c r="M6" s="8" t="n">
         <v>54.92</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="N6" s="8" t="n">
         <v>212.45</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="O6" s="8" t="n">
         <v>236.96</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="P6" s="8" t="n">
         <v>504.33</v>
       </c>
-      <c r="O6" s="8" t="n">
+      <c r="Q6" s="8" t="n">
         <v>68.8</v>
       </c>
     </row>
@@ -8953,33 +9151,36 @@
         <v>52</v>
       </c>
       <c r="F7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="6" t="n">
         <v>735.53</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="I7" s="6" t="n">
         <v>771.7</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="J7" s="6" t="n">
         <v>886.61</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="K7" s="6" t="n">
         <v>1069.64</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="L7" s="6" t="n">
         <v>1033.33</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="M7" s="6" t="n">
         <v>36.17</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="N7" s="6" t="n">
         <v>114.91</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="O7" s="6" t="n">
         <v>146.72</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="P7" s="6" t="n">
         <v>297.8</v>
       </c>
-      <c r="O7" s="6" t="n">
+      <c r="Q7" s="6" t="n">
         <v>71.2</v>
       </c>
     </row>
@@ -9003,33 +9204,37 @@
         <v>46</v>
       </c>
       <c r="F8" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="8" t="n">
         <v>660.95</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="I8" s="8" t="n">
         <v>687.75</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="J8" s="8" t="n">
         <v>762.77</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="K8" s="8" t="n">
         <v>933.4400000000001</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="L8" s="8" t="n">
         <v>885</v>
       </c>
-      <c r="K8" s="8" t="n">
+      <c r="M8" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="L8" s="8" t="n">
+      <c r="N8" s="8" t="n">
         <v>75.02</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="O8" s="8" t="n">
         <v>122.23</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="P8" s="8" t="n">
         <v>224.05</v>
       </c>
-      <c r="O8" s="8" t="n">
+      <c r="Q8" s="8" t="n">
         <v>74.7</v>
       </c>
     </row>
@@ -9053,33 +9258,36 @@
         <v>74</v>
       </c>
       <c r="F9" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H9" s="6" t="n">
         <v>407.79</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="I9" s="6" t="n">
         <v>428.72</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="J9" s="6" t="n">
         <v>501.77</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>581.23</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="L9" s="6" t="n">
         <v>585</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="M9" s="6" t="n">
         <v>20.93</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="N9" s="6" t="n">
         <v>73.05</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="O9" s="6" t="n">
         <v>83.23</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="P9" s="6" t="n">
         <v>177.21</v>
       </c>
-      <c r="O9" s="6" t="n">
+      <c r="Q9" s="6" t="n">
         <v>69.7</v>
       </c>
     </row>
@@ -9103,33 +9311,37 @@
         <v>63</v>
       </c>
       <c r="F10" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="8" t="n">
         <v>314.1</v>
       </c>
-      <c r="G10" s="8" t="n">
+      <c r="I10" s="8" t="n">
         <v>323.55</v>
       </c>
-      <c r="H10" s="8" t="n">
+      <c r="J10" s="8" t="n">
         <v>380.42</v>
       </c>
-      <c r="I10" s="8" t="n">
+      <c r="K10" s="8" t="n">
         <v>457.13</v>
       </c>
-      <c r="J10" s="8" t="n">
+      <c r="L10" s="8" t="n">
         <v>446.54</v>
       </c>
-      <c r="K10" s="8" t="n">
+      <c r="M10" s="8" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="L10" s="8" t="n">
+      <c r="N10" s="8" t="n">
         <v>56.87</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="O10" s="8" t="n">
         <v>66.12</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="P10" s="8" t="n">
         <v>132.44</v>
       </c>
-      <c r="O10" s="8" t="n">
+      <c r="Q10" s="8" t="n">
         <v>70.3</v>
       </c>
     </row>
@@ -9153,33 +9365,36 @@
         <v>29</v>
       </c>
       <c r="F11" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="6" t="n">
         <v>361.74</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="I11" s="6" t="n">
         <v>377.81</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>450.16</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>545.45</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="L11" s="6" t="n">
         <v>530</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="M11" s="6" t="n">
         <v>16.07</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="N11" s="6" t="n">
         <v>72.34999999999999</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="O11" s="6" t="n">
         <v>79.84</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="P11" s="6" t="n">
         <v>168.26</v>
       </c>
-      <c r="O11" s="6" t="n">
+      <c r="Q11" s="6" t="n">
         <v>68.3</v>
       </c>
     </row>
@@ -9203,33 +9418,41 @@
         <v>9</v>
       </c>
       <c r="F12" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Descriptive-only (Method 3.8)</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
         <v>231.78</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="I12" s="8" t="n">
         <v>241.16</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="J12" s="8" t="n">
         <v>279.01</v>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="K12" s="8" t="n">
         <v>325</v>
       </c>
-      <c r="J12" s="8" t="n">
+      <c r="L12" s="8" t="n">
         <v>330</v>
       </c>
-      <c r="K12" s="8" t="n">
+      <c r="M12" s="8" t="n">
         <v>9.380000000000001</v>
       </c>
-      <c r="L12" s="8" t="n">
+      <c r="N12" s="8" t="n">
         <v>37.85</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="O12" s="8" t="n">
         <v>50.99</v>
       </c>
-      <c r="N12" s="8" t="n">
+      <c r="P12" s="8" t="n">
         <v>98.22</v>
       </c>
-      <c r="O12" s="8" t="n">
+      <c r="Q12" s="8" t="n">
         <v>70.2</v>
       </c>
     </row>
@@ -9253,33 +9476,41 @@
         <v>15</v>
       </c>
       <c r="F13" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Descriptive-only (Method 3.8)</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n">
         <v>188.91</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="I13" s="6" t="n">
         <v>195.61</v>
       </c>
-      <c r="H13" s="6" t="n">
+      <c r="J13" s="6" t="n">
         <v>234.46</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="K13" s="6" t="n">
         <v>263.01</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="L13" s="6" t="n">
         <v>267.5</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="M13" s="6" t="n">
         <v>6.7</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="N13" s="6" t="n">
         <v>38.85</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="O13" s="6" t="n">
         <v>33.04</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="P13" s="6" t="n">
         <v>78.59</v>
       </c>
-      <c r="O13" s="6" t="n">
+      <c r="Q13" s="6" t="n">
         <v>70.59999999999999</v>
       </c>
     </row>
@@ -9303,23 +9534,31 @@
         <v>6</v>
       </c>
       <c r="F14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Descriptive-only (Method 3.8)</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
         <v>163.45</v>
       </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="8" t="n">
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="8" t="n">
         <v>179.53</v>
       </c>
-      <c r="I14" s="8" t="n">
+      <c r="K14" s="8" t="n">
         <v>230</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="L14" s="8" t="n">
         <v>215</v>
       </c>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
       <c r="M14" s="7" t="n"/>
       <c r="N14" s="7" t="n"/>
-      <c r="O14" s="8" t="n">
+      <c r="O14" s="7" t="n"/>
+      <c r="P14" s="7" t="n"/>
+      <c r="Q14" s="8" t="n">
         <v>76</v>
       </c>
     </row>
@@ -9342,34 +9581,39 @@
       <c r="E15" t="n">
         <v>423</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Pooled over chain-complete species</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n">
         <v>560.34</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="I15" s="6" t="n">
         <v>586.13</v>
       </c>
-      <c r="H15" s="6" t="n">
+      <c r="J15" s="6" t="n">
         <v>678.85</v>
       </c>
-      <c r="I15" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>809</v>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="L15" s="6" t="n">
         <v>790.26</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="M15" s="6" t="n">
         <v>25.79</v>
       </c>
-      <c r="L15" s="6" t="n">
+      <c r="N15" s="6" t="n">
         <v>92.72</v>
       </c>
-      <c r="M15" s="6" t="n">
+      <c r="O15" s="6" t="n">
         <v>111.41</v>
       </c>
-      <c r="N15" s="6" t="n">
+      <c r="P15" s="6" t="n">
         <v>229.92</v>
       </c>
-      <c r="O15" s="6" t="n">
+      <c r="Q15" s="6" t="n">
         <v>70.90000000000001</v>
       </c>
     </row>
@@ -10377,14 +10621,14 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply syndicate control</t>
+          <t>Unsold fish spoilage loss</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>36.7</v>
+        <v>40</v>
       </c>
       <c r="E5" t="n">
         <v>9</v>
@@ -10393,10 +10637,10 @@
         <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>26.7</v>
+        <v>23.3</v>
       </c>
       <c r="I5" t="n">
         <v>28</v>
@@ -10408,14 +10652,14 @@
     <row r="6">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Unsold fish spoilage loss</t>
+          <t>Supply syndicate control</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>40</v>
+        <v>36.7</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>9</v>
@@ -10424,10 +10668,10 @@
         <v>30</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>23.3</v>
+        <v>26.7</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>28</v>
@@ -10532,26 +10776,26 @@
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Waterlogging during monsoon</t>
+          <t>Low landings in lean season</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>23.3</v>
+        <v>30</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>20</v>
+        <v>26.7</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>30</v>
+        <v>16.7</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>22</v>
@@ -10563,26 +10807,26 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Low landings in lean season</t>
+          <t>Waterlogging during monsoon</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G11" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="H11" s="6" t="n">
         <v>30</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>16.7</v>
       </c>
       <c r="I11" t="n">
         <v>22</v>
@@ -10592,22 +10836,22 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Rising cost of ice and salt</t>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Irregular electricity and load-shedding</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>26.7</v>
+        <v>13.3</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>7</v>
@@ -10623,22 +10867,22 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Irregular electricity and load-shedding</t>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rising cost of ice and salt</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>13.3</v>
+        <v>26.7</v>
       </c>
       <c r="G13" t="n">
         <v>7</v>

--- a/analysis_outputs/Analysis_Summary.xlsx
+++ b/analysis_outputs/Analysis_Summary.xlsx
@@ -10621,14 +10621,14 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unsold fish spoilage loss</t>
+          <t>Supply syndicate control</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>40</v>
+        <v>36.7</v>
       </c>
       <c r="E5" t="n">
         <v>9</v>
@@ -10637,10 +10637,10 @@
         <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>23.3</v>
+        <v>26.7</v>
       </c>
       <c r="I5" t="n">
         <v>28</v>
@@ -10652,14 +10652,14 @@
     <row r="6">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Supply syndicate control</t>
+          <t>Unsold fish spoilage loss</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>36.7</v>
+        <v>40</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>9</v>
@@ -10668,10 +10668,10 @@
         <v>30</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>26.7</v>
+        <v>23.3</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>28</v>
@@ -10900,20 +10900,20 @@
     <row r="14">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Rising toll and lease burden</t>
+          <t>Delayed credit recovery</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>26.7</v>
+        <v>23.3</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>7</v>
@@ -10931,20 +10931,20 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Delayed credit recovery</t>
+          <t>Rising toll and lease burden</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>23.3</v>
+        <v>26.7</v>
       </c>
       <c r="G15" t="n">
         <v>7</v>

--- a/analysis_outputs/Analysis_Summary.xlsx
+++ b/analysis_outputs/Analysis_Summary.xlsx
@@ -611,7 +611,7 @@
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -1471,7 +1471,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Unweighted means of species-level means over chain-complete species only (n_species=9; see Table 3 note). Producer &amp; auction prices from landing-linked markets M1/M6 (first-sale proxy, Methodology 3.11c); wholesale price = Bepari sell over all markets; retail price = consumer-paid anchor (Form C slips). Margins are differences of consecutive level means, so they sum exactly to the total spread and PS% + spread% = 100. Margin % is expressed as a share of the pooled consumer price.</t>
+          <t>Unweighted means of species-level means over chain-complete species only (n_species=8; see Table 3 note). Producer &amp; auction prices from landing-linked markets M1/M6 (first-sale proxy, Methodology 3.11c); wholesale price = Bepari sell over all markets; retail price = consumer-paid anchor (Form C slips). Margins are differences of consecutive level means, so they sum exactly to the total spread and PS% + spread% = 100. Margin % is expressed as a share of the pooled consumer price.</t>
         </is>
       </c>
     </row>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>25.79</v>
+        <v>27.84</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>3.3</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>92.72</v>
+        <v>99.58</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>11.7</v>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>111.41</v>
+        <v>118.97</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1552,10 +1552,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>229.92</v>
+        <v>246.39</v>
       </c>
       <c r="E8" s="8" t="n">
         <v>29.1</v>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>70.90000000000001</v>
@@ -8907,7 +8907,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:Q15"/>
+  <dimension ref="B2:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.6" customWidth="1" min="2" max="2"/>
@@ -8915,17 +8915,18 @@
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="13.55" customWidth="1" min="5" max="5"/>
     <col width="18.8" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="17.75" customWidth="1" min="8" max="8"/>
-    <col width="21.95" customWidth="1" min="9" max="9"/>
-    <col width="20.9" customWidth="1" min="10" max="10"/>
-    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="17.75" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="17.75" customWidth="1" min="9" max="9"/>
+    <col width="21.95" customWidth="1" min="10" max="10"/>
+    <col width="20.9" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="24.05" customWidth="1" min="13" max="13"/>
-    <col width="23" customWidth="1" min="14" max="14"/>
-    <col width="25.1" customWidth="1" min="15" max="15"/>
-    <col width="21.95" customWidth="1" min="16" max="16"/>
-    <col width="20.9" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="24.05" customWidth="1" min="14" max="14"/>
+    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="25.1" customWidth="1" min="16" max="16"/>
+    <col width="21.95" customWidth="1" min="17" max="17"/>
+    <col width="20.9" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -8938,7 +8939,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Producer price = net auction price paid to fishers (Form A buy) at the landing-linked markets M1/M6 only; Aratdar sell = auction hammer price at M1/M6; Bepari sell = Form B sell over all markets; Retailer sell = Form R vendor quote (descriptive; margins use the consumer-paid anchor); Consumer = focal-species purchases actually paid (Form C). Margins = differences of consecutive level means and telescope to the total spread. K/D-flagged prices excluded. Species without a complete chain show blank margins and are excluded from ALL (see Local_name note). Reporting_status marks species observed in fewer than three markets as descriptive-only (Methodology 3.8): S08/S09/S10 quotes are few and their share figures are indicative, not inferential.</t>
+          <t>Producer price = net auction price paid to fishers (Form A buy) at the landing-linked markets M1/M6 only; Aratdar sell = auction hammer price at M1/M6; Bepari sell = Form B sell over all markets; Retailer sell = Form R vendor quote (descriptive; margins use the consumer-paid anchor); Consumer = focal-species purchases actually paid (Form C). Margins = differences of consecutive level means and telescope to the total spread. K/D-flagged prices excluded. Species without a complete chain - or with fewer than MIN_CONS consumer-paid observations - show prices but blank margins/share and are excluded from ALL (see Local_name note); Consumer_paid_n reports the actual number of consumer slips behind each share. Reporting_status lists Method 3.8 descriptive-only reasons (S08/S09/S10 in the current set).</t>
         </is>
       </c>
     </row>
@@ -8970,55 +8971,60 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
+          <t>Consumer_paid_n</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
           <t>Reporting_status</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>Producer_BDT_kg</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Aratdar_sell_BDT_kg</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Bepari_sell_BDT_kg</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>Retailer_sell_BDT_kg</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Consumer_paid_BDT_kg</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Aratdar_margin_BDT_kg</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>Bepari_margin_BDT_kg</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>Retailer_margin_BDT_kg</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>Total_spread_BDT_kg</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>Producer_share_pct</t>
         </is>
@@ -9046,34 +9052,37 @@
       <c r="F5" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="G5" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" s="6" t="n">
         <v>1031.62</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>1083.3</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>1236.41</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="L5" s="6" t="n">
         <v>1486.96</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="6" t="n">
         <v>1420</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="N5" s="6" t="n">
         <v>51.68</v>
       </c>
-      <c r="N5" s="6" t="n">
+      <c r="O5" s="6" t="n">
         <v>153.11</v>
       </c>
-      <c r="O5" s="6" t="n">
+      <c r="P5" s="6" t="n">
         <v>183.59</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="6" t="n">
         <v>388.38</v>
       </c>
-      <c r="Q5" s="6" t="n">
+      <c r="R5" s="6" t="n">
         <v>72.59999999999999</v>
       </c>
     </row>
@@ -9099,35 +9108,38 @@
       <c r="F6" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="8" t="n">
+      <c r="G6" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="7" t="inlineStr"/>
+      <c r="I6" s="8" t="n">
         <v>1110.67</v>
       </c>
-      <c r="I6" s="8" t="n">
+      <c r="J6" s="8" t="n">
         <v>1165.59</v>
       </c>
-      <c r="J6" s="8" t="n">
+      <c r="K6" s="8" t="n">
         <v>1378.04</v>
       </c>
-      <c r="K6" s="8" t="n">
+      <c r="L6" s="8" t="n">
         <v>1619.16</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="M6" s="8" t="n">
         <v>1615</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="N6" s="8" t="n">
         <v>54.92</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="O6" s="8" t="n">
         <v>212.45</v>
       </c>
-      <c r="O6" s="8" t="n">
+      <c r="P6" s="8" t="n">
         <v>236.96</v>
       </c>
-      <c r="P6" s="8" t="n">
+      <c r="Q6" s="8" t="n">
         <v>504.33</v>
       </c>
-      <c r="Q6" s="8" t="n">
+      <c r="R6" s="8" t="n">
         <v>68.8</v>
       </c>
     </row>
@@ -9153,34 +9165,37 @@
       <c r="F7" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="6" t="n">
+      <c r="G7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" s="6" t="n">
         <v>735.53</v>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="J7" s="6" t="n">
         <v>771.7</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="6" t="n">
         <v>886.61</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="L7" s="6" t="n">
         <v>1069.64</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="6" t="n">
         <v>1033.33</v>
       </c>
-      <c r="M7" s="6" t="n">
+      <c r="N7" s="6" t="n">
         <v>36.17</v>
       </c>
-      <c r="N7" s="6" t="n">
+      <c r="O7" s="6" t="n">
         <v>114.91</v>
       </c>
-      <c r="O7" s="6" t="n">
+      <c r="P7" s="6" t="n">
         <v>146.72</v>
       </c>
-      <c r="P7" s="6" t="n">
+      <c r="Q7" s="6" t="n">
         <v>297.8</v>
       </c>
-      <c r="Q7" s="6" t="n">
+      <c r="R7" s="6" t="n">
         <v>71.2</v>
       </c>
     </row>
@@ -9206,35 +9221,38 @@
       <c r="F8" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="8" t="n">
+      <c r="G8" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="7" t="inlineStr"/>
+      <c r="I8" s="8" t="n">
         <v>660.95</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="J8" s="8" t="n">
         <v>687.75</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="K8" s="8" t="n">
         <v>762.77</v>
       </c>
-      <c r="K8" s="8" t="n">
+      <c r="L8" s="8" t="n">
         <v>933.4400000000001</v>
       </c>
-      <c r="L8" s="8" t="n">
+      <c r="M8" s="8" t="n">
         <v>885</v>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="N8" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="N8" s="8" t="n">
+      <c r="O8" s="8" t="n">
         <v>75.02</v>
       </c>
-      <c r="O8" s="8" t="n">
+      <c r="P8" s="8" t="n">
         <v>122.23</v>
       </c>
-      <c r="P8" s="8" t="n">
+      <c r="Q8" s="8" t="n">
         <v>224.05</v>
       </c>
-      <c r="Q8" s="8" t="n">
+      <c r="R8" s="8" t="n">
         <v>74.7</v>
       </c>
     </row>
@@ -9260,34 +9278,37 @@
       <c r="F9" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="H9" s="6" t="n">
+      <c r="G9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" s="6" t="n">
         <v>407.79</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="J9" s="6" t="n">
         <v>428.72</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>501.77</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="L9" s="6" t="n">
         <v>581.23</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="M9" s="6" t="n">
         <v>585</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="N9" s="6" t="n">
         <v>20.93</v>
       </c>
-      <c r="N9" s="6" t="n">
+      <c r="O9" s="6" t="n">
         <v>73.05</v>
       </c>
-      <c r="O9" s="6" t="n">
+      <c r="P9" s="6" t="n">
         <v>83.23</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="6" t="n">
         <v>177.21</v>
       </c>
-      <c r="Q9" s="6" t="n">
+      <c r="R9" s="6" t="n">
         <v>69.7</v>
       </c>
     </row>
@@ -9313,35 +9334,38 @@
       <c r="F10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="8" t="n">
+      <c r="G10" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="8" t="n">
         <v>314.1</v>
       </c>
-      <c r="I10" s="8" t="n">
+      <c r="J10" s="8" t="n">
         <v>323.55</v>
       </c>
-      <c r="J10" s="8" t="n">
+      <c r="K10" s="8" t="n">
         <v>380.42</v>
       </c>
-      <c r="K10" s="8" t="n">
+      <c r="L10" s="8" t="n">
         <v>457.13</v>
       </c>
-      <c r="L10" s="8" t="n">
+      <c r="M10" s="8" t="n">
         <v>446.54</v>
       </c>
-      <c r="M10" s="8" t="n">
+      <c r="N10" s="8" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="N10" s="8" t="n">
+      <c r="O10" s="8" t="n">
         <v>56.87</v>
       </c>
-      <c r="O10" s="8" t="n">
+      <c r="P10" s="8" t="n">
         <v>66.12</v>
       </c>
-      <c r="P10" s="8" t="n">
+      <c r="Q10" s="8" t="n">
         <v>132.44</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="R10" s="8" t="n">
         <v>70.3</v>
       </c>
     </row>
@@ -9367,34 +9391,37 @@
       <c r="F11" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="H11" s="6" t="n">
+      <c r="G11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" s="6" t="n">
         <v>361.74</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>377.81</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>450.16</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="L11" s="6" t="n">
         <v>545.45</v>
       </c>
-      <c r="L11" s="6" t="n">
+      <c r="M11" s="6" t="n">
         <v>530</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="N11" s="6" t="n">
         <v>16.07</v>
       </c>
-      <c r="N11" s="6" t="n">
+      <c r="O11" s="6" t="n">
         <v>72.34999999999999</v>
       </c>
-      <c r="O11" s="6" t="n">
+      <c r="P11" s="6" t="n">
         <v>79.84</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="6" t="n">
         <v>168.26</v>
       </c>
-      <c r="Q11" s="6" t="n">
+      <c r="R11" s="6" t="n">
         <v>68.3</v>
       </c>
     </row>
@@ -9420,41 +9447,34 @@
       <c r="F12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="7" t="inlineStr">
-        <is>
-          <t>Descriptive-only (Method 3.8)</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="n">
+      <c r="G12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Descriptive-only (Method 3.8): retail quotes in 2 market(s); consumer quotes n=1 (&lt;3; share not reported)</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="n">
         <v>231.78</v>
       </c>
-      <c r="I12" s="8" t="n">
+      <c r="J12" s="8" t="n">
         <v>241.16</v>
       </c>
-      <c r="J12" s="8" t="n">
+      <c r="K12" s="8" t="n">
         <v>279.01</v>
       </c>
-      <c r="K12" s="8" t="n">
+      <c r="L12" s="8" t="n">
         <v>325</v>
       </c>
-      <c r="L12" s="8" t="n">
+      <c r="M12" s="8" t="n">
         <v>330</v>
       </c>
-      <c r="M12" s="8" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="N12" s="8" t="n">
-        <v>37.85</v>
-      </c>
-      <c r="O12" s="8" t="n">
-        <v>50.99</v>
-      </c>
-      <c r="P12" s="8" t="n">
-        <v>98.22</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>70.2</v>
-      </c>
+      <c r="N12" s="7" t="n"/>
+      <c r="O12" s="7" t="n"/>
+      <c r="P12" s="7" t="n"/>
+      <c r="Q12" s="7" t="n"/>
+      <c r="R12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -9478,39 +9498,42 @@
       <c r="F13" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Descriptive-only (Method 3.8)</t>
-        </is>
-      </c>
-      <c r="H13" s="6" t="n">
+      <c r="G13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>Descriptive-only (Method 3.8): retail quotes in 2 market(s)</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n">
         <v>188.91</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="J13" s="6" t="n">
         <v>195.61</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="6" t="n">
         <v>234.46</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="L13" s="6" t="n">
         <v>263.01</v>
       </c>
-      <c r="L13" s="6" t="n">
+      <c r="M13" s="6" t="n">
         <v>267.5</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="N13" s="6" t="n">
         <v>6.7</v>
       </c>
-      <c r="N13" s="6" t="n">
+      <c r="O13" s="6" t="n">
         <v>38.85</v>
       </c>
-      <c r="O13" s="6" t="n">
+      <c r="P13" s="6" t="n">
         <v>33.04</v>
       </c>
-      <c r="P13" s="6" t="n">
+      <c r="Q13" s="6" t="n">
         <v>78.59</v>
       </c>
-      <c r="Q13" s="6" t="n">
+      <c r="R13" s="6" t="n">
         <v>70.59999999999999</v>
       </c>
     </row>
@@ -9536,31 +9559,32 @@
       <c r="F14" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>Descriptive-only (Method 3.8)</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="G14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Descriptive-only (Method 3.8): retail quotes in 1 market(s); consumer quotes n=1 (&lt;3; share not reported)</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="n">
         <v>163.45</v>
       </c>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="8" t="n">
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="8" t="n">
         <v>179.53</v>
       </c>
-      <c r="K14" s="8" t="n">
+      <c r="L14" s="8" t="n">
         <v>230</v>
       </c>
-      <c r="L14" s="8" t="n">
+      <c r="M14" s="8" t="n">
         <v>215</v>
       </c>
-      <c r="M14" s="7" t="n"/>
       <c r="N14" s="7" t="n"/>
       <c r="O14" s="7" t="n"/>
       <c r="P14" s="7" t="n"/>
-      <c r="Q14" s="8" t="n">
-        <v>76</v>
-      </c>
+      <c r="Q14" s="7" t="n"/>
+      <c r="R14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -9570,7 +9594,7 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Mean of species means (chain-complete: S01, S02, S03, S04, S05, S06, S07, S08, S09)</t>
+          <t>Mean of species means (chain-complete: S01, S02, S03, S04, S05, S06, S07, S09)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9579,41 +9603,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>423</v>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>Pooled over chain-complete species</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>560.34</v>
+        <v>414</v>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>Pooled over 8 chain-complete species (consumer n &gt;= 3)</t>
+        </is>
       </c>
       <c r="I15" s="6" t="n">
-        <v>586.13</v>
+        <v>601.41</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>678.85</v>
+        <v>629.25</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>809</v>
+        <v>728.83</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>790.26</v>
+        <v>869.5</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>25.79</v>
+        <v>847.8</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>92.72</v>
+        <v>27.84</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>111.41</v>
+        <v>99.58</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>229.92</v>
+        <v>118.97</v>
       </c>
       <c r="Q15" s="6" t="n">
+        <v>246.39</v>
+      </c>
+      <c r="R15" s="6" t="n">
         <v>70.90000000000001</v>
       </c>
     </row>

--- a/analysis_outputs/Analysis_Summary.xlsx
+++ b/analysis_outputs/Analysis_Summary.xlsx
@@ -10377,14 +10377,14 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply syndicate control</t>
+          <t>Unsold fish spoilage loss</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>36.7</v>
+        <v>40</v>
       </c>
       <c r="E5" t="n">
         <v>9</v>
@@ -10393,10 +10393,10 @@
         <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>26.7</v>
+        <v>23.3</v>
       </c>
       <c r="I5" t="n">
         <v>28</v>
@@ -10408,14 +10408,14 @@
     <row r="6">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Unsold fish spoilage loss</t>
+          <t>Supply syndicate control</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>40</v>
+        <v>36.7</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>9</v>
@@ -10424,10 +10424,10 @@
         <v>30</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>23.3</v>
+        <v>26.7</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>28</v>
@@ -10532,26 +10532,26 @@
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Waterlogging during monsoon</t>
+          <t>Low landings in lean season</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>23.3</v>
+        <v>30</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>20</v>
+        <v>26.7</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>30</v>
+        <v>16.7</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>22</v>
@@ -10563,26 +10563,26 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Low landings in lean season</t>
+          <t>Waterlogging during monsoon</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="G11" t="n">
         <v>9</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="H11" s="6" t="n">
         <v>30</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>16.7</v>
       </c>
       <c r="I11" t="n">
         <v>22</v>

--- a/analysis_outputs/Analysis_Summary.xlsx
+++ b/analysis_outputs/Analysis_Summary.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E25"/>
+  <dimension ref="B2:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="2" max="2"/>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
         <v>5</v>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>4</v>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>11</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
@@ -920,6 +920,7 @@
         <v>5</v>
       </c>
     </row>
+    <row r="26"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -931,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E20"/>
+  <dimension ref="B2:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -950,7 +951,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Consumers n=30; focal purchases n=69 (Yes today n=52).</t>
+          <t>Consumers n=30; focal purchases n=75 (Yes today n=64).</t>
         </is>
       </c>
     </row>
@@ -988,10 +989,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>53.3</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -1006,10 +1007,10 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>46.7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -1020,14 +1021,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bKash</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>36.7</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="8">
@@ -1038,14 +1039,14 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>36.7</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="9">
@@ -1056,7 +1057,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nagad_app</t>
+          <t>bKash</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1067,21 +1068,21 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Payment method</t>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Main reason for choosing seller</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Proximity</t>
         </is>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>6.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -1096,10 +1097,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>33.3</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="12">
@@ -1110,7 +1111,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Familiar_shop</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
@@ -1128,14 +1129,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Proximity</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>23.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="14">
@@ -1146,47 +1147,46 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Familiar_shop</t>
+          <t>Variety</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>Main reason for choosing seller</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Variety</t>
-        </is>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mean visit interval (days)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>4.73</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>3.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Mean visit interval (days)</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>3.57</v>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Focal purchase source (per purchase)</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Retailer</t>
+        </is>
       </c>
       <c r="D16" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="E16" s="7" t="n"/>
+        <v>54</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="17">
       <c r="B17" s="9" t="inlineStr">
@@ -1196,60 +1196,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Retailer</t>
+          <t>Hawker</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>71</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Focal purchase source (per purchase)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Hawker</t>
-        </is>
+          <t>Mean focal-species price paid (BDT/kg)</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>654.77</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>4.3</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="E18" s="7" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>Mean focal-species price paid (BDT/kg)</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Mean purchase size (kg)</t>
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>699.04</v>
+        <v>1.23</v>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Mean purchase size (kg)</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="E20" s="7" t="n"/>
+        <v>64</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1265,7 +1247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E12"/>
+  <dimension ref="B2:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19.85" customWidth="1" min="2" max="2"/>
@@ -1313,129 +1295,97 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Khoira</t>
+          <t>Faisya</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>268</v>
+        <v>330</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Bagda chingri</t>
+          <t>Moid</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1033.33</v>
+        <v>203.75</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.83</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Datina</t>
+          <t>Khoira</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>356.67</v>
+        <v>303.33</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Moid</t>
+          <t>Datina</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>216.67</v>
+        <v>370</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>1</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kakra (crab)</t>
+          <t>Chatka chingri</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>570</v>
+        <v>385</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Chatka chingri</t>
+          <t>Kakra (crab)</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>440</v>
+        <v>510</v>
       </c>
       <c r="E10" s="8" t="n">
         <v>0.75</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Lobster (local)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>2615</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Faisya</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>310</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -1471,7 +1421,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Unweighted means of species-level means over chain-complete species only (n_species=8; see Table 3 note). Producer &amp; auction prices from landing-linked markets M1/M6 (first-sale proxy, Methodology 3.11c); wholesale price = Bepari sell over all markets; retail price = consumer-paid anchor (Form C slips). Margins are differences of consecutive level means, so they sum exactly to the total spread and PS% + spread% = 100. Margin % is expressed as a share of the pooled consumer price.</t>
+          <t>Unweighted means of species-level means over chain-complete species only (n_species=10; see Table 3 note). Producer &amp; auction prices from landing-linked markets M1/M6 (first-sale proxy, Methodology 3.11c); wholesale price = Bepari sell over all markets; retail price = consumer-paid anchor (Form C slips). Margins are differences of consecutive level means, so they sum exactly to the total spread and PS% + spread% = 100. Margin % is expressed as a share of the pooled consumer price.</t>
         </is>
       </c>
     </row>
@@ -1504,13 +1454,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>27.84</v>
+        <v>23.15</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -1520,13 +1470,13 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>99.58</v>
+        <v>93.78</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>11.7</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="7">
@@ -1536,13 +1486,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>118.97</v>
+        <v>117.95</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>14</v>
+        <v>15.6</v>
       </c>
     </row>
     <row r="8">
@@ -1552,13 +1502,13 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>246.39</v>
+        <v>234.88</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>29.1</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="9">
@@ -1568,10 +1518,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>70.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1658,22 +1608,22 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>1416</v>
+        <v>1520</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1480</v>
+        <v>1620</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1491</v>
+        <v>1644</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1497</v>
+        <v>1573</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1571</v>
+        <v>1745</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1445</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="6">
@@ -1683,22 +1633,22 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1586</v>
+        <v>1515</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1603</v>
+        <v>1675</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>1645</v>
+        <v>1720</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1597</v>
+        <v>1524</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1717</v>
+        <v>1641</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="7">
@@ -1707,17 +1657,23 @@
           <t>S03 Lakkha</t>
         </is>
       </c>
+      <c r="C7" s="6" t="n">
+        <v>1053</v>
+      </c>
       <c r="D7" s="6" t="n">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1047</v>
+        <v>1066</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1065</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1112</v>
+        <v>1140</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1045</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="8">
@@ -1726,21 +1682,23 @@
           <t>S04 Koral/Kurl</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n"/>
+      <c r="C8" s="8" t="n">
+        <v>880</v>
+      </c>
       <c r="D8" s="8" t="n">
-        <v>958</v>
+        <v>917</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>938</v>
+        <v>955</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>895</v>
+        <v>946</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>963</v>
+        <v>904</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>902</v>
+        <v>880</v>
       </c>
     </row>
     <row r="9">
@@ -1750,22 +1708,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>565</v>
+        <v>545</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>569</v>
+        <v>587</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>612</v>
+        <v>627</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>551</v>
+        <v>572</v>
       </c>
     </row>
     <row r="10">
@@ -1775,22 +1733,22 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>484</v>
+        <v>443</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11">
@@ -1800,19 +1758,22 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>528</v>
+        <v>502</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>555</v>
+        <v>532</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>595</v>
+        <v>571</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>563</v>
+        <v>562</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>565</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="12">
@@ -1822,14 +1783,22 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>310</v>
-      </c>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
+        <v>330</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>340</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>355</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>355</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>338</v>
+      </c>
       <c r="H12" s="8" t="n">
-        <v>340</v>
+        <v>327</v>
       </c>
     </row>
     <row r="13">
@@ -1839,10 +1808,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>247</v>
+        <v>258</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>268</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>268</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>279</v>
+        <v>265</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>280</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>256</v>
       </c>
     </row>
     <row r="14">
@@ -1851,14 +1832,24 @@
           <t>S10 Harina</t>
         </is>
       </c>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
+      <c r="C14" s="8" t="n">
+        <v>223</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>230</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>228</v>
+      </c>
       <c r="F14" s="8" t="n">
-        <v>230</v>
-      </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+        <v>232</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>225</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>223</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1874,7 +1865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L20"/>
+  <dimension ref="B2:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -1961,12 +1952,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>M1-A-03</t>
+          <t>M1-A-04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1975,11 +1966,11 @@
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1024.92</v>
+        <v>328.24</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M1-R-01</t>
+          <t>M1-R-03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1988,10 +1979,10 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1030</v>
+        <v>330</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>-5.08</v>
+        <v>-1.76</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -2015,7 +2006,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>M1-A-04</t>
+          <t>M1-A-05</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -2024,7 +2015,7 @@
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1145.5</v>
+        <v>1158.9</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
@@ -2037,10 +2028,10 @@
         </is>
       </c>
       <c r="J6" s="8" t="n">
-        <v>1145</v>
+        <v>1160</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="L6" s="7" t="b">
         <v>1</v>
@@ -2059,12 +2050,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>M1-A-05</t>
+          <t>M1-A-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2073,11 +2064,11 @@
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1004.82</v>
+        <v>408.63</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M1-R-02</t>
+          <t>M1-R-01</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2086,10 +2077,10 @@
         </is>
       </c>
       <c r="J7" s="6" t="n">
-        <v>1005</v>
+        <v>410</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>-0.18</v>
+        <v>-1.37</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -2108,12 +2099,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>M2-A-05</t>
+          <t>M2-A-03</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -2122,11 +2113,11 @@
         </is>
       </c>
       <c r="G8" s="8" t="n">
-        <v>435.42</v>
+        <v>203.64</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>M2-R-02</t>
+          <t>M2-R-03</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -2135,10 +2126,10 @@
         </is>
       </c>
       <c r="J8" s="8" t="n">
-        <v>435</v>
+        <v>205</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>0.42</v>
+        <v>-1.36</v>
       </c>
       <c r="L8" s="7" t="b">
         <v>1</v>
@@ -2157,12 +2148,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>M2-A-02</t>
+          <t>M2-A-04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2171,11 +2162,11 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>1292.87</v>
+        <v>783.76</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M2-R-05</t>
+          <t>M2-R-02</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2184,10 +2175,10 @@
         </is>
       </c>
       <c r="J9" s="6" t="n">
-        <v>1290</v>
+        <v>785</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>2.87</v>
+        <v>-1.24</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -2206,12 +2197,12 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>M3-A-03</t>
+          <t>M3-A-04</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -2220,11 +2211,11 @@
         </is>
       </c>
       <c r="G10" s="8" t="n">
-        <v>1091.91</v>
+        <v>462.22</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>M3-R-01</t>
+          <t>M3-R-03</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -2233,10 +2224,10 @@
         </is>
       </c>
       <c r="J10" s="8" t="n">
-        <v>1095</v>
+        <v>460</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>-3.09</v>
+        <v>2.22</v>
       </c>
       <c r="L10" s="7" t="b">
         <v>1</v>
@@ -2255,32 +2246,61 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>S06</t>
-        </is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>M3-A-05</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1232.58</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>M3-R-05</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>1230</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>2.58</v>
       </c>
       <c r="L11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>PAIR-M3-03</t>
+          <t>PAIR-M4-01</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>M3-A-01</t>
+          <t>M4-A-05</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -2289,11 +2309,11 @@
         </is>
       </c>
       <c r="G12" s="8" t="n">
-        <v>468.92</v>
+        <v>1165.59</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>M3-R-02</t>
+          <t>M4-R-05</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -2302,10 +2322,10 @@
         </is>
       </c>
       <c r="J12" s="8" t="n">
-        <v>465</v>
+        <v>1165</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>3.92</v>
+        <v>0.59</v>
       </c>
       <c r="L12" s="7" t="b">
         <v>1</v>
@@ -2314,7 +2334,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>PAIR-M4-01</t>
+          <t>PAIR-M4-02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2324,12 +2344,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>M4-A-04</t>
+          <t>M4-A-03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2338,11 +2358,11 @@
         </is>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1205.79</v>
+        <v>257.23</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>M4-R-03</t>
+          <t>M4-R-01</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2351,10 +2371,10 @@
         </is>
       </c>
       <c r="J13" s="6" t="n">
-        <v>1205</v>
+        <v>255</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>0.79</v>
+        <v>2.23</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -2363,7 +2383,7 @@
     <row r="14">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>PAIR-M4-02</t>
+          <t>PAIR-M4-03</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2373,12 +2393,12 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>M4-A-03</t>
+          <t>M4-A-02</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -2387,11 +2407,11 @@
         </is>
       </c>
       <c r="G14" s="8" t="n">
-        <v>401.93</v>
+        <v>198.29</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>M4-R-05</t>
+          <t>M4-R-04</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -2400,10 +2420,10 @@
         </is>
       </c>
       <c r="J14" s="8" t="n">
-        <v>401.93</v>
+        <v>200</v>
       </c>
       <c r="K14" s="16" t="n">
-        <v>0</v>
+        <v>-1.71</v>
       </c>
       <c r="L14" s="7" t="b">
         <v>1</v>
@@ -2422,12 +2442,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S08</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>M5-A-04</t>
+          <t>M5-A-05</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2436,11 +2456,11 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>468.92</v>
+        <v>254.56</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M5-R-03</t>
+          <t>M5-R-01</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2449,10 +2469,10 @@
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>465</v>
+        <v>255</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>3.92</v>
+        <v>-0.44</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -2471,12 +2491,12 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>M5-A-02</t>
+          <t>M5-A-04</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -2485,11 +2505,11 @@
         </is>
       </c>
       <c r="G16" s="8" t="n">
-        <v>1138.8</v>
+        <v>1259.38</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>M5-R-01</t>
+          <t>M5-R-04</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -2498,10 +2518,10 @@
         </is>
       </c>
       <c r="J16" s="8" t="n">
-        <v>1135</v>
+        <v>1260</v>
       </c>
       <c r="K16" s="16" t="n">
-        <v>3.8</v>
+        <v>-0.62</v>
       </c>
       <c r="L16" s="7" t="b">
         <v>1</v>
@@ -2520,11 +2540,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>S07</t>
-        </is>
+          <t>S09</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>M5-A-03</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>209</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>M5-R-03</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>210</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>-1</v>
       </c>
       <c r="L17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2540,12 +2589,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S09</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>M6-A-04</t>
+          <t>M6-A-05</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -2554,11 +2603,11 @@
         </is>
       </c>
       <c r="G18" s="8" t="n">
-        <v>1185.69</v>
+        <v>192.93</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>M6-R-05</t>
+          <t>M6-R-04</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -2567,10 +2616,10 @@
         </is>
       </c>
       <c r="J18" s="8" t="n">
-        <v>1185</v>
+        <v>195</v>
       </c>
       <c r="K18" s="16" t="n">
-        <v>0.6899999999999999</v>
+        <v>-2.07</v>
       </c>
       <c r="L18" s="7" t="b">
         <v>1</v>
@@ -2589,12 +2638,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>M6-A-01</t>
+          <t>M6-A-03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2603,11 +2652,11 @@
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>415.33</v>
+        <v>168.81</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>M6-R-04</t>
+          <t>M6-R-05</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2616,61 +2665,12 @@
         </is>
       </c>
       <c r="J19" s="6" t="n">
-        <v>415</v>
+        <v>170</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.33</v>
+        <v>-1.19</v>
       </c>
       <c r="L19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>PAIR-M6-03</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>M6-A-02</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Aratdar</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>422.03</v>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>M6-R-03</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Khuchra</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>420</v>
-      </c>
-      <c r="K20" s="16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="L20" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -2741,7 +2741,7 @@
         </is>
       </c>
       <c r="C7" s="15" t="n">
-        <v>0.59</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="8">
@@ -2751,7 +2751,7 @@
         </is>
       </c>
       <c r="C8" s="16" t="n">
-        <v>0.78</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="9">
@@ -2761,7 +2761,7 @@
         </is>
       </c>
       <c r="C9" s="15" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="C10" s="16" t="n">
-        <v>0.1157</v>
+        <v>0.3894</v>
       </c>
     </row>
     <row r="11">
@@ -2878,28 +2878,22 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1138.8</v>
+        <v>1299.57</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1416.25</v>
+        <v>1520</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>1352.5</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>277.45</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>213.7</v>
+        <v>220.43</v>
       </c>
     </row>
     <row r="6">
@@ -2914,25 +2908,29 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1266.08</v>
+        <v>1373.26</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1480</v>
+        <v>1620</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>1630</v>
+      </c>
       <c r="I6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>213.92</v>
-      </c>
-      <c r="K6" s="7" t="n"/>
+        <v>246.74</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>256.74</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -2946,28 +2944,22 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1333.07</v>
+        <v>1391.12</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1491</v>
+        <v>1643.63</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>1456.67</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>157.93</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>123.6</v>
+        <v>252.51</v>
       </c>
     </row>
     <row r="8">
@@ -2982,25 +2974,29 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>1225.88</v>
+        <v>1297.89</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>1496.76</v>
+        <v>1573.04</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>1575</v>
+      </c>
       <c r="I8" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>270.88</v>
-      </c>
-      <c r="K8" s="7" t="n"/>
+        <v>275.15</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>277.11</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -3014,22 +3010,28 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1282.82</v>
+        <v>1416.8</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1570.75</v>
+        <v>1745.49</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
+      <c r="H9" s="6" t="n">
+        <v>1700</v>
+      </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>287.93</v>
+        <v>328.69</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>283.2</v>
       </c>
     </row>
     <row r="10">
@@ -3044,28 +3046,28 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1244.31</v>
+        <v>1261.61</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>1445</v>
+        <v>1490.15</v>
       </c>
       <c r="G10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>1495</v>
+      </c>
+      <c r="I10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>1445</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="J10" s="8" t="n">
-        <v>200.69</v>
+        <v>228.54</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>200.69</v>
+        <v>233.39</v>
       </c>
     </row>
     <row r="11">
@@ -3080,28 +3082,22 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1309.62</v>
+        <v>1272.78</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1586</v>
+        <v>1515</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>1475</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>276.38</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>165.38</v>
+        <v>242.22</v>
       </c>
     </row>
     <row r="12">
@@ -3116,25 +3112,29 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>1415.13</v>
+        <v>1400.05</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>1603.33</v>
+        <v>1675</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>1660</v>
+      </c>
       <c r="I12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>188.2</v>
-      </c>
-      <c r="K12" s="7" t="n"/>
+        <v>274.95</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>259.95</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -3148,22 +3148,28 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1426.85</v>
+        <v>1424.61</v>
       </c>
       <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>1720</v>
+      </c>
+      <c r="G13" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="6" t="n">
-        <v>1645</v>
-      </c>
-      <c r="G13" t="n">
-        <v>4</v>
+      <c r="H13" s="6" t="n">
+        <v>1690</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>218.15</v>
+        <v>295.39</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>265.39</v>
       </c>
     </row>
     <row r="14">
@@ -3178,23 +3184,23 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1343.11</v>
+        <v>1342</v>
       </c>
       <c r="E14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>1523.75</v>
+      </c>
+      <c r="G14" s="7" t="n">
         <v>4</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>1596.67</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="H14" s="7" t="n"/>
       <c r="I14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>253.56</v>
+        <v>181.75</v>
       </c>
       <c r="K14" s="7" t="n"/>
     </row>
@@ -3210,28 +3216,28 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1429.53</v>
+        <v>1410.11</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1717.17</v>
+        <v>1641.44</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1685</v>
+        <v>1620</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>287.64</v>
+        <v>231.33</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>255.47</v>
+        <v>209.89</v>
       </c>
     </row>
     <row r="16">
@@ -3246,23 +3252,23 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1321.34</v>
+        <v>1319.67</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" s="7" t="n"/>
       <c r="I16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>268.66</v>
+        <v>260.33</v>
       </c>
       <c r="K16" s="7" t="n"/>
     </row>
@@ -3278,16 +3284,28 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>817.26</v>
+        <v>870.85</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
+      <c r="F17" s="6" t="n">
+        <v>1053.33</v>
+      </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1035</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>182.48</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>164.15</v>
       </c>
     </row>
     <row r="18">
@@ -3302,28 +3320,28 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>886.48</v>
+        <v>890.9400000000001</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>1055</v>
+        <v>1060</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>193.52</v>
+        <v>183.06</v>
       </c>
       <c r="K18" s="8" t="n">
-        <v>168.52</v>
+        <v>169.06</v>
       </c>
     </row>
     <row r="19">
@@ -3338,22 +3356,22 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>895.41</v>
+        <v>882.01</v>
       </c>
       <c r="E19" t="n">
         <v>3</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1046.67</v>
+        <v>1066.25</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>151.26</v>
+        <v>184.24</v>
       </c>
     </row>
     <row r="20">
@@ -3368,21 +3386,29 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>877.54</v>
+        <v>924.4400000000001</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>1065.11</v>
+      </c>
       <c r="G20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>1065</v>
+      </c>
       <c r="I20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>140.67</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>140.56</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -3396,28 +3422,22 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>919.41</v>
+        <v>937.84</v>
       </c>
       <c r="E21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1112.5</v>
+        <v>1140</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1075</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>193.09</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>155.59</v>
+        <v>202.16</v>
       </c>
     </row>
     <row r="22">
@@ -3432,29 +3452,25 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>866.38</v>
+        <v>877.55</v>
       </c>
       <c r="E22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>1032.8</v>
+      </c>
+      <c r="G22" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>1045</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>970</v>
-      </c>
+      <c r="H22" s="7" t="n"/>
       <c r="I22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>178.62</v>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>103.62</v>
-      </c>
+        <v>155.25</v>
+      </c>
+      <c r="K22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
@@ -3468,16 +3484,28 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>710.08</v>
+        <v>723.47</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
       </c>
+      <c r="F23" s="6" t="n">
+        <v>880</v>
+      </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>860</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>156.53</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>136.53</v>
       </c>
     </row>
     <row r="24">
@@ -3492,25 +3520,29 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>803.86</v>
+        <v>763.66</v>
       </c>
       <c r="E24" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>916.67</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="8" t="n">
-        <v>957.5</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" s="7" t="n"/>
+      <c r="H24" s="8" t="n">
+        <v>895</v>
+      </c>
       <c r="I24" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="8" t="n">
-        <v>153.64</v>
-      </c>
-      <c r="K24" s="7" t="n"/>
+        <v>153.01</v>
+      </c>
+      <c r="K24" s="8" t="n">
+        <v>131.34</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
@@ -3524,28 +3556,22 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>788.23</v>
+        <v>830.65</v>
       </c>
       <c r="E25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>938.33</v>
+        <v>955</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>925</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>150.1</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>136.77</v>
+        <v>124.35</v>
       </c>
     </row>
     <row r="26">
@@ -3560,28 +3586,28 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>743.5700000000001</v>
+        <v>797.16</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>895</v>
+        <v>945.62</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>2</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>860</v>
+        <v>930</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>151.43</v>
+        <v>148.46</v>
       </c>
       <c r="K26" s="8" t="n">
-        <v>116.43</v>
+        <v>132.84</v>
       </c>
     </row>
     <row r="27">
@@ -3596,22 +3622,22 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>790.46</v>
+        <v>770.37</v>
       </c>
       <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>904.34</v>
+      </c>
+      <c r="G27" t="n">
         <v>1</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>963.33</v>
-      </c>
-      <c r="G27" t="n">
-        <v>3</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>172.87</v>
+        <v>133.97</v>
       </c>
     </row>
     <row r="28">
@@ -3626,29 +3652,25 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>741.89</v>
+        <v>728.5</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>902.5</v>
+        <v>879.62</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>877.5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H28" s="7" t="n"/>
       <c r="I28" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>160.61</v>
-      </c>
-      <c r="K28" s="8" t="n">
-        <v>135.61</v>
-      </c>
+        <v>151.12</v>
+      </c>
+      <c r="K28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
@@ -3662,28 +3684,28 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>485</v>
+        <v>467.25</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>565</v>
+        <v>545</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>545</v>
+        <v>546.67</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>80</v>
+        <v>77.75</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>60</v>
+        <v>79.42</v>
       </c>
     </row>
     <row r="30">
@@ -3698,28 +3720,28 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>495.71</v>
+        <v>494.04</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>585</v>
+        <v>578.75</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>615</v>
+        <v>575</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="16" t="n">
-        <v>89.29000000000001</v>
-      </c>
-      <c r="K30" s="8" t="n">
-        <v>119.29</v>
+        <v>84.70999999999999</v>
+      </c>
+      <c r="K30" s="16" t="n">
+        <v>80.95999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -3734,28 +3756,28 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>527.53</v>
+        <v>509.11</v>
       </c>
       <c r="E31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>613.75</v>
+        <v>628.33</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>590</v>
+        <v>611.67</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="15" t="n">
-        <v>86.22</v>
-      </c>
-      <c r="K31" s="15" t="n">
-        <v>62.47</v>
+        <v>3</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>119.22</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>102.56</v>
       </c>
     </row>
     <row r="32">
@@ -3770,28 +3792,28 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>524.74</v>
+        <v>506.88</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>569.05</v>
+        <v>587.03</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>585</v>
+        <v>595</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="16" t="n">
-        <v>44.31</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="K32" s="16" t="n">
-        <v>60.26</v>
+        <v>88.12</v>
       </c>
     </row>
     <row r="33">
@@ -3806,13 +3828,13 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>518.04</v>
+        <v>539.25</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>611.53</v>
+        <v>627.1</v>
       </c>
       <c r="G33" t="n">
         <v>3</v>
@@ -3821,13 +3843,13 @@
         <v>610</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>93.48999999999999</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="K33" s="15" t="n">
-        <v>91.95999999999999</v>
+        <v>70.75</v>
       </c>
     </row>
     <row r="34">
@@ -3842,28 +3864,28 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>462.22</v>
+        <v>478.97</v>
       </c>
       <c r="E34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>571.67</v>
+      </c>
+      <c r="G34" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F34" s="8" t="n">
-        <v>551</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>5</v>
-      </c>
       <c r="H34" s="8" t="n">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" s="16" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="K34" s="8" t="n">
-        <v>117.78</v>
+        <v>92.7</v>
+      </c>
+      <c r="K34" s="16" t="n">
+        <v>81.03</v>
       </c>
     </row>
     <row r="35">
@@ -3878,28 +3900,28 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>360.06</v>
+        <v>370.67</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>416.25</v>
+        <v>431.25</v>
       </c>
       <c r="G35" t="n">
         <v>4</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>56.19</v>
+        <v>60.58</v>
       </c>
       <c r="K35" s="15" t="n">
-        <v>59.94</v>
+        <v>44.33</v>
       </c>
     </row>
     <row r="36">
@@ -3914,28 +3936,28 @@
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>378.49</v>
+        <v>398.58</v>
       </c>
       <c r="E36" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>472.5</v>
+        <v>465</v>
       </c>
       <c r="G36" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>452.5</v>
+      </c>
+      <c r="I36" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="H36" s="8" t="n">
-        <v>443.33</v>
-      </c>
-      <c r="I36" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="J36" s="16" t="n">
-        <v>94.01000000000001</v>
+        <v>66.42</v>
       </c>
       <c r="K36" s="16" t="n">
-        <v>64.84</v>
+        <v>53.92</v>
       </c>
     </row>
     <row r="37">
@@ -3950,28 +3972,28 @@
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>385.85</v>
+        <v>379.6</v>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>470</v>
+        <v>459.07</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>457.5</v>
+        <v>461.67</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>84.15000000000001</v>
+        <v>79.47</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>71.65000000000001</v>
+        <v>82.06999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -3986,28 +4008,28 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>390.77</v>
+        <v>381.83</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>463.06</v>
+        <v>437.5</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="I38" s="7" t="n">
         <v>2</v>
       </c>
       <c r="J38" s="16" t="n">
-        <v>72.29000000000001</v>
+        <v>55.67</v>
       </c>
       <c r="K38" s="16" t="n">
-        <v>54.23</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="39">
@@ -4022,28 +4044,28 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>393</v>
+        <v>388.53</v>
       </c>
       <c r="E39" t="n">
         <v>3</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>484.46</v>
+        <v>443.08</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>468.33</v>
+        <v>445</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39" s="15" t="n">
-        <v>91.45999999999999</v>
+        <v>54.55</v>
       </c>
       <c r="K39" s="15" t="n">
-        <v>75.33</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="40">
@@ -4061,25 +4083,25 @@
         <v>375.13</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J40" s="16" t="n">
-        <v>84.87</v>
+        <v>74.87</v>
       </c>
       <c r="K40" s="16" t="n">
-        <v>49.87</v>
+        <v>64.87</v>
       </c>
     </row>
     <row r="41">
@@ -4094,28 +4116,28 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>433.19</v>
+        <v>424.26</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>527.5</v>
+        <v>502.5</v>
       </c>
       <c r="G41" t="n">
         <v>2</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
       <c r="J41" s="15" t="n">
-        <v>94.31</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>76.81</v>
+        <v>75.73999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -4130,28 +4152,28 @@
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>462.22</v>
+        <v>451.05</v>
       </c>
       <c r="E42" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>532.5</v>
+      </c>
+      <c r="G42" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F42" s="8" t="n">
-        <v>555</v>
-      </c>
-      <c r="G42" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="H42" s="8" t="n">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="I42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="16" t="n">
-        <v>92.78</v>
+        <v>81.45</v>
       </c>
       <c r="K42" s="16" t="n">
-        <v>72.78</v>
+        <v>68.95</v>
       </c>
     </row>
     <row r="43">
@@ -4166,28 +4188,28 @@
         </is>
       </c>
       <c r="D43" s="6" t="n">
-        <v>448.82</v>
+        <v>475.62</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>595</v>
+        <v>571.4</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="6" t="n">
-        <v>146.18</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>101.18</v>
+      <c r="J43" s="15" t="n">
+        <v>95.78</v>
+      </c>
+      <c r="K43" s="15" t="n">
+        <v>94.38</v>
       </c>
     </row>
     <row r="44">
@@ -4202,29 +4224,25 @@
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>455.52</v>
+        <v>462.22</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>562.7</v>
+        <v>562.5</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>530</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H44" s="7" t="n"/>
       <c r="I44" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>107.18</v>
-      </c>
-      <c r="K44" s="16" t="n">
-        <v>74.48</v>
-      </c>
+        <v>100.28</v>
+      </c>
+      <c r="K44" s="7" t="n"/>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
@@ -4243,17 +4261,17 @@
       <c r="E45" t="n">
         <v>2</v>
       </c>
+      <c r="F45" s="6" t="n">
+        <v>565</v>
+      </c>
       <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" t="n">
         <v>0</v>
       </c>
-      <c r="H45" s="6" t="n">
-        <v>547.5</v>
-      </c>
-      <c r="I45" t="n">
-        <v>2</v>
-      </c>
-      <c r="K45" s="15" t="n">
-        <v>91.98</v>
+      <c r="J45" s="6" t="n">
+        <v>109.48</v>
       </c>
     </row>
     <row r="46">
@@ -4268,28 +4286,28 @@
         </is>
       </c>
       <c r="D46" s="8" t="n">
-        <v>462.22</v>
+        <v>428.73</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="I46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J46" s="16" t="n">
-        <v>42.78</v>
+        <v>81.27</v>
       </c>
       <c r="K46" s="16" t="n">
-        <v>27.78</v>
+        <v>71.27</v>
       </c>
     </row>
     <row r="47">
@@ -4304,22 +4322,28 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>251.88</v>
+        <v>274.65</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
+      <c r="H47" s="6" t="n">
+        <v>332.5</v>
+      </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>58.12</v>
+        <v>55.35</v>
+      </c>
+      <c r="K47" s="15" t="n">
+        <v>57.85</v>
       </c>
     </row>
     <row r="48">
@@ -4333,20 +4357,30 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="8" t="n">
+        <v>281.35</v>
+      </c>
       <c r="E48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>340</v>
+      </c>
       <c r="G48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>330</v>
+      </c>
       <c r="I48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="7" t="n"/>
-      <c r="K48" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="J48" s="16" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="K48" s="16" t="n">
+        <v>48.65</v>
+      </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
@@ -4360,17 +4394,23 @@
         </is>
       </c>
       <c r="D49" s="6" t="n">
-        <v>281.35</v>
+        <v>308.15</v>
       </c>
       <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>355</v>
+      </c>
+      <c r="G49" t="n">
         <v>1</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
+      <c r="J49" s="15" t="n">
+        <v>46.85</v>
+      </c>
     </row>
     <row r="50">
       <c r="B50" s="7" t="inlineStr">
@@ -4383,26 +4423,22 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="D50" s="8" t="n">
-        <v>291.4</v>
-      </c>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>355</v>
+      </c>
+      <c r="G50" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F50" s="7" t="n"/>
-      <c r="G50" s="7" t="n">
+      <c r="H50" s="7" t="n"/>
+      <c r="I50" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="8" t="n">
-        <v>330</v>
-      </c>
-      <c r="I50" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="J50" s="7" t="n"/>
-      <c r="K50" s="16" t="n">
-        <v>38.6</v>
-      </c>
+      <c r="K50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
@@ -4418,11 +4454,17 @@
       <c r="E51" t="n">
         <v>0</v>
       </c>
+      <c r="F51" s="6" t="n">
+        <v>337.5</v>
+      </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>335</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -4436,22 +4478,30 @@
           <t>M6</t>
         </is>
       </c>
-      <c r="D52" s="7" t="n"/>
+      <c r="D52" s="8" t="n">
+        <v>291.4</v>
+      </c>
       <c r="E52" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F52" s="8" t="n">
-        <v>340</v>
+        <v>326.62</v>
       </c>
       <c r="G52" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="8" t="n">
+        <v>330</v>
+      </c>
+      <c r="I52" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H52" s="7" t="n"/>
-      <c r="I52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="7" t="n"/>
-      <c r="K52" s="7" t="n"/>
+      <c r="J52" s="16" t="n">
+        <v>35.22</v>
+      </c>
+      <c r="K52" s="16" t="n">
+        <v>38.6</v>
+      </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
@@ -4464,17 +4514,29 @@
           <t>M1</t>
         </is>
       </c>
+      <c r="D53" s="6" t="n">
+        <v>218.83</v>
+      </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>246.67</v>
+        <v>257.5</v>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>252.5</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="J53" s="15" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="K53" s="15" t="n">
+        <v>33.67</v>
       </c>
     </row>
     <row r="54">
@@ -4489,14 +4551,16 @@
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>219.72</v>
+        <v>226.42</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>267.5</v>
+      </c>
       <c r="G54" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H54" s="8" t="n">
         <v>265</v>
@@ -4504,9 +4568,11 @@
       <c r="I54" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J54" s="7" t="n"/>
+      <c r="J54" s="16" t="n">
+        <v>41.08</v>
+      </c>
       <c r="K54" s="16" t="n">
-        <v>45.28</v>
+        <v>38.58</v>
       </c>
     </row>
     <row r="55">
@@ -4521,22 +4587,28 @@
         </is>
       </c>
       <c r="D55" s="6" t="n">
-        <v>241.16</v>
+        <v>225.08</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>267.5</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="J55" s="15" t="n">
+        <v>42.42</v>
       </c>
       <c r="K55" s="15" t="n">
-        <v>28.84</v>
+        <v>39.92</v>
       </c>
     </row>
     <row r="56">
@@ -4550,24 +4622,30 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="D56" s="7" t="n"/>
+      <c r="D56" s="8" t="n">
+        <v>222.4</v>
+      </c>
       <c r="E56" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" s="8" t="n">
-        <v>279.35</v>
+        <v>265</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="I56" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="7" t="n"/>
-      <c r="K56" s="7" t="n"/>
+      <c r="J56" s="16" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="K56" s="16" t="n">
+        <v>37.6</v>
+      </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
@@ -4580,23 +4658,17 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="D57" s="6" t="n">
-        <v>241.16</v>
-      </c>
       <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>280</v>
+      </c>
+      <c r="G57" t="n">
         <v>1</v>
       </c>
-      <c r="G57" t="n">
+      <c r="I57" t="n">
         <v>0</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>270</v>
-      </c>
-      <c r="I57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" s="15" t="n">
-        <v>28.84</v>
       </c>
     </row>
     <row r="58">
@@ -4611,24 +4683,28 @@
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>235.8</v>
+        <v>222.4</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="7" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="F58" s="8" t="n">
+        <v>256.25</v>
+      </c>
       <c r="G58" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="I58" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="J58" s="16" t="n">
+        <v>33.85</v>
+      </c>
       <c r="K58" s="16" t="n">
-        <v>24.2</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="59">
@@ -4646,13 +4722,25 @@
         <v>182.21</v>
       </c>
       <c r="E59" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>223.33</v>
+      </c>
+      <c r="G59" t="n">
+        <v>3</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="I59" t="n">
         <v>1</v>
       </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0</v>
+      <c r="J59" s="15" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="K59" s="15" t="n">
+        <v>32.79</v>
       </c>
     </row>
     <row r="60">
@@ -4666,22 +4754,30 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="D60" s="7" t="n"/>
+      <c r="D60" s="8" t="n">
+        <v>194.27</v>
+      </c>
       <c r="E60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>230</v>
+      </c>
       <c r="G60" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="I60" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J60" s="7" t="n"/>
-      <c r="K60" s="7" t="n"/>
+      <c r="J60" s="16" t="n">
+        <v>35.73</v>
+      </c>
+      <c r="K60" s="16" t="n">
+        <v>30.73</v>
+      </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
@@ -4694,15 +4790,24 @@
           <t>M3</t>
         </is>
       </c>
+      <c r="D61" s="6" t="n">
+        <v>200.96</v>
+      </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>227.76</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
+      <c r="J61" s="15" t="n">
+        <v>26.8</v>
+      </c>
     </row>
     <row r="62">
       <c r="B62" s="7" t="inlineStr">
@@ -4716,25 +4821,29 @@
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>184.89</v>
+        <v>195.61</v>
       </c>
       <c r="E62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F62" s="8" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="8" t="n">
         <v>230</v>
       </c>
-      <c r="G62" s="7" t="n">
+      <c r="I62" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H62" s="7" t="n"/>
-      <c r="I62" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="J62" s="16" t="n">
-        <v>45.11</v>
-      </c>
-      <c r="K62" s="7" t="n"/>
+        <v>36.89</v>
+      </c>
+      <c r="K62" s="16" t="n">
+        <v>34.39</v>
+      </c>
     </row>
     <row r="63">
       <c r="B63" t="inlineStr">
@@ -4747,14 +4856,29 @@
           <t>M5</t>
         </is>
       </c>
+      <c r="D63" s="6" t="n">
+        <v>192.26</v>
+      </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>224.86</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>222.5</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="J63" s="15" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="K63" s="15" t="n">
+        <v>30.24</v>
       </c>
     </row>
     <row r="64">
@@ -4769,20 +4893,24 @@
         </is>
       </c>
       <c r="D64" s="8" t="n">
-        <v>171.49</v>
+        <v>187.57</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" s="7" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>223.33</v>
+      </c>
       <c r="G64" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H64" s="7" t="n"/>
       <c r="I64" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J64" s="7" t="n"/>
+      <c r="J64" s="16" t="n">
+        <v>35.76</v>
+      </c>
       <c r="K64" s="7" t="n"/>
     </row>
   </sheetData>
@@ -4878,22 +5006,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>M1; M2; M3; M4; M5</t>
+          <t>M3; M4; M5; M6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M1=4; M2=4; M3=5; M4=4; M5=4</t>
+          <t>M3=4; M4=3; M5=4; M6=3</t>
         </is>
       </c>
       <c r="G5" s="15" t="n">
-        <v>10.721</v>
+        <v>12.227</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>0.0299</v>
+        <v>0.0066</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -4919,26 +5047,26 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>M1; M2; M3; M4; M5; M6</t>
+          <t>M1; M4; M5</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>M1=5; M2=3; M3=4; M4=3; M5=3; M6=4</t>
+          <t>M1=3; M4=4; M5=3</t>
         </is>
       </c>
       <c r="G6" s="16" t="n">
-        <v>11.163</v>
+        <v>5.972</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I6" s="16" t="n">
-        <v>0.0482</v>
+        <v>0.0505</v>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>reject H0 (p&lt;0.05): prices differ across markets</t>
+          <t>fail to reject H0 (p&gt;=0.05)</t>
         </is>
       </c>
     </row>
@@ -4960,22 +5088,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>M3; M5; M6</t>
+          <t>M1; M2; M3; M6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>M3=3; M5=4; M6=5</t>
+          <t>M1=3; M2=5; M3=4; M6=3</t>
         </is>
       </c>
       <c r="G7" s="15" t="n">
-        <v>6.121</v>
+        <v>9.493</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>0.0469</v>
+        <v>0.0234</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -4996,31 +5124,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>exploratory (n&gt;=3)</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>M2; M3; M5; M6</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>M2=4; M3=3; M5=3; M6=4</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>7.741</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" s="16" t="n">
-        <v>0.0517</v>
-      </c>
+          <t>not run</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>fail to reject H0 (p&gt;=0.05)</t>
+          <t>cells &lt; n threshold in &lt;3 markets -&gt; descriptive only</t>
         </is>
       </c>
     </row>
@@ -5047,17 +5161,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>M2=3; M3=4; M4=4; M5=3; M6=5</t>
+          <t>M2=4; M3=3; M4=3; M5=3; M6=3</t>
         </is>
       </c>
       <c r="G9" s="15" t="n">
-        <v>12.2</v>
+        <v>12.126</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>4</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.0159</v>
+        <v>0.0164</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5083,22 +5197,22 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>M1; M3; M4</t>
+          <t>M1; M2; M3; M5</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>M1=4; M3=4; M4=4</t>
+          <t>M1=4; M2=3; M3=3; M5=3</t>
         </is>
       </c>
       <c r="G10" s="16" t="n">
-        <v>6.885</v>
+        <v>10.678</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>0.032</v>
+        <v>0.0136</v>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
@@ -5219,7 +5333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H45"/>
+  <dimension ref="B2:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -5276,22 +5390,22 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>-3.252</v>
+        <v>3.29</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.0011</v>
+        <v>0.001</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.0115</v>
+        <v>0.006</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -5305,22 +5419,22 @@
     <row r="6">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>-1.937</v>
+        <v>-2.35</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0.0528</v>
+        <v>0.0188</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>0.4752</v>
+        <v>0.0939</v>
       </c>
       <c r="G6" s="7" t="b">
         <v>0</v>
@@ -5334,22 +5448,22 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D7" s="15" t="n">
-        <v>-1.769</v>
+        <v>2.037</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.0769</v>
+        <v>0.0417</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.6156</v>
+        <v>0.1667</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -5363,22 +5477,22 @@
     <row r="8">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>-1.655</v>
+        <v>-1.354</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>0.098</v>
+        <v>0.1758</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.6861</v>
+        <v>0.5275</v>
       </c>
       <c r="G8" s="7" t="b">
         <v>0</v>
@@ -5392,22 +5506,22 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
       <c r="D9" s="15" t="n">
-        <v>-1.598</v>
+        <v>1.097</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.1101</v>
+        <v>0.2728</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.6861</v>
+        <v>0.5456</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -5421,22 +5535,22 @@
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>-1.491</v>
+        <v>0.879</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>0.1358</v>
+        <v>0.3793</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.6861</v>
+        <v>0.5456</v>
       </c>
       <c r="G10" s="7" t="b">
         <v>0</v>
@@ -5450,116 +5564,116 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>-1.483</v>
+        <v>2.773</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>0.138</v>
+        <v>0.0056</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0.6861</v>
+        <v>0.0334</v>
       </c>
       <c r="G11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S03</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>-0.373</v>
+        <v>2.065</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.0389</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>1</v>
+        <v>0.1946</v>
       </c>
       <c r="G12" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.192</v>
+        <v>-1.997</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>0.8474</v>
+        <v>0.0459</v>
       </c>
       <c r="F13" s="15" t="n">
-        <v>1</v>
+        <v>0.1946</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>-0.171</v>
+        <v>-1.323</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0.8641</v>
+        <v>0.1858</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>1</v>
+        <v>0.5574</v>
       </c>
       <c r="G14" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S03</t>
         </is>
       </c>
     </row>
@@ -5571,118 +5685,118 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>-2.828</v>
+        <v>0.694</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.0047</v>
+        <v>0.4877</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.0702</v>
+        <v>0.9754</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S03</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>2.548</v>
+        <v>0.667</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.0108</v>
+        <v>0.5046</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.1518</v>
+        <v>0.9754</v>
       </c>
       <c r="G16" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>-2.171</v>
+        <v>2.711</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.0299</v>
+        <v>0.0067</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>0.3893</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>-2.171</v>
+        <v>2.625</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>0.0299</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>0.3893</v>
+        <v>0.078</v>
       </c>
       <c r="G18" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5691,155 +5805,155 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>-1.786</v>
+        <v>-2.254</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.074</v>
+        <v>0.0242</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.8144</v>
+        <v>0.1935</v>
       </c>
       <c r="G19" t="b">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D20" s="16" t="n">
-        <v>1.526</v>
+        <v>-2.162</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>0.1271</v>
+        <v>0.0306</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>1</v>
+        <v>0.2142</v>
       </c>
       <c r="G20" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>-1.186</v>
+        <v>1.506</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>0.2358</v>
+        <v>0.132</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>1</v>
+        <v>0.7922</v>
       </c>
       <c r="G21" t="b">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>1.186</v>
+        <v>-1.42</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>0.2358</v>
+        <v>0.1556</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>1</v>
+        <v>0.7922</v>
       </c>
       <c r="G22" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D23" s="15" t="n">
-        <v>-1.135</v>
+        <v>1.205</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>0.2563</v>
+        <v>0.2282</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>1</v>
+        <v>0.9129</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D24" s="16" t="n">
-        <v>-0.401</v>
+        <v>0.644</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>0.6884</v>
+        <v>0.5195</v>
       </c>
       <c r="F24" s="16" t="n">
         <v>1</v>
@@ -5849,14 +5963,14 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5865,10 +5979,10 @@
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>-0.401</v>
+        <v>-0.644</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.6884</v>
+        <v>0.5195</v>
       </c>
       <c r="F25" s="15" t="n">
         <v>1</v>
@@ -5878,26 +5992,26 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>0.227</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>0.8204</v>
+        <v>0.9314</v>
       </c>
       <c r="F26" s="16" t="n">
         <v>1</v>
@@ -5907,36 +6021,36 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>0.227</v>
+        <v>-2.93</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>0.8204</v>
+        <v>0.0034</v>
       </c>
       <c r="F27" s="15" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="G27" t="b">
         <v>1</v>
       </c>
-      <c r="G27" t="b">
-        <v>0</v>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S06</t>
         </is>
       </c>
     </row>
@@ -5948,24 +6062,24 @@
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>-0.178</v>
+        <v>-2.479</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>0.8587</v>
+        <v>0.0132</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>1</v>
+        <v>0.0659</v>
       </c>
       <c r="G28" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S06</t>
         </is>
       </c>
     </row>
@@ -5977,60 +6091,60 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>0</v>
+        <v>1.634</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>1</v>
+        <v>0.1023</v>
       </c>
       <c r="F29" s="15" t="n">
-        <v>1</v>
+        <v>0.4092</v>
       </c>
       <c r="G29" t="b">
         <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S06</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="7" t="inlineStr">
         <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
       <c r="D30" s="16" t="n">
-        <v>2.209</v>
+        <v>1.212</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>0.0271</v>
+        <v>0.2254</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>0.0814</v>
+        <v>0.6763</v>
       </c>
       <c r="G30" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6039,424 +6153,47 @@
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>-2.05</v>
+        <v>-1.183</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>0.0404</v>
+        <v>0.2367</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>0.0814</v>
+        <v>0.6763</v>
       </c>
       <c r="G31" t="b">
         <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S06</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="7" t="inlineStr">
         <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
       <c r="D32" s="16" t="n">
-        <v>-0.114</v>
+        <v>0.422</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>0.909</v>
+        <v>0.6733</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>0.909</v>
+        <v>0.6763</v>
       </c>
       <c r="G32" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>S03</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="n">
-        <v>2.883</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>0.0039</v>
-      </c>
-      <c r="F33" s="15" t="n">
-        <v>0.0394</v>
-      </c>
-      <c r="G33" t="b">
-        <v>1</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="D34" s="16" t="n">
-        <v>2.669</v>
-      </c>
-      <c r="E34" s="16" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="F34" s="16" t="n">
-        <v>0.06850000000000001</v>
-      </c>
-      <c r="G34" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="n">
-        <v>2.017</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>0.0437</v>
-      </c>
-      <c r="F35" s="15" t="n">
-        <v>0.3498</v>
-      </c>
-      <c r="G35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>-1.887</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>0.0592</v>
-      </c>
-      <c r="F36" s="16" t="n">
-        <v>0.4145</v>
-      </c>
-      <c r="G36" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>0.1261</v>
-      </c>
-      <c r="F37" s="15" t="n">
-        <v>0.7567</v>
-      </c>
-      <c r="G37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>-1.07</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>0.2848</v>
-      </c>
-      <c r="F38" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>-1.019</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.3083</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>0.4252</v>
-      </c>
-      <c r="F40" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="D41" s="15" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>0.4489</v>
-      </c>
-      <c r="F41" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="n">
-        <v>-0.019</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>0.9845</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="n">
-        <v>-2.509</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="F43" s="15" t="n">
-        <v>0.0363</v>
-      </c>
-      <c r="G43" t="b">
-        <v>1</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>S06</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="n">
-        <v>-1.919</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="F44" s="16" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G44" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>S06</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="D45" s="15" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0.5548999999999999</v>
-      </c>
-      <c r="F45" s="15" t="n">
-        <v>0.5548999999999999</v>
-      </c>
-      <c r="G45" t="b">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
@@ -6535,10 +6272,10 @@
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>40</v>
@@ -6554,16 +6291,16 @@
         <v>30</v>
       </c>
       <c r="D6" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="E6" s="7" t="n">
-        <v>14</v>
-      </c>
       <c r="F6" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>43.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -6576,16 +6313,16 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>36.7</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="8">
@@ -6602,7 +6339,7 @@
       <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>chi2=1.22, df=4, p=0.8749, G-test p=0.8809, Fisher-exact p=0.8945</t>
+          <t>chi2=0.92, df=4, p=0.9211, G-test p=0.9260, Fisher-exact p=0.9383</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6355,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>V=0.082 / min exp=3.67</t>
+          <t>V=0.072 / min exp=3.67</t>
         </is>
       </c>
     </row>
@@ -6730,31 +6467,31 @@
         <v>30</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>44.13</v>
+        <v>45.1</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.52</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>18.73</v>
+        <v>20.17</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>8.609999999999999</v>
+        <v>8.91</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>6.13</v>
+        <v>6.03</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>23.3</v>
+        <v>10</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>23.3</v>
+        <v>26.7</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>26.7</v>
+        <v>60</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>26.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -6764,34 +6501,34 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>40.1</v>
+        <v>39.11</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>9.73</v>
+        <v>12.7</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>15.85</v>
+        <v>12.5</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>4.65</v>
+        <v>5.22</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>65</v>
+        <v>27.8</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>30</v>
+        <v>27.8</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>5</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="7">
@@ -6801,34 +6538,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>40.4</v>
+        <v>43.67</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>12.19</v>
+        <v>10.28</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>17.9</v>
+        <v>12.83</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>10.44</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>4.3</v>
+        <v>4.75</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>10</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -6841,31 +6578,31 @@
         <v>30</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>38.77</v>
+        <v>37.87</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>11.31</v>
+        <v>11.58</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>12.77</v>
+        <v>11.97</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>7.95</v>
+        <v>7.65</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>4.7</v>
+        <v>4.43</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>23.3</v>
+        <v>10</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>23.3</v>
+        <v>56.7</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>43.3</v>
+        <v>26.7</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>10</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="9">
@@ -6878,31 +6615,31 @@
         <v>90</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>41.03</v>
+        <v>41.3</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>10.87</v>
+        <v>11.24</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>16.01</v>
+        <v>14.92</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>9.01</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>5.12</v>
+        <v>5.17</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>33.3</v>
+        <v>37.8</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>35.6</v>
+        <v>38.9</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
     </row>
   </sheetData>
@@ -6973,13 +6710,13 @@
         <v>30</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>30.14</v>
+        <v>28.27</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>9.630000000000001</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>30.62</v>
+        <v>27.04</v>
       </c>
     </row>
     <row r="6">
@@ -6992,13 +6729,13 @@
         <v>30</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>83.73999999999999</v>
+        <v>87.08</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>20.26</v>
+        <v>40.06</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>84.06999999999999</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="7">
@@ -7011,13 +6748,13 @@
         <v>30</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>182</v>
+        <v>194.5</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>45.88</v>
+        <v>84.69</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>176.02</v>
+        <v>194.06</v>
       </c>
     </row>
     <row r="8">
@@ -7073,7 +6810,7 @@
       <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>U=10, p&lt;0.0001</t>
+          <t>U=27, p&lt;0.0001</t>
         </is>
       </c>
     </row>
@@ -7144,13 +6881,13 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>4.42</v>
+        <v>6.69</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>195.58</v>
+        <v>180.31</v>
       </c>
     </row>
     <row r="6">
@@ -7165,13 +6902,13 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>218.75</v>
+        <v>211</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>8</v>
+        <v>7.42</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>210.75</v>
+        <v>203.58</v>
       </c>
     </row>
     <row r="7">
@@ -7186,13 +6923,13 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>148.33</v>
+        <v>237.5</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>5.82</v>
+        <v>1.93</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>142.51</v>
+        <v>235.57</v>
       </c>
     </row>
     <row r="8">
@@ -7207,13 +6944,13 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>5.06</v>
+        <v>3.9</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>169.94</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="9">
@@ -7228,13 +6965,13 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>158.75</v>
+        <v>110</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>2.94</v>
+        <v>6.43</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>155.81</v>
+        <v>103.57</v>
       </c>
     </row>
     <row r="10">
@@ -7249,13 +6986,13 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>198.33</v>
+        <v>132</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>8.470000000000001</v>
+        <v>6.19</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>189.86</v>
+        <v>125.81</v>
       </c>
     </row>
     <row r="11">
@@ -7270,13 +7007,13 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>115</v>
+        <v>189</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>3.67</v>
+        <v>6.02</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>111.33</v>
+        <v>182.98</v>
       </c>
     </row>
     <row r="12">
@@ -7291,13 +7028,13 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>8.5</v>
+        <v>5.28</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>175.5</v>
+        <v>130.72</v>
       </c>
     </row>
     <row r="13">
@@ -7312,13 +7049,13 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>3.62</v>
+        <v>4.24</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>156.38</v>
+        <v>218.76</v>
       </c>
     </row>
     <row r="14">
@@ -7333,13 +7070,13 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>197.5</v>
+        <v>152</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>4.12</v>
+        <v>4.87</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>193.38</v>
+        <v>147.13</v>
       </c>
     </row>
     <row r="15">
@@ -7354,13 +7091,13 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>205</v>
+        <v>259</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>5.38</v>
+        <v>2.92</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>199.62</v>
+        <v>256.08</v>
       </c>
     </row>
     <row r="16">
@@ -7375,13 +7112,13 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>154</v>
+        <v>231.25</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>4.24</v>
+        <v>4.93</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>149.76</v>
+        <v>226.32</v>
       </c>
     </row>
     <row r="17">
@@ -7396,13 +7133,13 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>201</v>
+        <v>157</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>3.4</v>
+        <v>16.38</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>197.6</v>
+        <v>140.62</v>
       </c>
     </row>
     <row r="18">
@@ -7417,13 +7154,13 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>192.5</v>
+        <v>183.55</v>
       </c>
       <c r="E18" s="16" t="n">
         <v>4.23</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>188.27</v>
+        <v>179.32</v>
       </c>
     </row>
     <row r="19">
@@ -7438,13 +7175,13 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>6.07</v>
+        <v>4.39</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>177.93</v>
+        <v>195.61</v>
       </c>
     </row>
     <row r="20">
@@ -7458,14 +7195,14 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n">
-        <v>132.5</v>
+      <c r="D20" s="16" t="n">
+        <v>99</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>129.34</v>
+        <v>13.02</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>85.98</v>
       </c>
     </row>
     <row r="21">
@@ -7480,13 +7217,13 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>133.33</v>
+        <v>294.75</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>3.02</v>
+        <v>4.25</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>130.31</v>
+        <v>290.49</v>
       </c>
     </row>
     <row r="22">
@@ -7501,13 +7238,13 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>179</v>
+        <v>228</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>4.13</v>
+        <v>3.17</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>174.87</v>
+        <v>224.83</v>
       </c>
     </row>
     <row r="23">
@@ -7525,10 +7262,10 @@
         <v>151</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>5.1</v>
+        <v>10.2</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>145.9</v>
+        <v>140.8</v>
       </c>
     </row>
     <row r="24">
@@ -7542,14 +7279,14 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="D24" s="16" t="n">
-        <v>96.47</v>
+      <c r="D24" s="8" t="n">
+        <v>242.5</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>91.8</v>
+        <v>5.91</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>236.59</v>
       </c>
     </row>
     <row r="25">
@@ -7564,13 +7301,13 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>188.33</v>
+        <v>252</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>5.54</v>
+        <v>4.82</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>182.79</v>
+        <v>247.18</v>
       </c>
     </row>
     <row r="26">
@@ -7585,13 +7322,13 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>171.25</v>
+        <v>212.35</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>4.71</v>
+        <v>12.39</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>166.54</v>
+        <v>199.96</v>
       </c>
     </row>
     <row r="27">
@@ -7606,13 +7343,13 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>4.37</v>
+        <v>4.05</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>197.63</v>
+        <v>180.95</v>
       </c>
     </row>
     <row r="28">
@@ -7627,13 +7364,13 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>202.5</v>
+        <v>206.25</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>7.29</v>
+        <v>6.87</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>195.21</v>
+        <v>199.38</v>
       </c>
     </row>
     <row r="29">
@@ -7648,13 +7385,13 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>241.16</v>
+        <v>264.6</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>6.01</v>
+        <v>13.51</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>235.15</v>
+        <v>251.09</v>
       </c>
     </row>
     <row r="30">
@@ -7669,13 +7406,13 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>180</v>
+        <v>255</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>5.48</v>
+        <v>5.09</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>174.52</v>
+        <v>249.91</v>
       </c>
     </row>
     <row r="31">
@@ -7690,13 +7427,13 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>142</v>
+        <v>258.91</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>4.06</v>
+        <v>5.22</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>137.94</v>
+        <v>253.69</v>
       </c>
     </row>
     <row r="32">
@@ -7711,13 +7448,13 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>157.5</v>
+        <v>147</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>154.3</v>
+        <v>141.75</v>
       </c>
     </row>
     <row r="33">
@@ -7732,13 +7469,13 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>201.25</v>
+        <v>115</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>4.49</v>
+        <v>8.75</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>196.76</v>
+        <v>106.25</v>
       </c>
     </row>
     <row r="34">
@@ -7753,13 +7490,13 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>210</v>
+        <v>184</v>
       </c>
       <c r="E34" s="16" t="n">
-        <v>4.85</v>
+        <v>3.82</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>205.15</v>
+        <v>180.18</v>
       </c>
     </row>
     <row r="35">
@@ -7775,10 +7512,10 @@
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="15" t="n">
-        <v>0.43</v>
+        <v>-0.334</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>0.0177</v>
+        <v>0.0709</v>
       </c>
     </row>
   </sheetData>
@@ -7843,10 +7580,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>0.8544</v>
+        <v>0.7972</v>
       </c>
       <c r="E5" s="15" t="n">
         <v>0</v>
@@ -7864,10 +7601,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>0.8457</v>
+        <v>0.8024</v>
       </c>
       <c r="E6" s="16" t="n">
         <v>0</v>
@@ -7885,10 +7622,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>0.9076</v>
+        <v>0.8688</v>
       </c>
       <c r="E7" s="15" t="n">
         <v>0</v>
@@ -7906,10 +7643,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.8708</v>
       </c>
       <c r="E8" s="16" t="n">
         <v>0</v>
@@ -7927,10 +7664,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.8333</v>
+        <v>0.7765</v>
       </c>
       <c r="E9" s="15" t="n">
         <v>0</v>
@@ -8055,25 +7792,25 @@
         <v>30</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>797.4</v>
+        <v>775.01</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>272.75</v>
+        <v>347.99</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>821</v>
+        <v>671.8</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>373.2</v>
+        <v>298.6</v>
       </c>
       <c r="H5" s="6" t="n">
         <v>1306.2</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5.37</v>
+        <v>5.33</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>636.67</v>
+        <v>666.67</v>
       </c>
     </row>
     <row r="6">
@@ -8086,27 +7823,27 @@
         <v>30</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>204.51</v>
+        <v>210.73</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>107.05</v>
+        <v>121.4</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>186.6</v>
+        <v>205.3</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>44.8</v>
+        <v>41</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>410.5</v>
+        <v>447.8</v>
       </c>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
       <c r="K6" s="8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>79.97</v>
+        <v>80.5</v>
       </c>
       <c r="M6" s="7" t="n"/>
     </row>
@@ -8120,22 +7857,22 @@
         <v>30</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>99.95</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>27.47</v>
+        <v>28.91</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>103.5</v>
+        <v>83.5</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>5.43</v>
+        <v>5.33</v>
       </c>
     </row>
   </sheetData>
@@ -8152,7 +7889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F34"/>
+  <dimension ref="B2:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="2" max="2"/>
@@ -8220,10 +7957,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -8243,10 +7980,10 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -8266,10 +8003,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>83.3</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="8">
@@ -8289,10 +8026,10 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>16.7</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="9">
@@ -8312,10 +8049,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>43.3</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="10">
@@ -8335,10 +8072,10 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>40</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="11">
@@ -8358,10 +8095,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
@@ -8372,19 +8109,19 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Source location</t>
+          <t>Supplier category</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Karnaphuli river ghat</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>30</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="13">
@@ -8400,14 +8137,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fishery Ghat landing</t>
+          <t>Karnaphuli river ghat</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="14">
@@ -8423,14 +8160,14 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Bhola charter landing</t>
+          <t>Fishery Ghat landing</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -8446,14 +8183,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kuakata</t>
+          <t>Cox's Bazar landing</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="16">
@@ -8469,14 +8206,14 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Teknaf</t>
+          <t>Kuakata</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="17">
@@ -8515,14 +8252,14 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Kutubdia</t>
+          <t>Bhola charter landing</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -8538,7 +8275,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cox's Bazar landing</t>
+          <t>Teknaf</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -8565,10 +8302,10 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -8588,10 +8325,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
@@ -8611,10 +8348,10 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>26.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -8634,10 +8371,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>56.7</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="24">
@@ -8657,10 +8394,10 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="25">
@@ -8676,14 +8413,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fisherman</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>16.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="26">
@@ -8699,14 +8436,14 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Fisherman</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="27">
@@ -8726,10 +8463,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>70</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="28">
@@ -8745,14 +8482,14 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Hawker</t>
+          <t>Hotel</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="29">
@@ -8768,14 +8505,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Hawker</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="30">
@@ -8791,14 +8528,14 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Institutional</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>6.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="31">
@@ -8809,19 +8546,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sells to</t>
+          <t>Sells on credit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Institutional</t>
+          <t>Almost_all</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="32">
@@ -8837,14 +8574,14 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Almost_all</t>
+          <t>Some</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>16.7</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="33">
@@ -8860,36 +8597,13 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Some</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Form R (Retailer)</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Sells on credit</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9047,43 +8761,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>6</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1031.62</v>
+        <v>1090.23</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1083.3</v>
+        <v>1140.48</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>1236.41</v>
+        <v>1331.09</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>1486.96</v>
+        <v>1612.56</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>1420</v>
+        <v>1595.71</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>51.68</v>
+        <v>50.25</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>153.11</v>
+        <v>190.61</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>183.59</v>
+        <v>264.62</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>388.38</v>
+        <v>505.48</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>72.59999999999999</v>
+        <v>68.3</v>
       </c>
     </row>
     <row r="6">
@@ -9103,7 +8817,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>6</v>
@@ -9113,34 +8827,34 @@
       </c>
       <c r="H6" s="7" t="inlineStr"/>
       <c r="I6" s="8" t="n">
-        <v>1110.67</v>
+        <v>1100.52</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>1165.59</v>
+        <v>1150.29</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>1378.04</v>
+        <v>1358.9</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>1619.16</v>
+        <v>1589.29</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>1615</v>
+        <v>1656.67</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>54.92</v>
+        <v>49.77</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>212.45</v>
+        <v>208.61</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>236.96</v>
+        <v>297.77</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>504.33</v>
+        <v>556.15</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>68.8</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -9160,43 +8874,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>3</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>735.53</v>
+        <v>734.64</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>771.7</v>
+        <v>770.36</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>886.61</v>
+        <v>905.1799999999999</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>1069.64</v>
+        <v>1064.62</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>1033.33</v>
+        <v>1053.33</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>36.17</v>
+        <v>35.72</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>114.91</v>
+        <v>134.82</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>146.72</v>
+        <v>148.15</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>297.8</v>
+        <v>318.69</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>71.2</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="8">
@@ -9216,44 +8930,44 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
       <c r="I8" s="8" t="n">
-        <v>660.95</v>
+        <v>627.46</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>687.75</v>
+        <v>652.02</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>762.77</v>
+        <v>754.73</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>933.4400000000001</v>
+        <v>913.98</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>885</v>
+        <v>895</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>26.8</v>
+        <v>24.56</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>75.02</v>
+        <v>102.71</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>122.23</v>
+        <v>140.27</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>224.05</v>
+        <v>267.54</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>74.7</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -9273,43 +8987,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>6</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>407.79</v>
+        <v>396.57</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>428.72</v>
+        <v>413.99</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>501.77</v>
+        <v>496.09</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>581.23</v>
+        <v>594.26</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>585</v>
+        <v>579.17</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>20.93</v>
+        <v>17.42</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>73.05</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>83.23</v>
+        <v>83.08</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>177.21</v>
+        <v>182.6</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>69.7</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="10">
@@ -9329,7 +9043,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>6</v>
@@ -9339,34 +9053,34 @@
       </c>
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="8" t="n">
-        <v>314.1</v>
+        <v>316.75</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>323.55</v>
+        <v>332.07</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>380.42</v>
+        <v>382.23</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>457.13</v>
+        <v>446.97</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>446.54</v>
+        <v>444.62</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>9.449999999999999</v>
+        <v>15.32</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>56.87</v>
+        <v>50.16</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>66.12</v>
+        <v>62.39</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>132.44</v>
+        <v>127.87</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>70.3</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="11">
@@ -9386,43 +9100,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>361.74</v>
+        <v>363.42</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>377.81</v>
+        <v>375.13</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>450.16</v>
+        <v>447.86</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>545.45</v>
+        <v>543.4400000000001</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>530</v>
+        <v>522.5</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>16.07</v>
+        <v>11.71</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>72.34999999999999</v>
+        <v>72.73</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>79.84</v>
+        <v>74.64</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>168.26</v>
+        <v>159.08</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>68.3</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -9442,39 +9156,45 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>Descriptive-only (Method 3.8): retail quotes in 2 market(s); consumer quotes n=1 (&lt;3; share not reported)</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
       <c r="I12" s="8" t="n">
-        <v>231.78</v>
+        <v>237.81</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>241.16</v>
+        <v>250.09</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>279.01</v>
+        <v>290.92</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>325</v>
+        <v>340.36</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>330</v>
-      </c>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
-      <c r="P12" s="7" t="n"/>
-      <c r="Q12" s="7" t="n"/>
-      <c r="R12" s="7" t="n"/>
+        <v>332</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>41.08</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>94.19</v>
+      </c>
+      <c r="R12" s="8" t="n">
+        <v>71.59999999999999</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -9493,48 +9213,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>Descriptive-only (Method 3.8): retail quotes in 2 market(s)</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>188.91</v>
+        <v>184.89</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>195.61</v>
+        <v>192.39</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>234.46</v>
+        <v>222.62</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>263.01</v>
+        <v>263.08</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>267.5</v>
+        <v>258.33</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>38.85</v>
+        <v>30.23</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>33.04</v>
+        <v>35.71</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>78.59</v>
+        <v>73.44</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -9554,37 +9269,45 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="F14" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="8" t="n">
-        <v>1</v>
-      </c>
       <c r="G14" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>Descriptive-only (Method 3.8): retail quotes in 1 market(s); consumer quotes n=1 (&lt;3; share not reported)</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="8" t="n">
-        <v>163.45</v>
-      </c>
-      <c r="J14" s="7" t="n"/>
+        <v>159.24</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>166.13</v>
+      </c>
       <c r="K14" s="8" t="n">
-        <v>179.53</v>
+        <v>191.14</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>230</v>
+        <v>226.34</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>215</v>
-      </c>
-      <c r="N14" s="7" t="n"/>
-      <c r="O14" s="7" t="n"/>
-      <c r="P14" s="7" t="n"/>
-      <c r="Q14" s="7" t="n"/>
-      <c r="R14" s="7" t="n"/>
+        <v>223</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="P14" s="8" t="n">
+        <v>31.86</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>63.76</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>71.40000000000001</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
@@ -9594,7 +9317,7 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Mean of species means (chain-complete: S01, S02, S03, S04, S05, S06, S07, S09)</t>
+          <t>Mean of species means (chain-complete: S01, S02, S03, S04, S05, S06, S07, S08, S09, S10)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9603,42 +9326,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Pooled over 8 chain-complete species (consumer n &gt;= 3)</t>
+          <t>Pooled over 10 chain-complete species (consumer n &gt;= 3)</t>
         </is>
       </c>
       <c r="I15" s="6" t="n">
-        <v>601.41</v>
+        <v>521.15</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>629.25</v>
+        <v>544.3</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>728.83</v>
+        <v>638.08</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>869.5</v>
+        <v>759.49</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>847.8</v>
+        <v>756.03</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>27.84</v>
+        <v>23.15</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>99.58</v>
+        <v>93.78</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>118.97</v>
+        <v>117.95</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>246.39</v>
+        <v>234.88</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>70.90000000000001</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -9735,13 +9458,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -9766,13 +9489,13 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>184444.44</v>
+        <v>197272.73</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>64986.17</v>
+        <v>84764.75999999999</v>
       </c>
       <c r="H6" s="7" t="inlineStr"/>
     </row>
@@ -9793,13 +9516,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>19583.33</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>9440.799999999999</v>
+        <v>12500</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>10388.87</v>
       </c>
     </row>
     <row r="8">
@@ -9819,13 +9542,13 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>8330.77</v>
+        <v>8523.33</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>3205.84</v>
+        <v>3078.03</v>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
     </row>
@@ -9846,13 +9569,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>9025</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>2223.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -9875,10 +9592,10 @@
         <v>30</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>5.37</v>
+        <v>5.33</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>2.47</v>
+        <v>1.97</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
@@ -9906,10 +9623,10 @@
         <v>30</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>636.67</v>
+        <v>666.67</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>122.43</v>
+        <v>91.29000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -9929,13 +9646,13 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>6093.75</v>
+        <v>7088.24</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>3045.32</v>
+        <v>3260.73</v>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
     </row>
@@ -9959,10 +9676,10 @@
         <v>30</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1880</v>
+        <v>1698.33</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1172.21</v>
+        <v>1170.14</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
@@ -9990,10 +9707,10 @@
         <v>30</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>1636.67</v>
+        <v>1943.33</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>821.89</v>
+        <v>1025.85</v>
       </c>
       <c r="H14" s="7" t="inlineStr"/>
     </row>
@@ -10017,10 +9734,10 @@
         <v>30</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="16">
@@ -10043,10 +9760,10 @@
         <v>30</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>258.33</v>
+        <v>316.67</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>119.69</v>
+        <v>121.3</v>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
     </row>
@@ -10070,10 +9787,10 @@
         <v>30</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>79.97</v>
+        <v>80.5</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>27.03</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="18">
@@ -10096,10 +9813,10 @@
         <v>30</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>259.33</v>
+        <v>253</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>91.91</v>
+        <v>96.14</v>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
     </row>
@@ -10120,13 +9837,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.96</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -10146,13 +9863,13 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>700</v>
+        <v>560</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>244.95</v>
+        <v>134.16</v>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
     </row>
@@ -10176,7 +9893,7 @@
         <v>30</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1.86</v>
@@ -10202,10 +9919,10 @@
         <v>30</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>204.67</v>
+        <v>221.33</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>81.84</v>
+        <v>97.03</v>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
     </row>
@@ -10229,10 +9946,10 @@
         <v>30</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>185.33</v>
+        <v>158.5</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>56.54</v>
+        <v>55.94</v>
       </c>
     </row>
     <row r="24">
@@ -10255,10 +9972,10 @@
         <v>30</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>79.83</v>
+        <v>87.67</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>37.31</v>
+        <v>33.65</v>
       </c>
       <c r="H24" s="7" t="inlineStr"/>
     </row>
@@ -10282,10 +9999,10 @@
         <v>30</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>5.43</v>
+        <v>5.33</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
     </row>
   </sheetData>
@@ -10302,7 +10019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:K11"/>
+  <dimension ref="B2:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.65" customWidth="1" min="2" max="2"/>
@@ -10385,22 +10102,22 @@
     </row>
     <row r="5">
       <c r="B5" s="6" t="n">
-        <v>67.59999999999999</v>
+        <v>67.73</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>13.63</v>
+        <v>15</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>18.77</v>
+        <v>17.27</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>12</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -10413,22 +10130,22 @@
     </row>
     <row r="6">
       <c r="B6" s="8" t="n">
-        <v>63.87</v>
+        <v>63.5</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>15.7</v>
+        <v>17.03</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>20.43</v>
+        <v>19.47</v>
       </c>
       <c r="E6" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="F6" s="8" t="n">
-        <v>14</v>
-      </c>
       <c r="G6" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
@@ -10443,19 +10160,19 @@
     </row>
     <row r="7">
       <c r="B7" s="6" t="n">
-        <v>55.23</v>
+        <v>51.83</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>28.63</v>
+        <v>26.9</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>16.13</v>
+        <v>21.27</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>3</v>
@@ -10478,11 +10195,11 @@
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>bKash</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="I8" s="8" t="n">
-        <v>36.7</v>
+        <v>56.7</v>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
@@ -10496,11 +10213,11 @@
     <row r="9">
       <c r="H9" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="I9" s="6" t="n">
-        <v>36.7</v>
+        <v>23.3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -10520,7 +10237,7 @@
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Nagad_app</t>
+          <t>bKash</t>
         </is>
       </c>
       <c r="I10" s="8" t="n">
@@ -10532,24 +10249,6 @@
         </is>
       </c>
       <c r="K10" s="7" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Credit</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Consumer (Form C)</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
         <v>30</v>
       </c>
     </row>
@@ -10645,26 +10344,26 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply syndicate control</t>
+          <t>Transport cost increase</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>36.7</v>
+        <v>26.7</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>30</v>
+        <v>23.3</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>26.7</v>
+        <v>43.3</v>
       </c>
       <c r="I5" t="n">
         <v>28</v>
@@ -10676,14 +10375,14 @@
     <row r="6">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Unsold fish spoilage loss</t>
+          <t>Low landings in lean season</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>9</v>
@@ -10692,41 +10391,41 @@
         <v>30</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>23.3</v>
+        <v>30</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>31.1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Competition from frozen imported fish</t>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Waterlogging during monsoon</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E7" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="F7" s="6" t="n">
         <v>26.7</v>
       </c>
-      <c r="E7" t="n">
-        <v>10</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>33.3</v>
-      </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="I7" t="n">
         <v>26</v>
@@ -10738,14 +10437,14 @@
     <row r="8">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>High ice price</t>
+          <t>Day-to-day price volatility</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>10</v>
@@ -10754,10 +10453,10 @@
         <v>33.3</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>23.3</v>
+        <v>26.7</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>24</v>
@@ -10769,26 +10468,26 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Day-to-day price volatility</t>
+          <t>Delayed credit recovery</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
         <v>7</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="F9" s="6" t="n">
         <v>23.3</v>
       </c>
-      <c r="E9" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>20</v>
-      </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>33.3</v>
+        <v>23.3</v>
       </c>
       <c r="I9" t="n">
         <v>23</v>
@@ -10798,16 +10497,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Low landings in lean season</t>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Irregular electricity and load-shedding</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>8</v>
@@ -10816,22 +10515,22 @@
         <v>26.7</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>16.7</v>
+        <v>30</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Waterlogging during monsoon</t>
+          <t>Rising toll and lease burden</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -10841,35 +10540,35 @@
         <v>23.3</v>
       </c>
       <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="G11" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="H11" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G11" t="n">
-        <v>9</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>30</v>
-      </c>
       <c r="I11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Irregular electricity and load-shedding</t>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Supply syndicate control</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>4</v>
@@ -10878,10 +10577,10 @@
         <v>13.3</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>21</v>
@@ -10891,22 +10590,22 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Rising cost of ice and salt</t>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Competition from frozen imported fish</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="G13" t="n">
         <v>7</v>
@@ -10915,16 +10614,16 @@
         <v>23.3</v>
       </c>
       <c r="I13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Delayed credit recovery</t>
+          <t>Rising cost of ice and salt</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
@@ -10934,16 +10633,16 @@
         <v>20</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>23.3</v>
+        <v>26.7</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>20</v>
@@ -10955,45 +10654,45 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rising toll and lease burden</t>
+          <t>Unsold fish spoilage loss</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="E15" t="n">
         <v>5</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="F15" s="6" t="n">
         <v>16.7</v>
       </c>
-      <c r="E15" t="n">
-        <v>8</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>26.7</v>
-      </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="I15" t="n">
+        <v>18</v>
+      </c>
+      <c r="J15" s="6" t="n">
         <v>20</v>
-      </c>
-      <c r="J15" s="6" t="n">
-        <v>22.2</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Transport cost increase</t>
+          <t>High ice price</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>5</v>
@@ -11008,10 +10707,10 @@
         <v>26.7</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
     </row>
   </sheetData>

--- a/analysis_outputs/Analysis_Summary.xlsx
+++ b/analysis_outputs/Analysis_Summary.xlsx
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17" t="n">
         <v>11</v>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E21" t="n">
         <v>7</v>
@@ -931,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E20"/>
+  <dimension ref="B2:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="2" max="2"/>
@@ -950,7 +950,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Consumers n=30; focal purchases n=69 (Yes today n=52).</t>
+          <t>Consumers n=30; focal purchases n=66 (Yes today n=54).</t>
         </is>
       </c>
     </row>
@@ -988,10 +988,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>53.3</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="6">
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>46.7</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="7">
@@ -1020,14 +1020,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bKash</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>36.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1038,14 +1038,14 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Nagad_app</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>36.7</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="9">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nagad_app</t>
+          <t>bKash</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1096,10 +1096,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>33.3</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="12">
@@ -1110,14 +1110,14 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Price</t>
+          <t>Familiar_shop</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Proximity</t>
+          <t>Price</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="14">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Familiar_shop</t>
+          <t>Proximity</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
@@ -1164,46 +1164,45 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Main reason for choosing seller</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
           <t>Variety</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="E16" s="8" t="n">
         <v>3.3</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="7" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Mean visit interval (days)</t>
         </is>
       </c>
-      <c r="C16" s="8" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="D16" s="7" t="n">
+      <c r="C17" s="6" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="D17" t="n">
         <v>30</v>
-      </c>
-      <c r="E16" s="7" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>Focal purchase source (per purchase)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Retailer</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>49</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>71</v>
       </c>
     </row>
     <row r="18">
@@ -1214,42 +1213,60 @@
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Hawker</t>
+          <t>Retailer</t>
         </is>
       </c>
       <c r="D18" s="7" t="n">
-        <v>3</v>
+        <v>51</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>4.3</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="9" t="inlineStr">
         <is>
+          <t>Focal purchase source (per purchase)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Hawker</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="10" t="inlineStr">
+        <is>
           <t>Mean focal-species price paid (BDT/kg)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
-        <v>699.04</v>
-      </c>
-      <c r="D19" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="n">
+        <v>752.22</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="E20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Mean purchase size (kg)</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="D20" s="7" t="n">
-        <v>52</v>
-      </c>
-      <c r="E20" s="7" t="n"/>
+      <c r="C21" s="6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="D21" t="n">
+        <v>54</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1313,17 +1330,17 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Khoira</t>
+          <t>Datina</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>268</v>
+        <v>378.33</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
@@ -1336,7 +1353,7 @@
         <v>3</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1033.33</v>
+        <v>995</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>0.83</v>
@@ -1345,65 +1362,65 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Datina</t>
+          <t>Chatka chingri</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>356.67</v>
+        <v>467.5</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Moid</t>
+          <t>Kakra (crab)</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>216.67</v>
+        <v>575</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kakra (crab)</t>
+          <t>Moid</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>570</v>
+        <v>180</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Chatka chingri</t>
+          <t>Faisya</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>440</v>
+        <v>332.5</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11">
@@ -1413,29 +1430,29 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2615</v>
+        <v>2800</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Faisya</t>
+          <t>Khoira</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1471,7 +1488,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Unweighted means of species-level means over chain-complete species only (n_species=8; see Table 3 note). Producer &amp; auction prices from landing-linked markets M1/M6 (first-sale proxy, Methodology 3.11c); wholesale price = Bepari sell over all markets; retail price = consumer-paid anchor (Form C slips). Margins are differences of consecutive level means, so they sum exactly to the total spread and PS% + spread% = 100. Margin % is expressed as a share of the pooled consumer price.</t>
+          <t>Unweighted means of species-level means over chain-complete species only (n_species=7; see Table 3 note). Producer &amp; auction prices from landing-linked markets M1/M6 (first-sale proxy, Methodology 3.11c); wholesale price = Bepari sell over all markets; retail price = consumer-paid anchor (Form C slips). Margins are differences of consecutive level means, so they sum exactly to the total spread and PS% + spread% = 100. Margin % is expressed as a share of the pooled consumer price.</t>
         </is>
       </c>
     </row>
@@ -1504,13 +1521,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>27.84</v>
+        <v>27.01</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -1520,13 +1537,13 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>99.58</v>
+        <v>108.26</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>11.7</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="7">
@@ -1536,13 +1553,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>118.97</v>
+        <v>124.18</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>14</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="8">
@@ -1552,13 +1569,13 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>246.39</v>
+        <v>259.45</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>29.1</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="9">
@@ -1568,10 +1585,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>70.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1658,22 +1675,22 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>1416</v>
+        <v>1441</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1480</v>
+        <v>1558</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>1491</v>
+        <v>1551</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1497</v>
+        <v>1536</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1571</v>
+        <v>1654</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1445</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="6">
@@ -1683,22 +1700,22 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1586</v>
+        <v>1708</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1603</v>
+        <v>1689</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>1645</v>
+        <v>1713</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1597</v>
+        <v>1615</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1717</v>
+        <v>1742</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>1590</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="7">
@@ -1707,17 +1724,23 @@
           <t>S03 Lakkha</t>
         </is>
       </c>
+      <c r="C7" s="6" t="n">
+        <v>998</v>
+      </c>
       <c r="D7" s="6" t="n">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1047</v>
+        <v>1130</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1126</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1112</v>
+        <v>1090</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1045</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="8">
@@ -1726,21 +1749,21 @@
           <t>S04 Koral/Kurl</t>
         </is>
       </c>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="8" t="n">
-        <v>958</v>
-      </c>
+      <c r="C8" s="8" t="n">
+        <v>886</v>
+      </c>
+      <c r="D8" s="7" t="n"/>
       <c r="E8" s="8" t="n">
-        <v>938</v>
+        <v>994</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>895</v>
+        <v>980</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>963</v>
+        <v>955</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>902</v>
+        <v>907</v>
       </c>
     </row>
     <row r="9">
@@ -1750,22 +1773,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>614</v>
+        <v>629</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>569</v>
+        <v>612</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>551</v>
+        <v>582</v>
       </c>
     </row>
     <row r="10">
@@ -1775,22 +1798,22 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>416</v>
+        <v>463</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>472</v>
+        <v>498</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>460</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11">
@@ -1800,19 +1823,19 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>555</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>595</v>
+        <v>567</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>563</v>
+        <v>575</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>545</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>505</v>
+        <v>520</v>
       </c>
     </row>
     <row r="12">
@@ -1821,16 +1844,14 @@
           <t>S08 Kankoita</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n">
-        <v>310</v>
-      </c>
+      <c r="C12" s="7" t="n"/>
       <c r="D12" s="7" t="n"/>
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="8" t="n">
-        <v>340</v>
-      </c>
+      <c r="G12" s="8" t="n">
+        <v>345</v>
+      </c>
+      <c r="H12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
@@ -1839,10 +1860,7 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>247</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>279</v>
+        <v>258</v>
       </c>
     </row>
     <row r="14">
@@ -1852,11 +1870,13 @@
         </is>
       </c>
       <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
-      <c r="F14" s="8" t="n">
-        <v>230</v>
-      </c>
+      <c r="D14" s="8" t="n">
+        <v>255</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>250</v>
+      </c>
+      <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="7" t="n"/>
     </row>
@@ -1874,7 +1894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L20"/>
+  <dimension ref="B2:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -1961,12 +1981,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>M1-A-03</t>
+          <t>M1-A-05</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1975,11 +1995,11 @@
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1024.92</v>
+        <v>783.76</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M1-R-01</t>
+          <t>M1-R-05</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1988,10 +2008,10 @@
         </is>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1030</v>
+        <v>783.76</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>-5.08</v>
+        <v>0</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -2010,12 +2030,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>M1-A-04</t>
+          <t>M1-A-01</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -2024,11 +2044,11 @@
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>1145.5</v>
+        <v>348.34</v>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>M1-R-04</t>
+          <t>M1-R-02</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -2037,10 +2057,10 @@
         </is>
       </c>
       <c r="J6" s="8" t="n">
-        <v>1145</v>
+        <v>350</v>
       </c>
       <c r="K6" s="16" t="n">
-        <v>0.5</v>
+        <v>-1.66</v>
       </c>
       <c r="L6" s="7" t="b">
         <v>1</v>
@@ -2049,22 +2069,22 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>PAIR-M1-03</t>
+          <t>PAIR-M2-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>M1-A-05</t>
+          <t>M2-A-04</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2073,11 +2093,11 @@
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>1004.82</v>
+        <v>870.85</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M1-R-02</t>
+          <t>M2-R-03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2086,10 +2106,10 @@
         </is>
       </c>
       <c r="J7" s="6" t="n">
-        <v>1005</v>
+        <v>870.85</v>
       </c>
       <c r="K7" s="15" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -2098,7 +2118,7 @@
     <row r="8">
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>PAIR-M2-01</t>
+          <t>PAIR-M2-02</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -2108,12 +2128,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S01</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>M2-A-05</t>
+          <t>M2-A-01</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -2122,11 +2142,11 @@
         </is>
       </c>
       <c r="G8" s="8" t="n">
-        <v>435.42</v>
+        <v>1205.79</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>M2-R-02</t>
+          <t>M2-R-05</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -2135,10 +2155,10 @@
         </is>
       </c>
       <c r="J8" s="8" t="n">
-        <v>435</v>
+        <v>1205.79</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="L8" s="7" t="b">
         <v>1</v>
@@ -2147,7 +2167,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>PAIR-M2-02</t>
+          <t>PAIR-M2-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2157,12 +2177,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>M2-A-02</t>
+          <t>M2-A-05</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2171,11 +2191,11 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>1292.87</v>
+        <v>448.82</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>M2-R-05</t>
+          <t>M2-R-01</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2184,10 +2204,10 @@
         </is>
       </c>
       <c r="J9" s="6" t="n">
-        <v>1290</v>
+        <v>450</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>2.87</v>
+        <v>-1.18</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -2206,12 +2226,12 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>S01</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>M3-A-03</t>
+          <t>M3-A-02</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -2220,11 +2240,11 @@
         </is>
       </c>
       <c r="G10" s="8" t="n">
-        <v>1091.91</v>
+        <v>756.97</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>M3-R-01</t>
+          <t>M3-R-03</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -2233,10 +2253,10 @@
         </is>
       </c>
       <c r="J10" s="8" t="n">
-        <v>1095</v>
+        <v>760</v>
       </c>
       <c r="K10" s="16" t="n">
-        <v>-3.09</v>
+        <v>-3.03</v>
       </c>
       <c r="L10" s="7" t="b">
         <v>1</v>
@@ -2255,32 +2275,61 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>S06</t>
-        </is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>M3-A-05</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1299.57</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>M3-R-04</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>-0.43</v>
       </c>
       <c r="L11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>PAIR-M3-03</t>
+          <t>PAIR-M4-01</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>M3-A-01</t>
+          <t>M4-A-01</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -2289,11 +2338,11 @@
         </is>
       </c>
       <c r="G12" s="8" t="n">
-        <v>468.92</v>
+        <v>1212.49</v>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>M3-R-02</t>
+          <t>M4-R-01</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -2302,10 +2351,10 @@
         </is>
       </c>
       <c r="J12" s="8" t="n">
-        <v>465</v>
+        <v>1219.19</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>3.92</v>
+        <v>-6.7</v>
       </c>
       <c r="L12" s="7" t="b">
         <v>1</v>
@@ -2314,7 +2363,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>PAIR-M4-01</t>
+          <t>PAIR-M4-02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2324,46 +2373,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>S02</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>M4-A-04</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Aratdar</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>1205.79</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>M4-R-03</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Khuchra</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>1205</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>0.79</v>
+          <t>S06</t>
+        </is>
       </c>
       <c r="L13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>PAIR-M4-02</t>
+          <t>PAIR-M4-03</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -2373,12 +2393,12 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>S07</t>
+          <t>S02</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>M4-A-03</t>
+          <t>M4-A-02</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -2387,11 +2407,11 @@
         </is>
       </c>
       <c r="G14" s="8" t="n">
-        <v>401.93</v>
+        <v>1205.79</v>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>M4-R-05</t>
+          <t>M4-R-02</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -2400,10 +2420,10 @@
         </is>
       </c>
       <c r="J14" s="8" t="n">
-        <v>401.93</v>
+        <v>1205</v>
       </c>
       <c r="K14" s="16" t="n">
-        <v>0</v>
+        <v>0.79</v>
       </c>
       <c r="L14" s="7" t="b">
         <v>1</v>
@@ -2422,12 +2442,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S06</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>M5-A-04</t>
+          <t>M5-A-03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2436,11 +2456,11 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>468.92</v>
+        <v>361.74</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>M5-R-03</t>
+          <t>M5-R-04</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2449,10 +2469,10 @@
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>465</v>
+        <v>360</v>
       </c>
       <c r="K15" s="15" t="n">
-        <v>3.92</v>
+        <v>1.74</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -2471,40 +2491,18 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>S01</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>M5-A-02</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Aratdar</t>
-        </is>
-      </c>
-      <c r="G16" s="8" t="n">
-        <v>1138.8</v>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>M5-R-01</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Khuchra</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="n">
-        <v>1135</v>
-      </c>
-      <c r="K16" s="16" t="n">
-        <v>3.8</v>
-      </c>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
       <c r="L16" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2520,11 +2518,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>S07</t>
-        </is>
+          <t>S05</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>M5-A-01</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Aratdar</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>468.92</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>M5-R-01</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Khuchra</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>465</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>3.92</v>
       </c>
       <c r="L17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -2540,12 +2567,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S03</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>M6-A-04</t>
+          <t>M6-A-02</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -2554,11 +2581,11 @@
         </is>
       </c>
       <c r="G18" s="8" t="n">
-        <v>1185.69</v>
+        <v>797.16</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>M6-R-05</t>
+          <t>M6-R-01</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -2567,10 +2594,10 @@
         </is>
       </c>
       <c r="J18" s="8" t="n">
-        <v>1185</v>
+        <v>795</v>
       </c>
       <c r="K18" s="16" t="n">
-        <v>0.6899999999999999</v>
+        <v>2.16</v>
       </c>
       <c r="L18" s="7" t="b">
         <v>1</v>
@@ -2589,12 +2616,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>M6-A-01</t>
+          <t>M6-A-05</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2603,7 +2630,7 @@
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>415.33</v>
+        <v>730.17</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2616,61 +2643,12 @@
         </is>
       </c>
       <c r="J19" s="6" t="n">
-        <v>415</v>
+        <v>730</v>
       </c>
       <c r="K19" s="15" t="n">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
       <c r="L19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>PAIR-M6-03</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>M6-A-02</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Aratdar</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>422.03</v>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>M6-R-03</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Khuchra</t>
-        </is>
-      </c>
-      <c r="J20" s="8" t="n">
-        <v>420</v>
-      </c>
-      <c r="K20" s="16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="L20" s="7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2721,7 +2699,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -2731,7 +2709,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -2741,7 +2719,7 @@
         </is>
       </c>
       <c r="C7" s="15" t="n">
-        <v>0.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2751,7 +2729,7 @@
         </is>
       </c>
       <c r="C8" s="16" t="n">
-        <v>0.78</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="9">
@@ -2761,7 +2739,7 @@
         </is>
       </c>
       <c r="C9" s="15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -2771,7 +2749,7 @@
         </is>
       </c>
       <c r="C10" s="16" t="n">
-        <v>0.1157</v>
+        <v>0.9219000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2878,28 +2856,28 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>1138.8</v>
+        <v>1155.55</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1416.25</v>
+        <v>1441.05</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1352.5</v>
+        <v>1410</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>277.45</v>
+        <v>285.5</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>213.7</v>
+        <v>254.45</v>
       </c>
     </row>
     <row r="6">
@@ -2914,25 +2892,29 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>1266.08</v>
+        <v>1329.72</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>4</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>1480</v>
+        <v>1557.74</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="7" t="n"/>
+      <c r="H6" s="8" t="n">
+        <v>1520</v>
+      </c>
       <c r="I6" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>213.92</v>
-      </c>
-      <c r="K6" s="7" t="n"/>
+        <v>228.02</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>190.28</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -2946,28 +2928,28 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1333.07</v>
+        <v>1311.63</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1491</v>
+        <v>1550.68</v>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1456.67</v>
+        <v>1582.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>157.93</v>
+        <v>239.05</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>123.6</v>
+        <v>270.87</v>
       </c>
     </row>
     <row r="8">
@@ -2982,25 +2964,29 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>1225.88</v>
+        <v>1286.17</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>1496.76</v>
+        <v>1535.79</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" s="7" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>1552.5</v>
+      </c>
       <c r="I8" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>270.88</v>
-      </c>
-      <c r="K8" s="7" t="n"/>
+        <v>249.62</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>266.33</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -3014,13 +3000,13 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1282.82</v>
+        <v>1303.59</v>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1570.75</v>
+        <v>1653.75</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -3029,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>287.93</v>
+        <v>350.16</v>
       </c>
     </row>
     <row r="10">
@@ -3044,28 +3030,28 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>1244.31</v>
+        <v>1260.72</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>1445</v>
+        <v>1475.65</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>1445</v>
+        <v>1420</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>200.69</v>
+        <v>214.93</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>200.69</v>
+        <v>159.28</v>
       </c>
     </row>
     <row r="11">
@@ -3080,28 +3066,28 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1309.62</v>
+        <v>1343.12</v>
       </c>
       <c r="E11" t="n">
         <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1586</v>
+        <v>1707.5</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1475</v>
+        <v>1585</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>276.38</v>
+        <v>364.38</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>165.38</v>
+        <v>241.88</v>
       </c>
     </row>
     <row r="12">
@@ -3116,13 +3102,13 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>1415.13</v>
+        <v>1426.85</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>1603.33</v>
+        <v>1688.58</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>3</v>
@@ -3132,7 +3118,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>188.2</v>
+        <v>261.73</v>
       </c>
       <c r="K12" s="7" t="n"/>
     </row>
@@ -3148,22 +3134,28 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1426.85</v>
+        <v>1375.49</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1645</v>
+        <v>1713.3</v>
       </c>
       <c r="G13" t="n">
         <v>4</v>
       </c>
+      <c r="H13" s="6" t="n">
+        <v>1755</v>
+      </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>218.15</v>
+        <v>337.81</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>379.51</v>
       </c>
     </row>
     <row r="14">
@@ -3178,13 +3170,13 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1343.11</v>
+        <v>1444.27</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>1596.67</v>
+        <v>1615</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>3</v>
@@ -3194,7 +3186,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>253.56</v>
+        <v>170.73</v>
       </c>
       <c r="K14" s="7" t="n"/>
     </row>
@@ -3210,28 +3202,22 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1429.53</v>
+        <v>1498.86</v>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1717.17</v>
+        <v>1741.67</v>
       </c>
       <c r="G15" t="n">
         <v>3</v>
       </c>
-      <c r="H15" s="6" t="n">
-        <v>1685</v>
-      </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>287.64</v>
-      </c>
-      <c r="K15" s="6" t="n">
-        <v>255.47</v>
+        <v>242.81</v>
       </c>
     </row>
     <row r="16">
@@ -3246,13 +3232,13 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1321.34</v>
+        <v>1359.86</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>1590</v>
+        <v>1564.36</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>4</v>
@@ -3262,7 +3248,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>268.66</v>
+        <v>204.5</v>
       </c>
       <c r="K16" s="7" t="n"/>
     </row>
@@ -3278,16 +3264,28 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>817.26</v>
+        <v>904.34</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
+      <c r="F17" s="6" t="n">
+        <v>998.12</v>
+      </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>1015</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>93.78</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>110.66</v>
       </c>
     </row>
     <row r="18">
@@ -3302,29 +3300,25 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>886.48</v>
+        <v>954.58</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>1080</v>
+        <v>1088.06</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>1055</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H18" s="7" t="n"/>
       <c r="I18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J18" s="8" t="n">
-        <v>193.52</v>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>168.52</v>
-      </c>
+        <v>133.48</v>
+      </c>
+      <c r="K18" s="7" t="n"/>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -3338,22 +3332,22 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>895.41</v>
+        <v>926.11</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1046.67</v>
+        <v>1129.82</v>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>151.26</v>
+        <v>203.71</v>
       </c>
     </row>
     <row r="20">
@@ -3368,20 +3362,24 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>877.54</v>
+        <v>931.13</v>
       </c>
       <c r="E20" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>1125.6</v>
+      </c>
+      <c r="G20" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="H20" s="7" t="n"/>
       <c r="I20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="J20" s="7" t="n"/>
+      <c r="J20" s="8" t="n">
+        <v>194.47</v>
+      </c>
       <c r="K20" s="7" t="n"/>
     </row>
     <row r="21">
@@ -3396,28 +3394,22 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>919.41</v>
+        <v>993.1</v>
       </c>
       <c r="E21" t="n">
         <v>4</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1112.5</v>
+        <v>1090</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>1075</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>193.09</v>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>155.59</v>
+        <v>0</v>
+      </c>
+      <c r="J21" s="15" t="n">
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3432,29 +3424,25 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>866.38</v>
+        <v>855.22</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>1045</v>
+        <v>1087.5</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>970</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H22" s="7" t="n"/>
       <c r="I22" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="8" t="n">
-        <v>178.62</v>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>103.62</v>
-      </c>
+        <v>232.28</v>
+      </c>
+      <c r="K22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
@@ -3468,16 +3456,28 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>710.08</v>
+        <v>730.17</v>
       </c>
       <c r="E23" t="n">
         <v>2</v>
       </c>
+      <c r="F23" s="6" t="n">
+        <v>885.85</v>
+      </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>905</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>155.68</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>174.83</v>
       </c>
     </row>
     <row r="24">
@@ -3492,25 +3492,25 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>803.86</v>
+        <v>793.8099999999999</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>957.5</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="F24" s="7" t="n"/>
       <c r="G24" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H24" s="7" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>925</v>
+      </c>
       <c r="I24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>153.64</v>
-      </c>
-      <c r="K24" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="J24" s="7" t="n"/>
+      <c r="K24" s="8" t="n">
+        <v>131.19</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
@@ -3524,28 +3524,22 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>788.23</v>
+        <v>826.1900000000001</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>938.33</v>
+        <v>993.73</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>925</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>150.1</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>136.77</v>
+        <v>167.54</v>
       </c>
     </row>
     <row r="26">
@@ -3560,29 +3554,25 @@
         </is>
       </c>
       <c r="D26" s="8" t="n">
-        <v>743.5700000000001</v>
+        <v>790.46</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>895</v>
+        <v>980</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="8" t="n">
-        <v>860</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H26" s="7" t="n"/>
       <c r="I26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J26" s="8" t="n">
-        <v>151.43</v>
-      </c>
-      <c r="K26" s="8" t="n">
-        <v>116.43</v>
-      </c>
+        <v>189.54</v>
+      </c>
+      <c r="K26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -3596,22 +3586,22 @@
         </is>
       </c>
       <c r="D27" s="6" t="n">
-        <v>790.46</v>
+        <v>857.45</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>963.33</v>
+        <v>955</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
-      <c r="J27" s="6" t="n">
-        <v>172.87</v>
+      <c r="J27" s="15" t="n">
+        <v>97.55</v>
       </c>
     </row>
     <row r="28">
@@ -3626,29 +3616,25 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>741.89</v>
+        <v>770.37</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>902.5</v>
+        <v>906.5700000000001</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H28" s="8" t="n">
-        <v>877.5</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="H28" s="7" t="n"/>
       <c r="I28" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J28" s="8" t="n">
-        <v>160.61</v>
-      </c>
-      <c r="K28" s="8" t="n">
-        <v>135.61</v>
-      </c>
+        <v>136.2</v>
+      </c>
+      <c r="K28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
@@ -3662,28 +3648,28 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>485</v>
+        <v>483.66</v>
       </c>
       <c r="E29" t="n">
         <v>5</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>565</v>
+        <v>561.08</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>545</v>
+        <v>572.5</v>
       </c>
       <c r="I29" t="n">
         <v>2</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>80</v>
+        <v>77.42</v>
       </c>
       <c r="K29" s="15" t="n">
-        <v>60</v>
+        <v>88.84</v>
       </c>
     </row>
     <row r="30">
@@ -3698,28 +3684,28 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>495.71</v>
+        <v>518.04</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>585</v>
+        <v>599.55</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>615</v>
+        <v>587.5</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="16" t="n">
-        <v>89.29000000000001</v>
-      </c>
-      <c r="K30" s="8" t="n">
-        <v>119.29</v>
+        <v>81.51000000000001</v>
+      </c>
+      <c r="K30" s="16" t="n">
+        <v>69.45999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -3734,28 +3720,28 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>527.53</v>
+        <v>515.8099999999999</v>
       </c>
       <c r="E31" t="n">
         <v>4</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>613.75</v>
+        <v>629.33</v>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>590</v>
+        <v>627.5</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="15" t="n">
-        <v>86.22</v>
-      </c>
-      <c r="K31" s="15" t="n">
-        <v>62.47</v>
+        <v>2</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>113.52</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>111.69</v>
       </c>
     </row>
     <row r="32">
@@ -3770,28 +3756,28 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>524.74</v>
+        <v>515.8099999999999</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>569.05</v>
+        <v>612.28</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>585</v>
+        <v>615</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J32" s="16" t="n">
-        <v>44.31</v>
+        <v>96.47</v>
       </c>
       <c r="K32" s="16" t="n">
-        <v>60.26</v>
+        <v>99.19</v>
       </c>
     </row>
     <row r="33">
@@ -3806,28 +3792,28 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>518.04</v>
+        <v>515.8099999999999</v>
       </c>
       <c r="E33" t="n">
         <v>3</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>611.53</v>
+        <v>622</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>610</v>
+        <v>647.5</v>
       </c>
       <c r="I33" t="n">
         <v>2</v>
       </c>
-      <c r="J33" s="15" t="n">
-        <v>93.48999999999999</v>
-      </c>
-      <c r="K33" s="15" t="n">
-        <v>91.95999999999999</v>
+      <c r="J33" s="6" t="n">
+        <v>106.19</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>131.69</v>
       </c>
     </row>
     <row r="34">
@@ -3842,29 +3828,25 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>462.22</v>
+        <v>497.05</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>551</v>
+        <v>581.92</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>580</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H34" s="7" t="n"/>
       <c r="I34" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="16" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="K34" s="8" t="n">
-        <v>117.78</v>
-      </c>
+        <v>84.87</v>
+      </c>
+      <c r="K34" s="7" t="n"/>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
@@ -3878,28 +3860,22 @@
         </is>
       </c>
       <c r="D35" s="6" t="n">
-        <v>360.06</v>
+        <v>377.37</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>416.25</v>
+        <v>463.33</v>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
-      </c>
-      <c r="H35" s="6" t="n">
-        <v>420</v>
+        <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>56.19</v>
-      </c>
-      <c r="K35" s="15" t="n">
-        <v>59.94</v>
+        <v>85.95999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3914,28 +3890,28 @@
         </is>
       </c>
       <c r="D36" s="8" t="n">
-        <v>378.49</v>
+        <v>405.28</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F36" s="8" t="n">
-        <v>472.5</v>
+        <v>497.94</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>443.33</v>
+        <v>450</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J36" s="16" t="n">
-        <v>94.01000000000001</v>
+        <v>92.66</v>
       </c>
       <c r="K36" s="16" t="n">
-        <v>64.84</v>
+        <v>44.72</v>
       </c>
     </row>
     <row r="37">
@@ -3950,28 +3926,28 @@
         </is>
       </c>
       <c r="D37" s="6" t="n">
-        <v>385.85</v>
+        <v>415.33</v>
       </c>
       <c r="E37" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>457.5</v>
+        <v>461.67</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>84.15000000000001</v>
+        <v>79.67</v>
       </c>
       <c r="K37" s="15" t="n">
-        <v>71.65000000000001</v>
+        <v>46.34</v>
       </c>
     </row>
     <row r="38">
@@ -3986,28 +3962,28 @@
         </is>
       </c>
       <c r="D38" s="8" t="n">
-        <v>390.77</v>
+        <v>404.16</v>
       </c>
       <c r="E38" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F38" s="8" t="n">
-        <v>463.06</v>
+        <v>461.25</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>4</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="I38" s="7" t="n">
         <v>2</v>
       </c>
       <c r="J38" s="16" t="n">
-        <v>72.29000000000001</v>
+        <v>57.09</v>
       </c>
       <c r="K38" s="16" t="n">
-        <v>54.23</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="39">
@@ -4022,28 +3998,28 @@
         </is>
       </c>
       <c r="D39" s="6" t="n">
-        <v>393</v>
+        <v>423.7</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>484.46</v>
+        <v>500</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>468.33</v>
+        <v>480</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J39" s="15" t="n">
-        <v>91.45999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="K39" s="15" t="n">
-        <v>75.33</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="40">
@@ -4058,28 +4034,28 @@
         </is>
       </c>
       <c r="D40" s="8" t="n">
-        <v>375.13</v>
+        <v>379.15</v>
       </c>
       <c r="E40" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>486.16</v>
+      </c>
+      <c r="G40" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="8" t="n">
-        <v>460</v>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="H40" s="8" t="n">
-        <v>425</v>
+        <v>457.5</v>
       </c>
       <c r="I40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="16" t="n">
-        <v>84.87</v>
+        <v>2</v>
+      </c>
+      <c r="J40" s="8" t="n">
+        <v>107.01</v>
       </c>
       <c r="K40" s="16" t="n">
-        <v>49.87</v>
+        <v>78.34999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -4094,28 +4070,28 @@
         </is>
       </c>
       <c r="D41" s="6" t="n">
-        <v>433.19</v>
+        <v>428.72</v>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>527.5</v>
+        <v>520.63</v>
       </c>
       <c r="G41" t="n">
+        <v>4</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>502.5</v>
+      </c>
+      <c r="I41" t="n">
         <v>2</v>
       </c>
-      <c r="H41" s="6" t="n">
-        <v>510</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1</v>
-      </c>
       <c r="J41" s="15" t="n">
-        <v>94.31</v>
+        <v>91.91</v>
       </c>
       <c r="K41" s="15" t="n">
-        <v>76.81</v>
+        <v>73.78</v>
       </c>
     </row>
     <row r="42">
@@ -4130,16 +4106,16 @@
         </is>
       </c>
       <c r="D42" s="8" t="n">
-        <v>462.22</v>
+        <v>457.75</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42" s="8" t="n">
-        <v>555</v>
+        <v>567.33</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H42" s="8" t="n">
         <v>535</v>
@@ -4147,11 +4123,11 @@
       <c r="I42" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="16" t="n">
-        <v>92.78</v>
+      <c r="J42" s="8" t="n">
+        <v>109.58</v>
       </c>
       <c r="K42" s="16" t="n">
-        <v>72.78</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="43">
@@ -4171,23 +4147,11 @@
       <c r="E43" t="n">
         <v>1</v>
       </c>
-      <c r="F43" s="6" t="n">
-        <v>595</v>
-      </c>
       <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="6" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>146.18</v>
-      </c>
-      <c r="K43" s="6" t="n">
-        <v>101.18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -4202,28 +4166,28 @@
         </is>
       </c>
       <c r="D44" s="8" t="n">
-        <v>455.52</v>
+        <v>442.12</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="8" t="n">
-        <v>562.7</v>
+        <v>575</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>530</v>
+        <v>545</v>
       </c>
       <c r="I44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="J44" s="8" t="n">
-        <v>107.18</v>
-      </c>
-      <c r="K44" s="16" t="n">
-        <v>74.48</v>
+        <v>132.88</v>
+      </c>
+      <c r="K44" s="8" t="n">
+        <v>102.88</v>
       </c>
     </row>
     <row r="45">
@@ -4238,22 +4202,28 @@
         </is>
       </c>
       <c r="D45" s="6" t="n">
-        <v>455.52</v>
+        <v>499.06</v>
       </c>
       <c r="E45" t="n">
         <v>2</v>
       </c>
+      <c r="F45" s="6" t="n">
+        <v>545</v>
+      </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>547.5</v>
+        <v>566.67</v>
       </c>
       <c r="I45" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="J45" s="15" t="n">
+        <v>45.94</v>
       </c>
       <c r="K45" s="15" t="n">
-        <v>91.98</v>
+        <v>67.61</v>
       </c>
     </row>
     <row r="46">
@@ -4267,30 +4237,22 @@
           <t>M6</t>
         </is>
       </c>
-      <c r="D46" s="8" t="n">
-        <v>462.22</v>
-      </c>
+      <c r="D46" s="7" t="n"/>
       <c r="E46" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="8" t="n">
-        <v>505</v>
+        <v>520</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="8" t="n">
-        <v>490</v>
-      </c>
+      <c r="H46" s="7" t="n"/>
       <c r="I46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="16" t="n">
-        <v>42.78</v>
-      </c>
-      <c r="K46" s="16" t="n">
-        <v>27.78</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J46" s="7" t="n"/>
+      <c r="K46" s="7" t="n"/>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
@@ -4304,23 +4266,17 @@
         </is>
       </c>
       <c r="D47" s="6" t="n">
-        <v>251.88</v>
+        <v>274.65</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="6" t="n">
-        <v>310</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
-      <c r="J47" s="15" t="n">
-        <v>58.12</v>
-      </c>
     </row>
     <row r="48">
       <c r="B48" s="7" t="inlineStr">
@@ -4333,20 +4289,26 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="D48" s="7" t="n"/>
+      <c r="D48" s="8" t="n">
+        <v>314.84</v>
+      </c>
       <c r="E48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="7" t="n"/>
       <c r="G48" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="7" t="n"/>
+      <c r="H48" s="8" t="n">
+        <v>365</v>
+      </c>
       <c r="I48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="7" t="n"/>
-      <c r="K48" s="7" t="n"/>
+      <c r="K48" s="16" t="n">
+        <v>50.16</v>
+      </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
@@ -4359,11 +4321,8 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="D49" s="6" t="n">
-        <v>281.35</v>
-      </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -4383,26 +4342,20 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="D50" s="8" t="n">
-        <v>291.4</v>
-      </c>
+      <c r="D50" s="7" t="n"/>
       <c r="E50" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F50" s="7" t="n"/>
       <c r="G50" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="8" t="n">
-        <v>330</v>
-      </c>
+      <c r="H50" s="7" t="n"/>
       <c r="I50" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="7" t="n"/>
-      <c r="K50" s="16" t="n">
-        <v>38.6</v>
-      </c>
+      <c r="K50" s="7" t="n"/>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
@@ -4418,8 +4371,11 @@
       <c r="E51" t="n">
         <v>0</v>
       </c>
+      <c r="F51" s="6" t="n">
+        <v>345</v>
+      </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -4440,11 +4396,9 @@
       <c r="E52" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F52" s="8" t="n">
-        <v>340</v>
-      </c>
+      <c r="F52" s="7" t="n"/>
       <c r="G52" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" s="7" t="n"/>
       <c r="I52" s="7" t="n">
@@ -4464,18 +4418,24 @@
           <t>M1</t>
         </is>
       </c>
+      <c r="D53" s="6" t="n">
+        <v>223.29</v>
+      </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>246.67</v>
+        <v>257.5</v>
       </c>
       <c r="G53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
+      <c r="J53" s="15" t="n">
+        <v>34.21</v>
+      </c>
     </row>
     <row r="54">
       <c r="B54" s="7" t="inlineStr">
@@ -4489,24 +4449,24 @@
         </is>
       </c>
       <c r="D54" s="8" t="n">
-        <v>219.72</v>
+        <v>251.88</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="7" t="n"/>
       <c r="G54" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>265</v>
+        <v>287.5</v>
       </c>
       <c r="I54" s="7" t="n">
         <v>2</v>
       </c>
       <c r="J54" s="7" t="n"/>
       <c r="K54" s="16" t="n">
-        <v>45.28</v>
+        <v>35.62</v>
       </c>
     </row>
     <row r="55">
@@ -4520,23 +4480,14 @@
           <t>M3</t>
         </is>
       </c>
-      <c r="D55" s="6" t="n">
-        <v>241.16</v>
-      </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="6" t="n">
-        <v>270</v>
-      </c>
       <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" s="15" t="n">
-        <v>28.84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -4554,17 +4505,13 @@
       <c r="E56" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F56" s="8" t="n">
-        <v>279.35</v>
-      </c>
+      <c r="F56" s="7" t="n"/>
       <c r="G56" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" s="8" t="n">
-        <v>275</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H56" s="7" t="n"/>
       <c r="I56" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="7" t="n"/>
       <c r="K56" s="7" t="n"/>
@@ -4580,23 +4527,17 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="D57" s="6" t="n">
-        <v>241.16</v>
-      </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="I57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" s="15" t="n">
-        <v>28.84</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
@@ -4611,24 +4552,24 @@
         </is>
       </c>
       <c r="D58" s="8" t="n">
-        <v>235.8</v>
+        <v>225.08</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="7" t="n"/>
       <c r="G58" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>260</v>
+        <v>271.67</v>
       </c>
       <c r="I58" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J58" s="7" t="n"/>
       <c r="K58" s="16" t="n">
-        <v>24.2</v>
+        <v>46.59</v>
       </c>
     </row>
     <row r="59">
@@ -4642,17 +4583,17 @@
           <t>M1</t>
         </is>
       </c>
-      <c r="D59" s="6" t="n">
-        <v>182.21</v>
-      </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
+      <c r="H59" s="6" t="n">
+        <v>235</v>
+      </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -4666,22 +4607,30 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="D60" s="7" t="n"/>
+      <c r="D60" s="8" t="n">
+        <v>206.32</v>
+      </c>
       <c r="E60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="F60" s="8" t="n">
+        <v>254.56</v>
+      </c>
       <c r="G60" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="I60" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="J60" s="7" t="n"/>
-      <c r="K60" s="7" t="n"/>
+      <c r="J60" s="16" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="K60" s="16" t="n">
+        <v>38.68</v>
+      </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
@@ -4694,15 +4643,24 @@
           <t>M3</t>
         </is>
       </c>
+      <c r="D61" s="6" t="n">
+        <v>206.32</v>
+      </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>250</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
+      <c r="J61" s="15" t="n">
+        <v>43.68</v>
+      </c>
     </row>
     <row r="62">
       <c r="B62" s="7" t="inlineStr">
@@ -4716,25 +4674,25 @@
         </is>
       </c>
       <c r="D62" s="8" t="n">
-        <v>184.89</v>
+        <v>208.11</v>
       </c>
       <c r="E62" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" s="7" t="n"/>
+      <c r="G62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>240</v>
+      </c>
+      <c r="I62" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F62" s="8" t="n">
-        <v>230</v>
-      </c>
-      <c r="G62" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="7" t="n"/>
-      <c r="I62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="16" t="n">
-        <v>45.11</v>
-      </c>
-      <c r="K62" s="7" t="n"/>
+      <c r="J62" s="7" t="n"/>
+      <c r="K62" s="16" t="n">
+        <v>31.89</v>
+      </c>
     </row>
     <row r="63">
       <c r="B63" t="inlineStr">
@@ -4768,11 +4726,9 @@
           <t>M6</t>
         </is>
       </c>
-      <c r="D64" s="8" t="n">
-        <v>171.49</v>
-      </c>
+      <c r="D64" s="7" t="n"/>
       <c r="E64" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" s="7" t="n"/>
       <c r="G64" s="7" t="n">
@@ -4878,22 +4834,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>M1; M2; M3; M4; M5</t>
+          <t>M1; M2; M3; M4; M5; M6</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M1=4; M2=4; M3=5; M4=4; M5=4</t>
+          <t>M1=5; M2=4; M3=3; M4=5; M5=4; M6=3</t>
         </is>
       </c>
       <c r="G5" s="15" t="n">
-        <v>10.721</v>
+        <v>14.354</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="15" t="n">
-        <v>0.0299</v>
+        <v>0.0135</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -4919,26 +4875,26 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>M1; M2; M3; M4; M5; M6</t>
+          <t>M2; M3; M4; M5; M6</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>M1=5; M2=3; M3=4; M4=3; M5=3; M6=4</t>
+          <t>M2=3; M3=4; M4=3; M5=3; M6=4</t>
         </is>
       </c>
       <c r="G6" s="16" t="n">
-        <v>11.163</v>
+        <v>9.208</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I6" s="16" t="n">
-        <v>0.0482</v>
+        <v>0.0561</v>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
-          <t>reject H0 (p&lt;0.05): prices differ across markets</t>
+          <t>fail to reject H0 (p&gt;=0.05)</t>
         </is>
       </c>
     </row>
@@ -4960,26 +4916,26 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>M3; M5; M6</t>
+          <t>M2; M3; M4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>M3=3; M5=4; M6=5</t>
+          <t>M2=4; M3=5; M4=3</t>
         </is>
       </c>
       <c r="G7" s="15" t="n">
-        <v>6.121</v>
+        <v>2.402</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>2</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>0.0469</v>
+        <v>0.301</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>reject H0 (p&lt;0.05): prices differ across markets</t>
+          <t>fail to reject H0 (p&gt;=0.05)</t>
         </is>
       </c>
     </row>
@@ -5001,26 +4957,26 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>M2; M3; M5; M6</t>
+          <t>M1; M3; M6</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>M2=4; M3=3; M5=3; M6=4</t>
+          <t>M1=3; M3=4; M6=5</t>
         </is>
       </c>
       <c r="G8" s="16" t="n">
-        <v>7.741</v>
+        <v>7.887</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I8" s="16" t="n">
-        <v>0.0517</v>
+        <v>0.0194</v>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>fail to reject H0 (p&gt;=0.05)</t>
+          <t>reject H0 (p&lt;0.05): prices differ across markets</t>
         </is>
       </c>
     </row>
@@ -5042,22 +4998,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>M2; M3; M4; M5; M6</t>
+          <t>M1; M3; M4; M5; M6</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>M2=3; M3=4; M4=4; M5=3; M6=5</t>
+          <t>M1=4; M3=3; M4=5; M5=5; M6=4</t>
         </is>
       </c>
       <c r="G9" s="15" t="n">
-        <v>12.2</v>
+        <v>11.931</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>4</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>0.0159</v>
+        <v>0.0179</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -5083,22 +5039,22 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>M1; M3; M4</t>
+          <t>M1; M2; M4; M5</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>M1=4; M3=4; M4=4</t>
+          <t>M1=3; M2=3; M4=4; M5=5</t>
         </is>
       </c>
       <c r="G10" s="16" t="n">
-        <v>6.885</v>
+        <v>9.598000000000001</v>
       </c>
       <c r="H10" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" s="16" t="n">
-        <v>0.032</v>
+        <v>0.0223</v>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
@@ -5219,7 +5175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H45"/>
+  <dimension ref="B2:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -5285,13 +5241,13 @@
         </is>
       </c>
       <c r="D5" s="15" t="n">
-        <v>-3.252</v>
+        <v>-3.437</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.0011</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.0115</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -5305,22 +5261,22 @@
     <row r="6">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>-1.937</v>
+        <v>2.716</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0.0528</v>
+        <v>0.0066</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>0.4752</v>
+        <v>0.0924</v>
       </c>
       <c r="G6" s="7" t="b">
         <v>0</v>
@@ -5334,22 +5290,22 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
       <c r="D7" s="15" t="n">
-        <v>-1.769</v>
+        <v>-1.987</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>0.0769</v>
+        <v>0.0469</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.6156</v>
+        <v>0.6094000000000001</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -5372,13 +5328,13 @@
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>-1.655</v>
+        <v>-1.789</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>0.098</v>
+        <v>0.0736</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.6861</v>
+        <v>0.8829</v>
       </c>
       <c r="G8" s="7" t="b">
         <v>0</v>
@@ -5392,22 +5348,22 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>-1.598</v>
+        <v>-1.769</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>0.1101</v>
+        <v>0.0769</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.6861</v>
+        <v>0.8829</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -5421,7 +5377,7 @@
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -5430,13 +5386,13 @@
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>-1.491</v>
+        <v>-1.75</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>0.1358</v>
+        <v>0.0801</v>
       </c>
       <c r="F10" s="16" t="n">
-        <v>0.6861</v>
+        <v>0.8829</v>
       </c>
       <c r="G10" s="7" t="b">
         <v>0</v>
@@ -5450,22 +5406,22 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>-1.483</v>
+        <v>1.443</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>0.138</v>
+        <v>0.149</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0.6861</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -5484,14 +5440,14 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>-0.373</v>
+        <v>-1.375</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.169</v>
       </c>
       <c r="F12" s="16" t="n">
         <v>1</v>
@@ -5513,14 +5469,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>0.192</v>
+        <v>-1.327</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>0.8474</v>
+        <v>0.1844</v>
       </c>
       <c r="F13" s="15" t="n">
         <v>1</v>
@@ -5537,19 +5493,19 @@
     <row r="14">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>-0.171</v>
+        <v>1.299</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0.8641</v>
+        <v>0.1938</v>
       </c>
       <c r="F14" s="16" t="n">
         <v>1</v>
@@ -5566,36 +5522,36 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>-2.828</v>
+        <v>1.233</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>0.0047</v>
+        <v>0.2175</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0.0702</v>
+        <v>1</v>
       </c>
       <c r="G15" t="b">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -5604,20 +5560,20 @@
         </is>
       </c>
       <c r="D16" s="16" t="n">
-        <v>2.548</v>
+        <v>-0.316</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>0.0108</v>
+        <v>0.7517</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.1518</v>
+        <v>1</v>
       </c>
       <c r="G16" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
     </row>
@@ -5629,60 +5585,60 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>-2.171</v>
+        <v>0.3</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>0.0299</v>
+        <v>0.7638</v>
       </c>
       <c r="F17" s="15" t="n">
-        <v>0.3893</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="7" t="inlineStr">
         <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
       <c r="D18" s="16" t="n">
-        <v>-2.171</v>
+        <v>0.22</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>0.0299</v>
+        <v>0.8262</v>
       </c>
       <c r="F18" s="16" t="n">
-        <v>0.3893</v>
+        <v>1</v>
       </c>
       <c r="G18" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5691,136 +5647,136 @@
         </is>
       </c>
       <c r="D19" s="15" t="n">
-        <v>-1.786</v>
+        <v>0.054</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>0.074</v>
+        <v>0.9569</v>
       </c>
       <c r="F19" s="15" t="n">
-        <v>0.8144</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="7" t="inlineStr">
         <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
       <c r="D20" s="16" t="n">
-        <v>1.526</v>
+        <v>-2.602</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>0.1271</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="F20" s="16" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="G20" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="G20" s="7" t="b">
-        <v>0</v>
-      </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S04</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>-1.186</v>
+        <v>2.191</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>0.2358</v>
+        <v>0.0284</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>1</v>
+        <v>0.0569</v>
       </c>
       <c r="G21" t="b">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S04</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D22" s="16" t="n">
-        <v>1.186</v>
+        <v>-0.709</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>0.2358</v>
+        <v>0.4784</v>
       </c>
       <c r="F22" s="16" t="n">
-        <v>1</v>
+        <v>0.4784</v>
       </c>
       <c r="G22" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S04</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>M3</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
       <c r="D23" s="15" t="n">
-        <v>-1.135</v>
+        <v>-2.682</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>0.2563</v>
+        <v>0.0073</v>
       </c>
       <c r="F23" s="15" t="n">
-        <v>1</v>
+        <v>0.0731</v>
       </c>
       <c r="G23" t="b">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
@@ -5832,24 +5788,24 @@
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="D24" s="16" t="n">
-        <v>-0.401</v>
+        <v>-2.604</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>0.6884</v>
+        <v>0.0092</v>
       </c>
       <c r="F24" s="16" t="n">
-        <v>1</v>
+        <v>0.0829</v>
       </c>
       <c r="G24" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
@@ -5861,31 +5817,31 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D25" s="15" t="n">
-        <v>-0.401</v>
+        <v>-2.459</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.6884</v>
+        <v>0.0139</v>
       </c>
       <c r="F25" s="15" t="n">
-        <v>1</v>
+        <v>0.1114</v>
       </c>
       <c r="G25" t="b">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
@@ -5894,20 +5850,20 @@
         </is>
       </c>
       <c r="D26" s="16" t="n">
-        <v>0.227</v>
+        <v>1.915</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>0.8204</v>
+        <v>0.0555</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>1</v>
+        <v>0.3887</v>
       </c>
       <c r="G26" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
@@ -5923,27 +5879,27 @@
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>0.227</v>
+        <v>1.73</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>0.8204</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>1</v>
+        <v>0.5018</v>
       </c>
       <c r="G27" t="b">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -5952,39 +5908,39 @@
         </is>
       </c>
       <c r="D28" s="16" t="n">
-        <v>-0.178</v>
+        <v>1.585</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>0.8587</v>
+        <v>0.1129</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>1</v>
+        <v>0.5645</v>
       </c>
       <c r="G28" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M6</t>
         </is>
       </c>
       <c r="D29" s="15" t="n">
-        <v>0</v>
+        <v>-0.829</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>1</v>
+        <v>0.407</v>
       </c>
       <c r="F29" s="15" t="n">
         <v>1</v>
@@ -5994,36 +5950,36 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>S02</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="7" t="inlineStr">
         <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
           <t>M5</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
       <c r="D30" s="16" t="n">
-        <v>2.209</v>
+        <v>0.546</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>0.0271</v>
+        <v>0.5849</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>0.0814</v>
+        <v>1</v>
       </c>
       <c r="G30" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
@@ -6035,198 +5991,198 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="D31" s="15" t="n">
-        <v>-2.05</v>
+        <v>0.413</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>0.0404</v>
+        <v>0.6793</v>
       </c>
       <c r="F31" s="15" t="n">
-        <v>0.0814</v>
+        <v>1</v>
       </c>
       <c r="G31" t="b">
         <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D32" s="16" t="n">
-        <v>-0.114</v>
+        <v>0.153</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>0.909</v>
+        <v>0.878</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>0.909</v>
+        <v>1</v>
       </c>
       <c r="G32" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>S03</t>
+          <t>S05</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D33" s="15" t="n">
-        <v>2.883</v>
+        <v>-2.593</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>0.0039</v>
+        <v>0.0095</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>0.0394</v>
+        <v>0.0572</v>
       </c>
       <c r="G33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S06</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="D34" s="16" t="n">
-        <v>2.669</v>
+        <v>2.13</v>
       </c>
       <c r="E34" s="16" t="n">
-        <v>0.0076</v>
+        <v>0.0332</v>
       </c>
       <c r="F34" s="16" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.1658</v>
       </c>
       <c r="G34" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S06</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D35" s="15" t="n">
-        <v>2.017</v>
+        <v>-2.049</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>0.0437</v>
+        <v>0.0405</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>0.3498</v>
+        <v>0.1658</v>
       </c>
       <c r="G35" t="b">
         <v>0</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S06</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="D36" s="16" t="n">
-        <v>-1.887</v>
+        <v>-1.695</v>
       </c>
       <c r="E36" s="16" t="n">
-        <v>0.0592</v>
+        <v>0.0901</v>
       </c>
       <c r="F36" s="16" t="n">
-        <v>0.4145</v>
+        <v>0.2703</v>
       </c>
       <c r="G36" s="7" t="b">
         <v>0</v>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S06</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>M4</t>
         </is>
       </c>
       <c r="D37" s="15" t="n">
-        <v>1.53</v>
+        <v>0.318</v>
       </c>
       <c r="E37" s="15" t="n">
-        <v>0.1261</v>
+        <v>0.7503</v>
       </c>
       <c r="F37" s="15" t="n">
-        <v>0.7567</v>
+        <v>1</v>
       </c>
       <c r="G37" t="b">
         <v>0</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>S05</t>
+          <t>S06</t>
         </is>
       </c>
     </row>
@@ -6238,14 +6194,14 @@
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M5</t>
         </is>
       </c>
       <c r="D38" s="16" t="n">
-        <v>-1.07</v>
+        <v>-0.154</v>
       </c>
       <c r="E38" s="16" t="n">
-        <v>0.2848</v>
+        <v>0.8779</v>
       </c>
       <c r="F38" s="16" t="n">
         <v>1</v>
@@ -6254,209 +6210,6 @@
         <v>0</v>
       </c>
       <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>-1.019</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.3083</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>0.4252</v>
-      </c>
-      <c r="F40" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="D41" s="15" t="n">
-        <v>0.757</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>0.4489</v>
-      </c>
-      <c r="F41" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="n">
-        <v>-0.019</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>0.9845</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>S05</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="n">
-        <v>-2.509</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0.0121</v>
-      </c>
-      <c r="F43" s="15" t="n">
-        <v>0.0363</v>
-      </c>
-      <c r="G43" t="b">
-        <v>1</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>S06</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="n">
-        <v>-1.919</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="F44" s="16" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G44" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>S06</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="D45" s="15" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0.5548999999999999</v>
-      </c>
-      <c r="F45" s="15" t="n">
-        <v>0.5548999999999999</v>
-      </c>
-      <c r="G45" t="b">
-        <v>0</v>
-      </c>
-      <c r="H45" t="inlineStr">
         <is>
           <t>S06</t>
         </is>
@@ -6532,16 +6285,16 @@
         <v>30</v>
       </c>
       <c r="D5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E5" t="n">
         <v>12</v>
       </c>
-      <c r="E5" t="n">
-        <v>13</v>
-      </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>40</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="6">
@@ -6554,16 +6307,16 @@
         <v>30</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>43.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -6576,16 +6329,16 @@
         <v>30</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
         <v>3</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>36.7</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="8">
@@ -6602,7 +6355,7 @@
       <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>chi2=1.22, df=4, p=0.8749, G-test p=0.8809, Fisher-exact p=0.8945</t>
+          <t>chi2=2.49, df=4, p=0.6472, G-test p=0.6349, Fisher-exact p=0.6603</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6371,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>V=0.082 / min exp=3.67</t>
+          <t>V=0.118 / min exp=4.00</t>
         </is>
       </c>
     </row>
@@ -6730,31 +6483,31 @@
         <v>30</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>44.13</v>
+        <v>47.1</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>10.52</v>
+        <v>9.49</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>18.73</v>
+        <v>20.63</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>8.609999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>6.13</v>
+        <v>5.9</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>23.3</v>
+        <v>13.3</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>23.3</v>
+        <v>36.7</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>26.7</v>
+        <v>43.3</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>26.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="6">
@@ -6764,34 +6517,34 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>40.1</v>
+        <v>39.82</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>9.73</v>
+        <v>11.4</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>15.85</v>
+        <v>16.23</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>9.4</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>4.65</v>
+        <v>4.73</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>0</v>
+        <v>13.6</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>65</v>
+        <v>36.4</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>30</v>
+        <v>40.9</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="7">
@@ -6801,34 +6554,34 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>40.4</v>
+        <v>45.38</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>12.19</v>
+        <v>9.24</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>17.9</v>
+        <v>16.38</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>10.44</v>
+        <v>5.76</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>4.3</v>
+        <v>4.62</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>50</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6841,28 +6594,28 @@
         <v>30</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>38.77</v>
+        <v>38.63</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>11.31</v>
+        <v>10.01</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>12.77</v>
+        <v>11.43</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>7.95</v>
+        <v>7.43</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>4.7</v>
+        <v>5.43</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>23.3</v>
+        <v>36.7</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>43.3</v>
+        <v>36.7</v>
       </c>
       <c r="L8" s="8" t="n">
         <v>10</v>
@@ -6878,31 +6631,31 @@
         <v>90</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>41.03</v>
+        <v>42.34</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>10.87</v>
+        <v>10.68</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>16.01</v>
+        <v>16.11</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>9.01</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>5.12</v>
+        <v>5.34</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>33.3</v>
+        <v>37.8</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>35.6</v>
+        <v>41.1</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>14.4</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -6973,13 +6726,13 @@
         <v>30</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>30.14</v>
+        <v>33.5</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>9.630000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>30.62</v>
+        <v>33.65</v>
       </c>
     </row>
     <row r="6">
@@ -6992,13 +6745,13 @@
         <v>30</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>83.73999999999999</v>
+        <v>81.22</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>20.26</v>
+        <v>30.21</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>84.06999999999999</v>
+        <v>83.23999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -7011,13 +6764,13 @@
         <v>30</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>182</v>
+        <v>172.5</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>45.88</v>
+        <v>62.23</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>176.02</v>
+        <v>175.02</v>
       </c>
     </row>
     <row r="8">
@@ -7035,7 +6788,7 @@
       <c r="E8" s="7" t="inlineStr"/>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>U=0, p&lt;0.0001</t>
+          <t>U=8, p&lt;0.0001</t>
         </is>
       </c>
     </row>
@@ -7073,7 +6826,7 @@
       <c r="E10" s="7" t="inlineStr"/>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>U=10, p&lt;0.0001</t>
+          <t>U=35, p&lt;0.0001</t>
         </is>
       </c>
     </row>
@@ -7144,13 +6897,13 @@
         </is>
       </c>
       <c r="D5" s="6" t="n">
-        <v>200</v>
+        <v>127</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>4.42</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>195.58</v>
+        <v>118.38</v>
       </c>
     </row>
     <row r="6">
@@ -7165,13 +6918,13 @@
         </is>
       </c>
       <c r="D6" s="8" t="n">
-        <v>218.75</v>
+        <v>128</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>8</v>
+        <v>2.6</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>210.75</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="7">
@@ -7186,13 +6939,13 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>148.33</v>
+        <v>173.75</v>
       </c>
       <c r="E7" s="15" t="n">
-        <v>5.82</v>
+        <v>12.67</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>142.51</v>
+        <v>161.08</v>
       </c>
     </row>
     <row r="8">
@@ -7207,13 +6960,13 @@
         </is>
       </c>
       <c r="D8" s="8" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>5.06</v>
+        <v>4.62</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>169.94</v>
+        <v>179.38</v>
       </c>
     </row>
     <row r="9">
@@ -7228,13 +6981,13 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>158.75</v>
+        <v>148.71</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>2.94</v>
+        <v>5.31</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>155.81</v>
+        <v>143.41</v>
       </c>
     </row>
     <row r="10">
@@ -7249,13 +7002,13 @@
         </is>
       </c>
       <c r="D10" s="8" t="n">
-        <v>198.33</v>
+        <v>248.33</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>8.470000000000001</v>
+        <v>10.49</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>189.86</v>
+        <v>237.84</v>
       </c>
     </row>
     <row r="11">
@@ -7269,14 +7022,14 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
-        <v>115</v>
+      <c r="D11" s="15" t="n">
+        <v>74.69</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>111.33</v>
+        <v>3.25</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>71.44</v>
       </c>
     </row>
     <row r="12">
@@ -7291,13 +7044,13 @@
         </is>
       </c>
       <c r="D12" s="8" t="n">
-        <v>184</v>
+        <v>144.69</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>8.5</v>
+        <v>5.95</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>175.5</v>
+        <v>138.74</v>
       </c>
     </row>
     <row r="13">
@@ -7312,13 +7065,13 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>160</v>
+        <v>221.06</v>
       </c>
       <c r="E13" s="15" t="n">
-        <v>3.62</v>
+        <v>4.93</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>156.38</v>
+        <v>216.14</v>
       </c>
     </row>
     <row r="14">
@@ -7333,13 +7086,13 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>197.5</v>
+        <v>246.18</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>4.12</v>
+        <v>5.56</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>193.38</v>
+        <v>240.62</v>
       </c>
     </row>
     <row r="15">
@@ -7354,13 +7107,13 @@
         </is>
       </c>
       <c r="D15" s="6" t="n">
-        <v>205</v>
+        <v>107.5</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>5.38</v>
+        <v>2.47</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>199.62</v>
+        <v>105.03</v>
       </c>
     </row>
     <row r="16">
@@ -7375,13 +7128,13 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>154</v>
+        <v>207.67</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>4.24</v>
+        <v>5.69</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>149.76</v>
+        <v>201.97</v>
       </c>
     </row>
     <row r="17">
@@ -7396,13 +7149,13 @@
         </is>
       </c>
       <c r="D17" s="6" t="n">
-        <v>201</v>
+        <v>208.75</v>
       </c>
       <c r="E17" s="15" t="n">
-        <v>3.4</v>
+        <v>3.81</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>197.6</v>
+        <v>204.94</v>
       </c>
     </row>
     <row r="18">
@@ -7417,13 +7170,13 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>192.5</v>
+        <v>306.67</v>
       </c>
       <c r="E18" s="16" t="n">
-        <v>4.23</v>
+        <v>3.63</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>188.27</v>
+        <v>303.04</v>
       </c>
     </row>
     <row r="19">
@@ -7438,13 +7191,13 @@
         </is>
       </c>
       <c r="D19" s="6" t="n">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>6.07</v>
+        <v>2.99</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>177.93</v>
+        <v>210.01</v>
       </c>
     </row>
     <row r="20">
@@ -7459,13 +7212,13 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>132.5</v>
+        <v>180.87</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>3.16</v>
+        <v>9.01</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>129.34</v>
+        <v>171.86</v>
       </c>
     </row>
     <row r="21">
@@ -7480,13 +7233,13 @@
         </is>
       </c>
       <c r="D21" s="6" t="n">
-        <v>133.33</v>
+        <v>204</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>3.02</v>
+        <v>6</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>130.31</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22">
@@ -7501,13 +7254,13 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="E22" s="16" t="n">
-        <v>4.13</v>
+        <v>2.88</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>174.87</v>
+        <v>143.12</v>
       </c>
     </row>
     <row r="23">
@@ -7522,13 +7275,13 @@
         </is>
       </c>
       <c r="D23" s="6" t="n">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>5.1</v>
+        <v>11.81</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>145.9</v>
+        <v>143.19</v>
       </c>
     </row>
     <row r="24">
@@ -7542,14 +7295,14 @@
           <t>M4</t>
         </is>
       </c>
-      <c r="D24" s="16" t="n">
-        <v>96.47</v>
+      <c r="D24" s="8" t="n">
+        <v>208</v>
       </c>
       <c r="E24" s="16" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>91.8</v>
+        <v>3.16</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>204.84</v>
       </c>
     </row>
     <row r="25">
@@ -7564,13 +7317,13 @@
         </is>
       </c>
       <c r="D25" s="6" t="n">
-        <v>188.33</v>
+        <v>140</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>5.54</v>
+        <v>3.44</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>182.79</v>
+        <v>136.56</v>
       </c>
     </row>
     <row r="26">
@@ -7588,10 +7341,10 @@
         <v>171.25</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>4.71</v>
+        <v>7.86</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>166.54</v>
+        <v>163.39</v>
       </c>
     </row>
     <row r="27">
@@ -7605,14 +7358,14 @@
           <t>M5</t>
         </is>
       </c>
-      <c r="D27" s="6" t="n">
-        <v>202</v>
+      <c r="D27" s="15" t="n">
+        <v>98.75</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="F27" s="6" t="n">
-        <v>197.63</v>
+        <v>8.119999999999999</v>
+      </c>
+      <c r="F27" s="15" t="n">
+        <v>90.62</v>
       </c>
     </row>
     <row r="28">
@@ -7627,13 +7380,13 @@
         </is>
       </c>
       <c r="D28" s="8" t="n">
-        <v>202.5</v>
+        <v>199</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>7.29</v>
+        <v>8.91</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>195.21</v>
+        <v>190.09</v>
       </c>
     </row>
     <row r="29">
@@ -7648,13 +7401,13 @@
         </is>
       </c>
       <c r="D29" s="6" t="n">
-        <v>241.16</v>
+        <v>189</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>6.01</v>
+        <v>3.57</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>235.15</v>
+        <v>185.43</v>
       </c>
     </row>
     <row r="30">
@@ -7669,13 +7422,13 @@
         </is>
       </c>
       <c r="D30" s="8" t="n">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>5.48</v>
+        <v>5.45</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>174.52</v>
+        <v>200.55</v>
       </c>
     </row>
     <row r="31">
@@ -7690,13 +7443,13 @@
         </is>
       </c>
       <c r="D31" s="6" t="n">
-        <v>142</v>
+        <v>159.43</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>4.06</v>
+        <v>3.35</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>137.94</v>
+        <v>156.08</v>
       </c>
     </row>
     <row r="32">
@@ -7711,13 +7464,13 @@
         </is>
       </c>
       <c r="D32" s="8" t="n">
-        <v>157.5</v>
+        <v>165</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>3.2</v>
+        <v>2.28</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>154.3</v>
+        <v>162.72</v>
       </c>
     </row>
     <row r="33">
@@ -7732,13 +7485,13 @@
         </is>
       </c>
       <c r="D33" s="6" t="n">
-        <v>201.25</v>
+        <v>133.33</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>4.49</v>
+        <v>10.45</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>196.76</v>
+        <v>122.88</v>
       </c>
     </row>
     <row r="34">
@@ -7753,13 +7506,13 @@
         </is>
       </c>
       <c r="D34" s="8" t="n">
-        <v>210</v>
+        <v>155</v>
       </c>
       <c r="E34" s="16" t="n">
-        <v>4.85</v>
+        <v>4.52</v>
       </c>
       <c r="F34" s="8" t="n">
-        <v>205.15</v>
+        <v>150.48</v>
       </c>
     </row>
     <row r="35">
@@ -7775,10 +7528,10 @@
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="15" t="n">
-        <v>0.43</v>
+        <v>0.055</v>
       </c>
       <c r="F35" s="15" t="n">
-        <v>0.0177</v>
+        <v>0.773</v>
       </c>
     </row>
   </sheetData>
@@ -7843,13 +7596,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>0.8544</v>
+        <v>0.9035</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -7864,13 +7617,13 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>0.8457</v>
+        <v>0.9046</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>0</v>
+        <v>0.0008</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -7885,10 +7638,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>0.9076</v>
+        <v>0.8959</v>
       </c>
       <c r="E7" s="15" t="n">
         <v>0</v>
@@ -7906,10 +7659,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.8951</v>
       </c>
       <c r="E8" s="16" t="n">
         <v>0</v>
@@ -7927,10 +7680,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.8333</v>
+        <v>0.8123</v>
       </c>
       <c r="E9" s="15" t="n">
         <v>0</v>
@@ -8055,25 +7808,25 @@
         <v>30</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>797.4</v>
+        <v>801.14</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>272.75</v>
+        <v>328.39</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>821</v>
+        <v>839.7</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>373.2</v>
+        <v>298.6</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1306.2</v>
+        <v>1268.9</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>5.37</v>
+        <v>5.47</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>636.67</v>
+        <v>673.33</v>
       </c>
     </row>
     <row r="6">
@@ -8086,27 +7839,27 @@
         <v>30</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>204.51</v>
+        <v>205.26</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>107.05</v>
+        <v>103.06</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>186.6</v>
+        <v>167.9</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>44.8</v>
+        <v>48.5</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>410.5</v>
+        <v>447.8</v>
       </c>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
       <c r="K6" s="8" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>79.97</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="M6" s="7" t="n"/>
     </row>
@@ -8120,22 +7873,22 @@
         <v>30</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>99.95</v>
+        <v>95.94</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>27.47</v>
+        <v>35.07</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>103.5</v>
+        <v>102.6</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>5.43</v>
+        <v>5.53</v>
       </c>
     </row>
   </sheetData>
@@ -8220,10 +7973,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>66.7</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="6">
@@ -8243,10 +7996,10 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>33.3</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="7">
@@ -8266,10 +8019,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>83.3</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="8">
@@ -8289,10 +8042,10 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>16.7</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="9">
@@ -8312,10 +8065,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>43.3</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="10">
@@ -8335,10 +8088,10 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>40</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="11">
@@ -8358,10 +8111,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="12">
@@ -8372,19 +8125,19 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Source location</t>
+          <t>Supplier category</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Karnaphuli river ghat</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>30</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="13">
@@ -8400,14 +8153,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Fishery Ghat landing</t>
+          <t>Karnaphuli river ghat</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="14">
@@ -8423,14 +8176,14 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>Bhola charter landing</t>
+          <t>Fishery Ghat landing</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -8446,14 +8199,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kuakata</t>
+          <t>Bhola charter landing</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="16">
@@ -8473,10 +8226,10 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="17">
@@ -8492,7 +8245,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Moheshkhali</t>
+          <t>Kuakata</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -8515,14 +8268,14 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>Kutubdia</t>
+          <t>Moheshkhali</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -8538,7 +8291,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cox's Bazar landing</t>
+          <t>Kutubdia</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -8588,10 +8341,10 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>70</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="22">
@@ -8611,10 +8364,10 @@
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>26.7</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="23">
@@ -8634,10 +8387,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>56.7</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="24">
@@ -8653,7 +8406,7 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Faria</t>
+          <t>Fisherman</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -8676,14 +8429,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fisherman</t>
+          <t>Faria</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="26">
@@ -8703,10 +8456,10 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" s="8" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="27">
@@ -8726,10 +8479,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>70</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="28">
@@ -8745,14 +8498,14 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Hawker</t>
+          <t>Hotel</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28" s="8" t="n">
-        <v>10</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="29">
@@ -8768,14 +8521,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Hawker</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="30">
@@ -8791,14 +8544,14 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Institutional</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="8" t="n">
-        <v>6.7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -8814,14 +8567,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Institutional</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>3.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="32">
@@ -8841,10 +8594,10 @@
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F32" s="8" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="33">
@@ -8864,10 +8617,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34">
@@ -9047,43 +8800,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>6</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>1031.62</v>
+        <v>1045.02</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>1083.3</v>
+        <v>1093.4</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>1236.41</v>
+        <v>1286.17</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>1486.96</v>
+        <v>1533.71</v>
       </c>
       <c r="M5" s="6" t="n">
-        <v>1420</v>
+        <v>1518</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>51.68</v>
+        <v>48.38</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>153.11</v>
+        <v>192.77</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>183.59</v>
+        <v>231.83</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>388.38</v>
+        <v>472.98</v>
       </c>
       <c r="R5" s="6" t="n">
-        <v>72.59999999999999</v>
+        <v>68.8</v>
       </c>
     </row>
     <row r="6">
@@ -9103,7 +8856,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>6</v>
@@ -9113,34 +8866,34 @@
       </c>
       <c r="H6" s="7" t="inlineStr"/>
       <c r="I6" s="8" t="n">
-        <v>1110.67</v>
+        <v>1147.17</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>1165.59</v>
+        <v>1198.25</v>
       </c>
       <c r="K6" s="8" t="n">
-        <v>1378.04</v>
+        <v>1419.09</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>1619.16</v>
+        <v>1666.39</v>
       </c>
       <c r="M6" s="8" t="n">
-        <v>1615</v>
+        <v>1641.67</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>54.92</v>
+        <v>51.08</v>
       </c>
       <c r="O6" s="8" t="n">
-        <v>212.45</v>
+        <v>220.84</v>
       </c>
       <c r="P6" s="8" t="n">
-        <v>236.96</v>
+        <v>222.58</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>504.33</v>
+        <v>494.5</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>68.8</v>
+        <v>69.90000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -9160,43 +8913,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Descriptive-only (Method 3.8): consumer quotes n=1 (&lt;3; share not reported)</t>
+        </is>
       </c>
       <c r="I7" s="6" t="n">
-        <v>735.53</v>
+        <v>762.83</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>771.7</v>
+        <v>798.83</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>886.61</v>
+        <v>932.25</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>1069.64</v>
+        <v>1101.84</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>1033.33</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>36.17</v>
-      </c>
-      <c r="O7" s="6" t="n">
-        <v>114.91</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v>146.72</v>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>297.8</v>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v>71.2</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="8">
@@ -9222,38 +8965,38 @@
         <v>5</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
       <c r="I8" s="8" t="n">
-        <v>660.95</v>
+        <v>651.13</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>687.75</v>
+        <v>681.9400000000001</v>
       </c>
       <c r="K8" s="8" t="n">
-        <v>762.77</v>
+        <v>801.47</v>
       </c>
       <c r="L8" s="8" t="n">
-        <v>933.4400000000001</v>
+        <v>937.02</v>
       </c>
       <c r="M8" s="8" t="n">
-        <v>885</v>
+        <v>911.67</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>26.8</v>
+        <v>30.81</v>
       </c>
       <c r="O8" s="8" t="n">
-        <v>75.02</v>
+        <v>119.53</v>
       </c>
       <c r="P8" s="8" t="n">
-        <v>122.23</v>
+        <v>110.2</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>224.05</v>
+        <v>260.54</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>74.7</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -9273,43 +9016,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>6</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>407.79</v>
+        <v>414.49</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>428.72</v>
+        <v>433.75</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>501.77</v>
+        <v>505.48</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>581.23</v>
+        <v>601.3200000000001</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>585</v>
+        <v>609.4400000000001</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>20.93</v>
+        <v>19.26</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>73.05</v>
+        <v>71.73</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>83.23</v>
+        <v>103.96</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>177.21</v>
+        <v>194.95</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>69.7</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -9329,44 +9072,44 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>6</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="8" t="n">
-        <v>314.1</v>
+        <v>320.42</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>323.55</v>
+        <v>333.82</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>380.42</v>
+        <v>400.1</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>457.13</v>
+        <v>483.74</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>446.54</v>
+        <v>461.11</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>9.449999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>56.87</v>
+        <v>66.28</v>
       </c>
       <c r="P10" s="8" t="n">
-        <v>66.12</v>
+        <v>61.01</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>132.44</v>
+        <v>140.69</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>70.3</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="11">
@@ -9386,7 +9129,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>5</v>
@@ -9395,34 +9138,34 @@
         <v>7</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>361.74</v>
+        <v>368.44</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>377.81</v>
+        <v>385.18</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>450.16</v>
+        <v>451.61</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>545.45</v>
+        <v>542.45</v>
       </c>
       <c r="M11" s="6" t="n">
-        <v>530</v>
+        <v>540.71</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>16.07</v>
+        <v>16.74</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>72.34999999999999</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>79.84</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>168.26</v>
+        <v>172.27</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>68.3</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -9442,33 +9185,33 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>1</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
-          <t>Descriptive-only (Method 3.8): retail quotes in 2 market(s); consumer quotes n=1 (&lt;3; share not reported)</t>
+          <t>Descriptive-only (Method 3.8): retail quotes in 1 market(s); consumer quotes n=1 (&lt;3; share not reported)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n">
-        <v>231.78</v>
+        <v>257.23</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>241.16</v>
+        <v>267.95</v>
       </c>
       <c r="K12" s="8" t="n">
-        <v>279.01</v>
+        <v>288.05</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>325</v>
+        <v>345</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>330</v>
+        <v>365</v>
       </c>
       <c r="N12" s="7" t="n"/>
       <c r="O12" s="7" t="n"/>
@@ -9493,48 +9236,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>Descriptive-only (Method 3.8): retail quotes in 2 market(s)</t>
+          <t>Descriptive-only (Method 3.8): retail quotes in 1 market(s)</t>
         </is>
       </c>
       <c r="I13" s="6" t="n">
-        <v>188.91</v>
+        <v>202.31</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>195.61</v>
+        <v>211.68</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>234.46</v>
+        <v>231.97</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>263.01</v>
+        <v>257.5</v>
       </c>
       <c r="M13" s="6" t="n">
-        <v>267.5</v>
+        <v>282.5</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>6.7</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>38.85</v>
+        <v>20.29</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>33.04</v>
+        <v>50.53</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>78.59</v>
+        <v>80.19</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -9554,31 +9297,29 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Descriptive-only (Method 3.8): retail quotes in 1 market(s); consumer quotes n=1 (&lt;3; share not reported)</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="n">
-        <v>163.45</v>
-      </c>
+          <t>Descriptive-only (Method 3.8): retail quotes in 2 market(s)</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="n"/>
       <c r="J14" s="7" t="n"/>
       <c r="K14" s="8" t="n">
-        <v>179.53</v>
+        <v>207.39</v>
       </c>
       <c r="L14" s="8" t="n">
-        <v>230</v>
+        <v>252.28</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="N14" s="7" t="n"/>
       <c r="O14" s="7" t="n"/>
@@ -9594,7 +9335,7 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Mean of species means (chain-complete: S01, S02, S03, S04, S05, S06, S07, S09)</t>
+          <t>Mean of species means (chain-complete: S01, S02, S04, S05, S06, S07, S09)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9603,42 +9344,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>414</v>
+        <v>368</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
-          <t>Pooled over 8 chain-complete species (consumer n &gt;= 3)</t>
+          <t>Pooled over 7 chain-complete species (consumer n &gt;= 3)</t>
         </is>
       </c>
       <c r="I15" s="6" t="n">
-        <v>601.41</v>
+        <v>592.71</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>629.25</v>
+        <v>619.72</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>728.83</v>
+        <v>727.98</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>869.5</v>
+        <v>860.3</v>
       </c>
       <c r="M15" s="6" t="n">
-        <v>847.8</v>
+        <v>852.16</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>27.84</v>
+        <v>27.01</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>99.58</v>
+        <v>108.26</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>118.97</v>
+        <v>124.18</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>246.39</v>
+        <v>259.45</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>70.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -9663,7 +9404,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="38" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -9735,13 +9476,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>3.34</v>
+        <v>2.92</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>1.06</v>
+        <v>0.83</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -9769,10 +9510,10 @@
         <v>18</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>184444.44</v>
+        <v>187222.22</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>64986.17</v>
+        <v>109063.15</v>
       </c>
       <c r="H6" s="7" t="inlineStr"/>
     </row>
@@ -9796,10 +9537,10 @@
         <v>12</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>19583.33</v>
+        <v>10291.67</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>9440.799999999999</v>
+        <v>9321.18</v>
       </c>
     </row>
     <row r="8">
@@ -9819,13 +9560,13 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>8330.77</v>
+        <v>7937.93</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>3205.84</v>
+        <v>3302.86</v>
       </c>
       <c r="H8" s="7" t="inlineStr"/>
     </row>
@@ -9846,13 +9587,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>9025</v>
+        <v>7600</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>2223.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -9875,10 +9616,10 @@
         <v>30</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>5.37</v>
+        <v>5.47</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>2.47</v>
+        <v>2.26</v>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
@@ -9906,10 +9647,10 @@
         <v>30</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>636.67</v>
+        <v>673.33</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>122.43</v>
+        <v>93.53</v>
       </c>
     </row>
     <row r="12">
@@ -9929,13 +9670,13 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>6093.75</v>
+        <v>6700</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>3045.32</v>
+        <v>3298.32</v>
       </c>
       <c r="H12" s="7" t="inlineStr"/>
     </row>
@@ -9959,10 +9700,10 @@
         <v>30</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1880</v>
+        <v>1228.33</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>1172.21</v>
+        <v>649.23</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
@@ -9990,10 +9731,10 @@
         <v>30</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>1636.67</v>
+        <v>1976.67</v>
       </c>
       <c r="G14" s="8" t="n">
-        <v>821.89</v>
+        <v>894.3099999999999</v>
       </c>
       <c r="H14" s="7" t="inlineStr"/>
     </row>
@@ -10017,10 +9758,10 @@
         <v>30</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="16">
@@ -10043,10 +9784,10 @@
         <v>30</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>258.33</v>
+        <v>283.33</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>119.69</v>
+        <v>142.84</v>
       </c>
       <c r="H16" s="7" t="inlineStr"/>
     </row>
@@ -10070,10 +9811,10 @@
         <v>30</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>79.97</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>27.03</v>
+        <v>27.91</v>
       </c>
     </row>
     <row r="18">
@@ -10096,10 +9837,10 @@
         <v>30</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>259.33</v>
+        <v>234.67</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>91.91</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="H18" s="7" t="inlineStr"/>
     </row>
@@ -10120,13 +9861,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>3.62</v>
+        <v>3.05</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.96</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="20">
@@ -10146,13 +9887,13 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>700</v>
+        <v>775</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>244.95</v>
+        <v>486.24</v>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
     </row>
@@ -10176,10 +9917,10 @@
         <v>30</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4.8</v>
+        <v>5.23</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="22">
@@ -10202,10 +9943,10 @@
         <v>30</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>204.67</v>
+        <v>214.5</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>81.84</v>
+        <v>85.69</v>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
     </row>
@@ -10229,10 +9970,10 @@
         <v>30</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>185.33</v>
+        <v>171.5</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>56.54</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="24">
@@ -10255,10 +9996,10 @@
         <v>30</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>79.83</v>
+        <v>80.83</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>37.31</v>
+        <v>37.26</v>
       </c>
       <c r="H24" s="7" t="inlineStr"/>
     </row>
@@ -10282,10 +10023,10 @@
         <v>30</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>5.43</v>
+        <v>5.53</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
     </row>
   </sheetData>
@@ -10385,22 +10126,22 @@
     </row>
     <row r="5">
       <c r="B5" s="6" t="n">
-        <v>67.59999999999999</v>
+        <v>69.63</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>13.63</v>
+        <v>14.17</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>18.77</v>
+        <v>16.2</v>
       </c>
       <c r="E5" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>13</v>
-      </c>
       <c r="G5" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -10413,22 +10154,22 @@
     </row>
     <row r="6">
       <c r="B6" s="8" t="n">
-        <v>63.87</v>
+        <v>64</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>15.7</v>
+        <v>17.43</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>20.43</v>
+        <v>18.57</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
@@ -10443,19 +10184,19 @@
     </row>
     <row r="7">
       <c r="B7" s="6" t="n">
-        <v>55.23</v>
+        <v>55.1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>28.63</v>
+        <v>27.37</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>16.13</v>
+        <v>17.53</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>3</v>
@@ -10478,11 +10219,11 @@
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>bKash</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="I8" s="8" t="n">
-        <v>36.7</v>
+        <v>50</v>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
@@ -10496,11 +10237,11 @@
     <row r="9">
       <c r="H9" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Nagad_app</t>
         </is>
       </c>
       <c r="I9" s="6" t="n">
-        <v>36.7</v>
+        <v>23.3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -10520,7 +10261,7 @@
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>Nagad_app</t>
+          <t>bKash</t>
         </is>
       </c>
       <c r="I10" s="8" t="n">
@@ -10645,69 +10386,69 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Supply syndicate control</t>
+          <t>Day-to-day price volatility</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>36.7</v>
+        <v>23.3</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>30</v>
+        <v>33.3</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>26.7</v>
+        <v>40</v>
       </c>
       <c r="I5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>31.1</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Unsold fish spoilage loss</t>
+          <t>Low landings in lean season</t>
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E6" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="H6" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H6" s="8" t="n">
-        <v>23.3</v>
-      </c>
       <c r="I6" s="7" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J6" s="8" t="n">
-        <v>31.1</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Competition from frozen imported fish</t>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rising cost of ice and salt</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -10742,16 +10483,16 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>23.3</v>
+        <v>30</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>33.3</v>
+        <v>30</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>7</v>
@@ -10760,54 +10501,54 @@
         <v>23.3</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J8" s="8" t="n">
-        <v>26.7</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Day-to-day price volatility</t>
+          <t>Waterlogging during monsoon</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>23.3</v>
+        <v>33.3</v>
       </c>
       <c r="E9" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G9" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="H9" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="G9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>33.3</v>
-      </c>
       <c r="I9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>25.6</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Low landings in lean season</t>
+          <t>Transport cost increase</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>30</v>
+        <v>13.3</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>8</v>
@@ -10816,84 +10557,84 @@
         <v>26.7</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>16.7</v>
+        <v>36.7</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J10" s="8" t="n">
-        <v>24.4</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Waterlogging during monsoon</t>
+          <t>Delayed credit recovery</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" s="6" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>21</v>
+      </c>
+      <c r="J11" s="6" t="n">
         <v>23.3</v>
       </c>
-      <c r="E11" t="n">
+    </row>
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Rising toll and lease burden</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="H12" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="G11" t="n">
-        <v>9</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" t="n">
-        <v>22</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>24.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Irregular electricity and load-shedding</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D12" s="8" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" s="8" t="n">
-        <v>23.3</v>
-      </c>
       <c r="I12" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J12" s="8" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rising cost of ice and salt</t>
+          <t>Supply syndicate control</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -10909,41 +10650,41 @@
         <v>26.7</v>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="I13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Delayed credit recovery</t>
+          <t>Unsold fish spoilage loss</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>23.3</v>
+        <v>10</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>23.3</v>
+        <v>26.7</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>20</v>
@@ -10953,65 +10694,65 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Rising toll and lease burden</t>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Competition from frozen imported fish</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G15" t="n">
         <v>5</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="H15" s="6" t="n">
         <v>16.7</v>
       </c>
-      <c r="E15" t="n">
-        <v>8</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G15" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>23.3</v>
-      </c>
       <c r="I15" t="n">
+        <v>18</v>
+      </c>
+      <c r="J15" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="J15" s="6" t="n">
-        <v>22.2</v>
-      </c>
     </row>
     <row r="16">
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Transport cost increase</t>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Irregular electricity and load-shedding</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" s="8" t="n">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>16.7</v>
+        <v>30</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>26.7</v>
+        <v>13.3</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" s="8" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
     </row>
   </sheetData>

--- a/analysis_outputs/Analysis_Summary.xlsx
+++ b/analysis_outputs/Analysis_Summary.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E25"/>
+  <dimension ref="B2:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="2" max="2"/>
@@ -920,6 +920,7 @@
         <v>5</v>
       </c>
     </row>
+    <row r="26"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6355,7 +6356,7 @@
       <c r="F8" s="7" t="inlineStr"/>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>chi2=2.49, df=4, p=0.6472, G-test p=0.6349, Fisher-exact p=0.6603</t>
+          <t>chi2=2.49, df=4, p=0.6472, G-test p=0.6349, Fisher-exact p=0.6640</t>
         </is>
       </c>
     </row>
